--- a/EDRMS_Utilization_Report_Checker_2026-08-14.xlsx
+++ b/EDRMS_Utilization_Report_Checker_2026-08-14.xlsx
@@ -2036,7 +2036,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Ask Mihal Le which API returns the installed app list per site, for app {B255A2AF-7F63-4A30-966A-5D5FD99F97D7}. Why: it defines which sites are in the report at all</t>
+          <t>Ask Leah Bancale for the PRODUCTION Cloud Governance Workspace report export, and whether a converted site is recorded in Cloud Governance the same way a created one is. Why: 'EDRMS Site Type' in that export is the compliant site list, so this single file defines which sites are in the report at all</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -2659,7 +2659,7 @@
     <row r="26">
       <c r="B26" s="33" t="inlineStr">
         <is>
-          <t>These counts are formulas over the six dashboard sheets, not typed numbers, so they follow any edit made there. LibreOffice cannot recalculate in the build environment, so they ship without cached values: Excel computes them on open, but a lightweight previewer may show them blank. Counted by hand at build time there were 109 figures, being 19 , 19 Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report, 8 Ask whether a project site register exists: site URL to project number, and sovereign or nonsovereign. Check Cloud Governance first. Why: it is the only thing missing for the whole Project Insights dashboard, every measure on it is already producible, 7 Ask RAC for the physical holdings system: boxes, folders, locations, transfers and retrievals. Slide 67 names eServe for retrievals and shows an IR Dashboard screenshot. Why: none of it is in any system this report reads, and access to that dashboard may answer most of it, 5 Ask the development team to add a term reference to the document row, or supply a term to library mapping list. Why: nothing links a term to a document, so no per term figure can be produced even once the file plan is located, 4 Raise a change request for a disposal status field: status, approver, and date disposed. Why: nothing records that a disposal happened, so every completion figure is unanswerable, 4 Ask whether audit log access can be granted, and confirm the purpose. Why: access requests, external sharing and permission exceptions live in the audit log, a different Graph surface with a different permission set, 3 Ask which system owns staff, contractor and consultant classification and training completion. The client asks the same question on their own slide 54. Why: nothing in SharePoint holds it, 3 Ask who supplies division alongside department. Why: the tier was reinstated at the client's request but nothing in the tenant populates it, so the RAC list has to carry a division column too, 3 Ask whether an inactive site is 90 days or 300. The deck says 90, the metrics document says 300. Why: it changes every inactivity figure, and it is a one line change either way, 3 Ask who maintains this list and where it will live. Why: it is not a measurement, nothing can generate it, and without an owner the panel stays empty, 2 Confirm the 12 month window is the one they want on the tile, and that the 30 day, 90 day and 12 month figures should nest inside one another, 2 Ask Mihal Le which API returns the installed app list per site, for app {B255A2AF-7F63-4A30-966A-5D5FD99F97D7}. Why: it defines which sites are in the report at all. Also Ask whether an inactive site is 90 days or 300. The deck says 90, the metrics document says 300. Why: it changes every inactivity figure, and it is a one line change either way, 2 Ask where the institutional file plan actually lives. It is in neither the term store, which holds 6 dropdown value sets and 16 terms one level deep, nor Purview, which holds 53 flat retention labels. Why: a whole dashboard waits on the answer, 1 How should EDRMS User be defined? Aldo Enriquez raised this on 10 Aug and Kylee Williamson replied that it will need defining. Neither settled it, and every option is buildable today, so this is a definition to agree rather than work to do, 1 Four questions, in the FINAL REMARKS column, ready to send to development, 1 Ask the development team to capture Author on the document scan. Why: without it, creation activity can only be measured for records, not for documents, 1 None, but be explicit with the client that every rate waits on the scan, 1 Confirm that a deleted site should be counted from its disappearance between two exports. Why: absence cannot distinguish a deletion from a permissions change that hides the site, 1 Ask what archived means for a site, and how it is marked. Why: there is no definition anywhere, so the figure cannot be counted, 1 Confirm the job start date with the client. Why: the trend can only begin when weekly capture begins, and history never captured cannot be recovered, 1 Ask RAC for the file extension to format group mapping, a short list. Why: without it every extension falls into All other formats, 1 Tell the client this cannot be produced and offer records created per library instead. Why: Microsoft exposes no per library activity anywhere, 1 Ask whether a library owner is maintained anywhere. Why: the site owner is the only one the tenant returns, 1 Confirm the definition. Why: the client wrote 'with same filenames?' themselves, so they already suspect it is imprecise, 1 Confirm what counts as orphaned. Why: a missing site, a missing library and a missing owner give three different numbers, 1 Confirm the label names in use. Why: the tiles must carry the tenant's own wording, 1 Add External Sharing to the site table, and check the four link count columns on production. Why: they are all zero in the test tenant, which may mean no sharing or may mean not populated, and those are very different answers, 1 Tell the client search analytics cannot be attributed to a record. Why: Microsoft reports them at tenant level only, 1 Offer most active sites instead. Why: document grain analytics do not exist, 1 Warn the client only 7 day and all time windows exist. Why: their slide implies a monthly figure, 1 Ask where the institutional file plan actually lives. It is in neither the term store, which holds 6 dropdown value sets and 16 terms one level deep, nor Purview, which holds 53 flat retention labels. Why: a whole dashboard waits on the answer. Also Ask the development team to add a term reference to the document row, or supply a term to library mapping list. Why: nothing links a term to a document, so no per term figure can be produced even once the file plan is located, 1 Tell the client this is not available at library grain. Why: Microsoft exposes no per library viewer feed, 1 Ask the development team to add a term reference to the document row, or supply a term to library mapping list. Why: nothing links a term to a document, so no per term figure can be produced even once the file plan is located. Also Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report, 1 Ask what a business process is and how it relates to a file plan term. Why: the two are not the same thing, and it cannot be counted until somebody says what it counts, 1 Warn that this counts dates passed, not action outstanding. Why: the two read alike and are not the same, 1 Check the mapping list's key yourself before asking anyone. Why: it decides whether this metric is safe or fragile, and it is a five minute check, 1 Ask RAC for the physical holdings system: boxes, folders, locations, transfers and retrievals. Slide 67 names eServe for retrievals and shows an IR Dashboard screenshot. Why: none of it is in any system this report reads, and access to that dashboard may answer most of it. Answer their direct question: capacity can be displayed the moment somebody holds the figure, 1 Ask for access to the IR Dashboard shown on slide 67, and ask what is available in Opus. Why: both are their own questions to us, and the IR Dashboard may already hold most of this.</t>
+          <t>These counts are formulas over the six dashboard sheets, not typed numbers, so they follow any edit made there. LibreOffice cannot recalculate in the build environment, so they ship without cached values: Excel computes them on open, but a lightweight previewer may show them blank. Counted by hand at build time there were 109 figures, being 19 , 19 Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report, 8 Ask whether a project site register exists: site URL to project number, and sovereign or nonsovereign. Check Cloud Governance first. Why: it is the only thing missing for the whole Project Insights dashboard, every measure on it is already producible, 7 Ask RAC for the physical holdings system: boxes, folders, locations, transfers and retrievals. Slide 67 names eServe for retrievals and shows an IR Dashboard screenshot. Why: none of it is in any system this report reads, and access to that dashboard may answer most of it, 5 Ask the development team to add a term reference to the document row, or supply a term to library mapping list. Why: nothing links a term to a document, so no per term figure can be produced even once the file plan is located, 4 Raise a change request for a disposal status field: status, approver, and date disposed. Why: nothing records that a disposal happened, so every completion figure is unanswerable, 4 Ask whether audit log access can be granted, and confirm the purpose. Why: access requests, external sharing and permission exceptions live in the audit log, a different Graph surface with a different permission set, 3 Ask which system owns staff, contractor and consultant classification and training completion. The client asks the same question on their own slide 54. Why: nothing in SharePoint holds it, 3 Ask who supplies division alongside department. Why: the tier was reinstated at the client's request but nothing in the tenant populates it, so the RAC list has to carry a division column too, 3 Ask whether an inactive site is 90 days or 300. The deck says 90, the metrics document says 300. Why: it changes every inactivity figure, and it is a one line change either way, 3 Ask who maintains this list and where it will live. Why: it is not a measurement, nothing can generate it, and without an owner the panel stays empty, 2 Confirm the 12 month window is the one they want on the tile, and that the 30 day, 90 day and 12 month figures should nest inside one another, 2 Ask Leah Bancale for the PRODUCTION Cloud Governance Workspace report export, and whether a converted site is recorded in Cloud Governance the same way a created one is. Why: 'EDRMS Site Type' in that export is the compliant site list, so this single file defines which sites are in the report at all. Also Ask whether an inactive site is 90 days or 300. The deck says 90, the metrics document says 300. Why: it changes every inactivity figure, and it is a one line change either way, 2 Ask where the institutional file plan actually lives. It is in neither the term store, which holds 6 dropdown value sets and 16 terms one level deep, nor Purview, which holds 53 flat retention labels. Why: a whole dashboard waits on the answer, 1 How should EDRMS User be defined? Aldo Enriquez raised this on 10 Aug and Kylee Williamson replied that it will need defining. Neither settled it, and every option is buildable today, so this is a definition to agree rather than work to do, 1 Four questions, in the FINAL REMARKS column, ready to send to development, 1 Ask the development team to capture Author on the document scan. Why: without it, creation activity can only be measured for records, not for documents, 1 None, but be explicit with the client that every rate waits on the scan, 1 Confirm that a deleted site should be counted from its disappearance between two exports. Why: absence cannot distinguish a deletion from a permissions change that hides the site, 1 Ask what archived means for a site, and how it is marked. Why: there is no definition anywhere, so the figure cannot be counted, 1 Confirm the job start date with the client. Why: the trend can only begin when weekly capture begins, and history never captured cannot be recovered, 1 Ask RAC for the file extension to format group mapping, a short list. Why: without it every extension falls into All other formats, 1 Tell the client this cannot be produced and offer records created per library instead. Why: Microsoft exposes no per library activity anywhere, 1 Ask whether a library owner is maintained anywhere. Why: the site owner is the only one the tenant returns, 1 Confirm the definition. Why: the client wrote 'with same filenames?' themselves, so they already suspect it is imprecise, 1 Confirm what counts as orphaned. Why: a missing site, a missing library and a missing owner give three different numbers, 1 Confirm the label names in use. Why: the tiles must carry the tenant's own wording, 1 Add External Sharing to the site table, and check the four link count columns on production. Why: they are all zero in the test tenant, which may mean no sharing or may mean not populated, and those are very different answers, 1 Tell the client search analytics cannot be attributed to a record. Why: Microsoft reports them at tenant level only, 1 Offer most active sites instead. Why: document grain analytics do not exist, 1 Warn the client only 7 day and all time windows exist. Why: their slide implies a monthly figure, 1 Ask where the institutional file plan actually lives. It is in neither the term store, which holds 6 dropdown value sets and 16 terms one level deep, nor Purview, which holds 53 flat retention labels. Why: a whole dashboard waits on the answer. Also Ask the development team to add a term reference to the document row, or supply a term to library mapping list. Why: nothing links a term to a document, so no per term figure can be produced even once the file plan is located, 1 Tell the client this is not available at library grain. Why: Microsoft exposes no per library viewer feed, 1 Ask the development team to add a term reference to the document row, or supply a term to library mapping list. Why: nothing links a term to a document, so no per term figure can be produced even once the file plan is located. Also Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report, 1 Ask what a business process is and how it relates to a file plan term. Why: the two are not the same thing, and it cannot be counted until somebody says what it counts, 1 Warn that this counts dates passed, not action outstanding. Why: the two read alike and are not the same, 1 Check the mapping list's key yourself before asking anyone. Why: it decides whether this metric is safe or fragile, and it is a five minute check, 1 Ask RAC for the physical holdings system: boxes, folders, locations, transfers and retrievals. Slide 67 names eServe for retrievals and shows an IR Dashboard screenshot. Why: none of it is in any system this report reads, and access to that dashboard may answer most of it. Answer their direct question: capacity can be displayed the moment somebody holds the figure, 1 Ask for access to the IR Dashboard shown on slide 67, and ask what is available in Opus. Why: both are their own questions to us, and the IR Dashboard may already hold most of this.</t>
         </is>
       </c>
     </row>
@@ -3399,15 +3399,750 @@
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
+          <t>AvePoint Cloud Governance</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Governance Workspace report, exported as CSV</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>1. Open AvePoint Online Services, then Cloud Governance
+2. Left nav: Directory, then Workspace report
+3. Click Export report, top left. The file is queued, not downloaded immediately
+4. Collect it from Job monitor in the left nav when the job shows green
+5. The export carries 93 columns and one row per workspace, 1,209 in the test tenant. 45 of those columns are empty on every row, so check population before relying on one
+6. The column that matters is 'EDRMS Site Type'. Filter to rows where it is not blank</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>'EDRMS Site Type', 'Status', 'Last Active Time', 'Department'</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Filter to rows where 'EDRMS Site Type' is not blank, which is the compliant site list, then keep rows where 'Status' is Active, then count. In the test tenant that is 1,032 sites of 1,209 workspaces. Break down by 'Department'. This REPLACES the earlier recipe over the M365 usage export, which could not apply a compliance filter at all and fills Last Activity Date on only 381 of 1,918 live sites. Cloud Governance fills it on every row</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>2 Site Activity</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>IsEdrmsCompliant, LastActivityDate, ADBDepartmentOwner</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>Yes, 2 need a rule</t>
+        </is>
+      </c>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>Yes, in test</t>
+        </is>
+      </c>
+      <c r="O10" s="10" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="P10" s="12" t="inlineStr">
+        <is>
+          <t>Needs department list</t>
+        </is>
+      </c>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
+          <t>Ask Leah Bancale for the PRODUCTION Cloud Governance Workspace report export, and whether a converted site is recorded in Cloud Governance the same way a created one is. Why: 'EDRMS Site Type' in that export is the compliant site list, so this single file defines which sites are in the report at all. Also Ask whether an inactive site is 90 days or 300. The deck says 90, the metrics document says 300. Why: it changes every inactivity figure, and it is a one line change either way</t>
+        </is>
+      </c>
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>How do we determine the list of all edrms compliant sites? Currently we know a site is an edrms compliant if it gets cg adopted. How are we going to know these list? Is it possible that all sites in the cloud governance be the count for this? Essentially when a site is cg created it is found in cloud governance and is it possible that all cg adopted sites are going to be move to the cloud governance then from there we can get the list?</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>ANSWERED 14 Aug 2026 by exporting the Cloud Governance Workspace report.
+The export carries 93 columns over 1,209 workspaces. The column 'EDRMS Site Type' is populated on 1,032 rows with a single value, 'EDRMS Project Site'. It is a yes/no flag and it is the compliant site list. The 177 blanks are template and admin sites: edrmstemplate, template_drmdefault, app_edrms_data.
+1,032 against the 1,057 placeholder that has been in the prototype since before this project. Nobody could justify that number. It was close.
+'Department' is populated on 1,030 of the 1,032. That is the site to department mapping RAC has been asked for and 29 requirements have been waiting on. BUT 240 sites carry SEVERAL departments, semicolon separated, such as ADBI;BOD and ADBI;BOD;CSD;CWRD;SARD. That is 23 percent, and it contradicts the 10 August decision that a site has one department owner.
+Also arriving with it, all 100 percent populated over the 1,032: Created Time, Last Active Time, Primary Business Owner, Storage Used (GB), Storage Quota (GB), External Sharing for Site, and Status as Active, Locked or Archived.
+'Last Active Time' is the important one for THIS row. The M365 usage export fills Last Activity Date on only 381 of 1,918 live sites, so most sites cannot be judged active or inactive from it. Cloud Governance fills it on every row.
+NOT VERIFIED: whether every workspace carrying 'EDRMS Site Type' actually has the app installed. A register records intent. The app records reality. They can drift and nothing announces it.
+TEST TENANT. Every URL is 7rkd12 and the site names are generated, such as dane-Site-Title-ddos-125. No count here transfers to production.</t>
+        </is>
+      </c>
+      <c r="T10" s="10" t="inlineStr">
+        <is>
+          <t>Get the list from the cloud governance. In cloud gov, sites listed are both cg adopted and cg created which are the basis of the edrms compliant site number.
+Leah Bancale confirmed on 14 Aug that EDRMS sites exist which did not come through Cloud Governance originally, and that those get converted to become compliant. So the CG CREATED list alone would be incomplete: it would miss every converted site, and those are the older, established departmental sites most likely to hold the largest volume of declared records.
+This is the better definition, not merely the easier one. A site RAC designated as EDRMS where the app deployment failed disappears entirely under a technical test, and nobody ever learns it is broken. Under the register it appears with zero declared records and somebody asks why. That gap is a compliance finding worth reporting.
+STILL TO DO:
+1. Get the PRODUCTION export. Everything above is structure learned from the test tenant.
+2. Confirm a converted site is recorded in Cloud Governance the same way a created one is.
+3. Validate the register against the app once, on a sample of about twenty sites, in both directions.
+4. Put the multi-department question to RAC. Either a document counts to several departments, and departmental totals will not sum to the bank-wide figure, or one is picked as primary and the rest are dropped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Top panel</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Active EDRMS Sites, Sovereign Projects</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Sites belonging to sovereign projects</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>No source</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>No file exists</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>No column in any export identifies a project site</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Cannot be worked out. Once a project register exists, it would be: count the sites whose project number is a sovereign facility</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>2 Site Activity</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>No column exists</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O11" s="10" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="P11" s="13" t="inlineStr">
+        <is>
+          <t>Needs new data source</t>
+        </is>
+      </c>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>Ask whether a project site register exists: site URL to project number, and sovereign or nonsovereign. Check Cloud Governance first. Why: it is the only thing missing for the whole Project Insights dashboard, every measure on it is already producible</t>
+        </is>
+      </c>
+      <c r="R11" s="10" t="inlineStr"/>
+      <c r="S11" s="10" t="inlineStr"/>
+      <c r="T11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Top panel</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Active EDRMS Sites, Nonsovereign Projects</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Sites belonging to nonsovereign projects</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>No source</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>No file exists</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>No column in any export identifies a project site</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>Cannot be worked out. Same as the row above, filtered to nonsovereign</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>2 Site Activity</t>
+        </is>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>No column exists</t>
+        </is>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O12" s="10" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="P12" s="13" t="inlineStr">
+        <is>
+          <t>Needs new data source</t>
+        </is>
+      </c>
+      <c r="Q12" s="10" t="inlineStr">
+        <is>
+          <t>Ask whether a project site register exists: site URL to project number, and sovereign or nonsovereign. Check Cloud Governance first. Why: it is the only thing missing for the whole Project Insights dashboard, every measure on it is already producible</t>
+        </is>
+      </c>
+      <c r="R12" s="10" t="inlineStr"/>
+      <c r="S12" s="10" t="inlineStr"/>
+      <c r="T12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Users drill</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Never accessed EDRMS</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Licensed users who have never opened anything</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
           <t>M365 usage report</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>SharePoint activity user detail report, exported as CSV</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointActivity
+2. Sign in as a Microsoft 365 reports reader or global reader
+3. Set the period selector to 30 days
+4. Click Export. A CSV downloads, named like SharePointActivityUserDetail_2026-08-12.csv
+5. Open it in Excel. It has 12 columns and one row per LICENSED user, 30 rows in the test tenant. It is NOT a list of active users, which is the mistake to avoid</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>'Last Activity Date'</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>Count the rows where 'Last Activity Date' is BLANK. In the test tenant that is 5 of the 30 rows. A blank means the person has a licence but has never touched SharePoint</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>3 User Activity</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>LastActivityDate</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O13" s="10" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="P13" s="11" t="inlineStr">
+        <is>
+          <t>Buildable now</t>
+        </is>
+      </c>
+      <c r="Q13" s="10" t="inlineStr"/>
+      <c r="R13" s="10" t="inlineStr"/>
+      <c r="S13" s="10" t="inlineStr"/>
+      <c r="T13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Users drill</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>No access in 90 days</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Users who have gone quiet</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>M365 usage report</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>SharePoint activity user detail report, exported as CSV</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointActivity
+2. Sign in as a Microsoft 365 reports reader or global reader
+3. Set the period selector to 30 days
+4. Click Export. A CSV downloads, named like SharePointActivityUserDetail_2026-08-12.csv
+5. Open it in Excel. It has 12 columns and one row per LICENSED user, 30 rows in the test tenant. It is NOT a list of active users, which is the mistake to avoid</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>'Last Activity Date'</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>Count rows where 'Last Activity Date' is not blank AND is older than 90 days from the 'Report Refresh Date' at the top of the same row. Use the refresh date, not today, because Microsoft's figures lag by about two days</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>3 User Activity</t>
+        </is>
+      </c>
+      <c r="L14" s="10" t="inlineStr">
+        <is>
+          <t>LastActivityDate</t>
+        </is>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O14" s="10" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="P14" s="11" t="inlineStr">
+        <is>
+          <t>Buildable now</t>
+        </is>
+      </c>
+      <c r="Q14" s="10" t="inlineStr"/>
+      <c r="R14" s="10" t="inlineStr"/>
+      <c r="S14" s="10" t="inlineStr"/>
+      <c r="T14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Users drill</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Staff, Contractors, Consultants</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Employment class of each user</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>No source</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>No file exists</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Nothing in the user export gives employment type. 'Assigned Products' gives the licence name only, such as MICROSOFT 365 E5 DEVELOPER</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>Cannot be worked out from any Microsoft export. It would be a join from an HR or LMS extract on 'User Principal Name'</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>3 User Activity</t>
+        </is>
+      </c>
+      <c r="L15" s="10" t="inlineStr">
+        <is>
+          <t>No column exists</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O15" s="10" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="P15" s="13" t="inlineStr">
+        <is>
+          <t>Needs new data source</t>
+        </is>
+      </c>
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>Ask which system owns staff, contractor and consultant classification and training completion. The client asks the same question on their own slide 54. Why: nothing in SharePoint holds it</t>
+        </is>
+      </c>
+      <c r="R15" s="10" t="inlineStr"/>
+      <c r="S15" s="10" t="inlineStr"/>
+      <c r="T15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Users drill</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Training completion</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>Share of users who completed training</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>No source</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>No file exists</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>No column exists in any Microsoft export</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>Cannot be worked out. Would be completed / total, both from a training system</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
+        <is>
+          <t>No column exists</t>
+        </is>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O16" s="10" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="P16" s="14" t="inlineStr">
+        <is>
+          <t>Needs reference list</t>
+        </is>
+      </c>
+      <c r="Q16" s="10" t="inlineStr">
+        <is>
+          <t>Ask which system owns staff, contractor and consultant classification and training completion. The client asks the same question on their own slide 54. Why: nothing in SharePoint holds it</t>
+        </is>
+      </c>
+      <c r="R16" s="10" t="inlineStr"/>
+      <c r="S16" s="10" t="inlineStr"/>
+      <c r="T16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Users drill</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>By department</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Every user figure cut by department</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>No source</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>No file exists</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>No department column exists in the user export</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>Cannot be worked out yet. Once the RAC list exists: match the user to their sites, then to the department that owns those sites</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>3 User Activity</t>
+        </is>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>ADBDepartmentOwner</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>Column exists, unpopulated</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O17" s="10" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="P17" s="12" t="inlineStr">
+        <is>
+          <t>Needs department list</t>
+        </is>
+      </c>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
+        </is>
+      </c>
+      <c r="R17" s="10" t="inlineStr"/>
+      <c r="S17" s="10" t="inlineStr"/>
+      <c r="T17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Documents drill</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Documents held per department</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Volume of content</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>M365 usage report</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>SharePoint site usage report, exported as CSV</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
 2. Sign in as a Microsoft 365 reports reader or global reader
@@ -3417,706 +4152,90 @@
 6. WARNING: the Site URL column is EMPTY on every row. Use Site Id and match it to a site list from Graph if you need the address</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>'Last Activity Date', 'Is Deleted', and the compliance rule</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>Filter out rows where 'Is Deleted' is True, then keep rows where 'Last Activity Date' is within the last 90 days, then count them. In the test tenant 'Last Activity Date' is filled on only 381 of the 1,918 live sites, so the rest cannot be judged either way. The compliance filter cannot be applied at all yet, see the question column</t>
-        </is>
-      </c>
-      <c r="K10" s="10" t="inlineStr">
-        <is>
-          <t>2 Site Activity</t>
-        </is>
-      </c>
-      <c r="L10" s="10" t="inlineStr">
-        <is>
-          <t>IsEdrmsCompliant, LastActivityDate, ADBDepartmentOwner</t>
-        </is>
-      </c>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>Yes, 2 need a rule</t>
-        </is>
-      </c>
-      <c r="N10" s="10" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>'File Count' and 'Site Id'</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>Sum 'File Count' grouped by the department that owns each site. The department comes from the RAC list matched on site, it is not in the export</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>1 Utilization Report</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>FileCreatedDate, SiteUrl</t>
+        </is>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N18" s="10" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="O10" s="10" t="inlineStr">
+      <c r="O18" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="P10" s="12" t="inlineStr">
+      <c r="P18" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q10" s="10" t="inlineStr">
-        <is>
-          <t>Ask Mihal Le which API returns the installed app list per site, for app {B255A2AF-7F63-4A30-966A-5D5FD99F97D7}. Why: it defines which sites are in the report at all. Also Ask whether an inactive site is 90 days or 300. The deck says 90, the metrics document says 300. Why: it changes every inactivity figure, and it is a one line change either way</t>
-        </is>
-      </c>
-      <c r="R10" s="10" t="inlineStr"/>
-      <c r="S10" s="10" t="inlineStr"/>
-      <c r="T10" s="10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Top panel</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Active EDRMS Sites, Sovereign Projects</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>Sites belonging to sovereign projects</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>No source</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>No file exists</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>No column in any export identifies a project site</t>
-        </is>
-      </c>
-      <c r="J11" s="10" t="inlineStr">
-        <is>
-          <t>Cannot be worked out. Once a project register exists, it would be: count the sites whose project number is a sovereign facility</t>
-        </is>
-      </c>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t>2 Site Activity</t>
-        </is>
-      </c>
-      <c r="L11" s="10" t="inlineStr">
-        <is>
-          <t>No column exists</t>
-        </is>
-      </c>
-      <c r="M11" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N11" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O11" s="10" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="P11" s="13" t="inlineStr">
-        <is>
-          <t>Needs new data source</t>
-        </is>
-      </c>
-      <c r="Q11" s="10" t="inlineStr">
-        <is>
-          <t>Ask whether a project site register exists: site URL to project number, and sovereign or nonsovereign. Check Cloud Governance first. Why: it is the only thing missing for the whole Project Insights dashboard, every measure on it is already producible</t>
-        </is>
-      </c>
-      <c r="R11" s="10" t="inlineStr"/>
-      <c r="S11" s="10" t="inlineStr"/>
-      <c r="T11" s="10" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Top panel</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Active EDRMS Sites, Nonsovereign Projects</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>Sites belonging to nonsovereign projects</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>No source</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>No file exists</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>No column in any export identifies a project site</t>
-        </is>
-      </c>
-      <c r="J12" s="10" t="inlineStr">
-        <is>
-          <t>Cannot be worked out. Same as the row above, filtered to nonsovereign</t>
-        </is>
-      </c>
-      <c r="K12" s="10" t="inlineStr">
-        <is>
-          <t>2 Site Activity</t>
-        </is>
-      </c>
-      <c r="L12" s="10" t="inlineStr">
-        <is>
-          <t>No column exists</t>
-        </is>
-      </c>
-      <c r="M12" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N12" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O12" s="10" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="P12" s="13" t="inlineStr">
-        <is>
-          <t>Needs new data source</t>
-        </is>
-      </c>
-      <c r="Q12" s="10" t="inlineStr">
-        <is>
-          <t>Ask whether a project site register exists: site URL to project number, and sovereign or nonsovereign. Check Cloud Governance first. Why: it is the only thing missing for the whole Project Insights dashboard, every measure on it is already producible</t>
-        </is>
-      </c>
-      <c r="R12" s="10" t="inlineStr"/>
-      <c r="S12" s="10" t="inlineStr"/>
-      <c r="T12" s="10" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Users drill</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>Never accessed EDRMS</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>Licensed users who have never opened anything</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="Q18" s="10" t="inlineStr">
+        <is>
+          <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
+        </is>
+      </c>
+      <c r="R18" s="10" t="inlineStr"/>
+      <c r="S18" s="10" t="inlineStr"/>
+      <c r="T18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Documents drill</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Storage per department</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Space consumed</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>M365 usage report</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>SharePoint activity user detail report, exported as CSV</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointActivity
-2. Sign in as a Microsoft 365 reports reader or global reader
-3. Set the period selector to 30 days
-4. Click Export. A CSV downloads, named like SharePointActivityUserDetail_2026-08-12.csv
-5. Open it in Excel. It has 12 columns and one row per LICENSED user, 30 rows in the test tenant. It is NOT a list of active users, which is the mistake to avoid</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>'Last Activity Date'</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="inlineStr">
-        <is>
-          <t>Count the rows where 'Last Activity Date' is BLANK. In the test tenant that is 5 of the 30 rows. A blank means the person has a licence but has never touched SharePoint</t>
-        </is>
-      </c>
-      <c r="K13" s="10" t="inlineStr">
-        <is>
-          <t>3 User Activity</t>
-        </is>
-      </c>
-      <c r="L13" s="10" t="inlineStr">
-        <is>
-          <t>LastActivityDate</t>
-        </is>
-      </c>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N13" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O13" s="10" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="P13" s="11" t="inlineStr">
-        <is>
-          <t>Buildable now</t>
-        </is>
-      </c>
-      <c r="Q13" s="10" t="inlineStr"/>
-      <c r="R13" s="10" t="inlineStr"/>
-      <c r="S13" s="10" t="inlineStr"/>
-      <c r="T13" s="10" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Users drill</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>No access in 90 days</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>Users who have gone quiet</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>M365 usage report</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>SharePoint activity user detail report, exported as CSV</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointActivity
-2. Sign in as a Microsoft 365 reports reader or global reader
-3. Set the period selector to 30 days
-4. Click Export. A CSV downloads, named like SharePointActivityUserDetail_2026-08-12.csv
-5. Open it in Excel. It has 12 columns and one row per LICENSED user, 30 rows in the test tenant. It is NOT a list of active users, which is the mistake to avoid</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>'Last Activity Date'</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>Count rows where 'Last Activity Date' is not blank AND is older than 90 days from the 'Report Refresh Date' at the top of the same row. Use the refresh date, not today, because Microsoft's figures lag by about two days</t>
-        </is>
-      </c>
-      <c r="K14" s="10" t="inlineStr">
-        <is>
-          <t>3 User Activity</t>
-        </is>
-      </c>
-      <c r="L14" s="10" t="inlineStr">
-        <is>
-          <t>LastActivityDate</t>
-        </is>
-      </c>
-      <c r="M14" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N14" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O14" s="10" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="P14" s="11" t="inlineStr">
-        <is>
-          <t>Buildable now</t>
-        </is>
-      </c>
-      <c r="Q14" s="10" t="inlineStr"/>
-      <c r="R14" s="10" t="inlineStr"/>
-      <c r="S14" s="10" t="inlineStr"/>
-      <c r="T14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Users drill</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Staff, Contractors, Consultants</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>Employment class of each user</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>No source</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>No file exists</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>Nothing in the user export gives employment type. 'Assigned Products' gives the licence name only, such as MICROSOFT 365 E5 DEVELOPER</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="inlineStr">
-        <is>
-          <t>Cannot be worked out from any Microsoft export. It would be a join from an HR or LMS extract on 'User Principal Name'</t>
-        </is>
-      </c>
-      <c r="K15" s="10" t="inlineStr">
-        <is>
-          <t>3 User Activity</t>
-        </is>
-      </c>
-      <c r="L15" s="10" t="inlineStr">
-        <is>
-          <t>No column exists</t>
-        </is>
-      </c>
-      <c r="M15" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N15" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O15" s="10" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="P15" s="13" t="inlineStr">
-        <is>
-          <t>Needs new data source</t>
-        </is>
-      </c>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>Ask which system owns staff, contractor and consultant classification and training completion. The client asks the same question on their own slide 54. Why: nothing in SharePoint holds it</t>
-        </is>
-      </c>
-      <c r="R15" s="10" t="inlineStr"/>
-      <c r="S15" s="10" t="inlineStr"/>
-      <c r="T15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Users drill</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Training completion</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>Share of users who completed training</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>No source</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>No file exists</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>No column exists in any Microsoft export</t>
-        </is>
-      </c>
-      <c r="J16" s="10" t="inlineStr">
-        <is>
-          <t>Cannot be worked out. Would be completed / total, both from a training system</t>
-        </is>
-      </c>
-      <c r="K16" s="10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L16" s="10" t="inlineStr">
-        <is>
-          <t>No column exists</t>
-        </is>
-      </c>
-      <c r="M16" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N16" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O16" s="10" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="P16" s="14" t="inlineStr">
-        <is>
-          <t>Needs reference list</t>
-        </is>
-      </c>
-      <c r="Q16" s="10" t="inlineStr">
-        <is>
-          <t>Ask which system owns staff, contractor and consultant classification and training completion. The client asks the same question on their own slide 54. Why: nothing in SharePoint holds it</t>
-        </is>
-      </c>
-      <c r="R16" s="10" t="inlineStr"/>
-      <c r="S16" s="10" t="inlineStr"/>
-      <c r="T16" s="10" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>Users drill</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>By department</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>Every user figure cut by department</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>No source</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>No file exists</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>No department column exists in the user export</t>
-        </is>
-      </c>
-      <c r="J17" s="10" t="inlineStr">
-        <is>
-          <t>Cannot be worked out yet. Once the RAC list exists: match the user to their sites, then to the department that owns those sites</t>
-        </is>
-      </c>
-      <c r="K17" s="10" t="inlineStr">
-        <is>
-          <t>3 User Activity</t>
-        </is>
-      </c>
-      <c r="L17" s="10" t="inlineStr">
-        <is>
-          <t>ADBDepartmentOwner</t>
-        </is>
-      </c>
-      <c r="M17" s="10" t="inlineStr">
-        <is>
-          <t>Column exists, unpopulated</t>
-        </is>
-      </c>
-      <c r="N17" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O17" s="10" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="P17" s="12" t="inlineStr">
-        <is>
-          <t>Needs department list</t>
-        </is>
-      </c>
-      <c r="Q17" s="10" t="inlineStr">
-        <is>
-          <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
-        </is>
-      </c>
-      <c r="R17" s="10" t="inlineStr"/>
-      <c r="S17" s="10" t="inlineStr"/>
-      <c r="T17" s="10" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Documents drill</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Documents held per department</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>Volume of content</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>M365 usage report</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>SharePoint site usage report, exported as CSV</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
 2. Sign in as a Microsoft 365 reports reader or global reader
@@ -4126,90 +4245,1065 @@
 6. WARNING: the Site URL column is EMPTY on every row. Use Site Id and match it to a site list from Graph if you need the address</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>'File Count' and 'Site Id'</t>
-        </is>
-      </c>
-      <c r="J18" s="10" t="inlineStr">
-        <is>
-          <t>Sum 'File Count' grouped by the department that owns each site. The department comes from the RAC list matched on site, it is not in the export</t>
-        </is>
-      </c>
-      <c r="K18" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>'Storage Used (Byte)'</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>Sum 'Storage Used (Byte)' then divide by 1,073,741,824 to get GB. The test tenant totals 142.4 GB. NOTE this includes version history, so it reads higher than the sum of file sizes, which is expected and not an error</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>2 Site Activity</t>
+        </is>
+      </c>
+      <c r="L19" s="10" t="inlineStr">
+        <is>
+          <t>StorageUsed</t>
+        </is>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O19" s="10" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="P19" s="12" t="inlineStr">
+        <is>
+          <t>Needs department list</t>
+        </is>
+      </c>
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
+          <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
+        </is>
+      </c>
+      <c r="R19" s="10" t="inlineStr"/>
+      <c r="S19" s="10" t="inlineStr"/>
+      <c r="T19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Documents drill</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Users creating documents</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Distinct authors</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>No source</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>No file exists</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>No author column exists in any export, and the scan does not capture one</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>Cannot be worked out for undeclared documents. For declared records only, it would be COUNT(DISTINCT "CreatedBy") on the Records table, which counts declarers not authors</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
         <is>
           <t>1 Utilization Report</t>
         </is>
       </c>
-      <c r="L18" s="10" t="inlineStr">
-        <is>
-          <t>FileCreatedDate, SiteUrl</t>
-        </is>
-      </c>
-      <c r="M18" s="10" t="inlineStr">
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>CreatedBy covers declarers only</t>
+        </is>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O20" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P20" s="15" t="inlineStr">
+        <is>
+          <t>Needs new column or join</t>
+        </is>
+      </c>
+      <c r="Q20" s="10" t="inlineStr">
+        <is>
+          <t>Ask the development team to capture Author on the document scan. Why: without it, creation activity can only be measured for records, not for documents</t>
+        </is>
+      </c>
+      <c r="R20" s="10" t="inlineStr"/>
+      <c r="S20" s="10" t="inlineStr"/>
+      <c r="T20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Records drill</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Records declared per department</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Declaration volume</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>The EDRMS database, drm-npr, table public."Records"</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>1. Connect to the drm-npr PostgreSQL database with any SQL client
+2. The table is public."Records", quoted because of the capital R
+3. It holds DECLARED RECORDS ONLY, about 1,990 rows in UAT. There is no row for a document that was never declared, which is why every rate needs the scan built first</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>The whole table, plus SiteUrl to attach a department</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) FROM public."Records" GROUP BY the department that owns "SiteUrl". The department itself comes from the RAC list, matched on site URL</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>1 Utilization Report</t>
+        </is>
+      </c>
+      <c r="L21" s="10" t="inlineStr">
+        <is>
+          <t>IsDeclaredRecord, ADBDepartmentOwner</t>
+        </is>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N18" s="10" t="inlineStr">
+      <c r="N21" s="10" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="O18" s="10" t="inlineStr">
+      <c r="O21" s="10" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="P21" s="12" t="inlineStr">
+        <is>
+          <t>Needs department list</t>
+        </is>
+      </c>
+      <c r="Q21" s="10" t="inlineStr">
+        <is>
+          <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
+        </is>
+      </c>
+      <c r="R21" s="10" t="inlineStr"/>
+      <c r="S21" s="10" t="inlineStr"/>
+      <c r="T21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Records drill</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Users declaring records</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>How many people are declaring</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>The EDRMS database, drm-npr, table public."Records"</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>1. Connect to the drm-npr PostgreSQL database with any SQL client
+2. The table is public."Records", quoted because of the capital R
+3. It holds DECLARED RECORDS ONLY, about 1,990 rows in UAT. There is no row for a document that was never declared, which is why every rate needs the scan built first</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>'CreatedBy'</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(DISTINCT "CreatedBy") FROM public."Records". Distinct, not a row count, or one person declaring 400 records counts 400 times</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>1 Utilization Report</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="inlineStr">
+        <is>
+          <t>CreatedBy</t>
+        </is>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O22" s="10" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="P22" s="12" t="inlineStr">
+        <is>
+          <t>Needs department list</t>
+        </is>
+      </c>
+      <c r="Q22" s="10" t="inlineStr">
+        <is>
+          <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
+        </is>
+      </c>
+      <c r="R22" s="10" t="inlineStr"/>
+      <c r="S22" s="10" t="inlineStr"/>
+      <c r="T22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Records drill</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Declaration rate</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>Share of content formally declared</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>No single file. Computed from the tables above</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>Produced by the refresh job from the sources above rather than read from one export. Verify it by checking the inputs named in the next two columns</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Two numbers: declared records, and total documents</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>Records Declared divided by Total Documents, times 100. The numerator comes from the Records table, the denominator from the scan. Until the scan exists this rate CANNOT be produced, because the denominator does not exist anywhere</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>1 Utilization Report</t>
+        </is>
+      </c>
+      <c r="L23" s="10" t="inlineStr">
+        <is>
+          <t>IsDeclaredRecord over all rows</t>
+        </is>
+      </c>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O23" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="P18" s="12" t="inlineStr">
+      <c r="P23" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q18" s="10" t="inlineStr">
+      <c r="Q23" s="10" t="inlineStr">
+        <is>
+          <t>None, but be explicit with the client that every rate waits on the scan</t>
+        </is>
+      </c>
+      <c r="R23" s="10" t="inlineStr"/>
+      <c r="S23" s="10" t="inlineStr"/>
+      <c r="T23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Records drill</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>By division</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Drill tier</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>The same figures one level below department</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>No source</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>No file exists</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>No division column exists anywhere</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>Cannot be worked out. The RAC list would have to carry a division alongside department</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>1 Utilization Report</t>
+        </is>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>No division column exists</t>
+        </is>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O24" s="10" t="inlineStr">
+        <is>
+          <t>Easy once supplied</t>
+        </is>
+      </c>
+      <c r="P24" s="13" t="inlineStr">
+        <is>
+          <t>Needs new data source</t>
+        </is>
+      </c>
+      <c r="Q24" s="10" t="inlineStr">
+        <is>
+          <t>Ask who supplies division alongside department. Why: the tier was reinstated at the client's request but nothing in the tenant populates it, so the RAC list has to carry a division column too</t>
+        </is>
+      </c>
+      <c r="R24" s="10" t="inlineStr"/>
+      <c r="S24" s="10" t="inlineStr"/>
+      <c r="T24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Counterparts drill</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Physical counterparts by department</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>Records with a paper copy</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>The EDRMS database, drm-npr, table public."Records"</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>1. Connect to the drm-npr PostgreSQL database with any SQL client
+2. The table is public."Records", quoted because of the capital R
+3. It holds DECLARED RECORDS ONLY, about 1,990 rows in UAT. There is no row for a document that was never declared, which is why every rate needs the scan built first</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>EDRMSMeta key HasPhysical, plus SiteUrl</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>Count rows where the HasPhysical key is true, grouped by the department that owns the site</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>1 Utilization Report</t>
+        </is>
+      </c>
+      <c r="L25" s="10" t="inlineStr">
+        <is>
+          <t>HasPhysical, ADBDepartmentOwner</t>
+        </is>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="O25" s="10" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="P25" s="12" t="inlineStr">
+        <is>
+          <t>Needs department list</t>
+        </is>
+      </c>
+      <c r="Q25" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R18" s="10" t="inlineStr"/>
-      <c r="S18" s="10" t="inlineStr"/>
-      <c r="T18" s="10" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>Documents drill</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Storage per department</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="R25" s="10" t="inlineStr"/>
+      <c r="S25" s="10" t="inlineStr"/>
+      <c r="T25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Counterparts drill</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Turned over to RAC, Completion rate</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>Table column</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>Space consumed</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Counterparts physically transferred</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>No source</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>No file exists</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>No column exists in any system</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>Cannot be worked out. Would be transferred divided by flagged as having a counterpart</t>
+        </is>
+      </c>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L26" s="10" t="inlineStr">
+        <is>
+          <t>No column exists</t>
+        </is>
+      </c>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O26" s="10" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="P26" s="13" t="inlineStr">
+        <is>
+          <t>Needs new data source</t>
+        </is>
+      </c>
+      <c r="Q26" s="10" t="inlineStr">
+        <is>
+          <t>Ask RAC for the physical holdings system: boxes, folders, locations, transfers and retrievals. Slide 67 names eServe for retrievals and shows an IR Dashboard screenshot. Why: none of it is in any system this report reads, and access to that dashboard may answer most of it</t>
+        </is>
+      </c>
+      <c r="R26" s="10" t="inlineStr"/>
+      <c r="S26" s="10" t="inlineStr"/>
+      <c r="T26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Disposal drill</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Records due, Next due date</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>What falls due and when</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>The EDRMS database, drm-npr, table public."Records"</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>1. Connect to the drm-npr PostgreSQL database with any SQL client
+2. The table is public."Records", quoted because of the capital R
+3. It holds DECLARED RECORDS ONLY, about 1,990 rows in UAT. There is no row for a document that was never declared, which is why every rate needs the scan built first</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>'EDRMSDueDateForDisposal'</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>COUNT(*) for the number due, and MIN("EDRMSDueDateForDisposal") for the next date, grouped by department. Exclude anything whose duration is Permanent, which never falls due</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>1 Utilization Report</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
+          <t>EDRMSDueDateForDisposal</t>
+        </is>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O27" s="10" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="P27" s="12" t="inlineStr">
+        <is>
+          <t>Needs department list</t>
+        </is>
+      </c>
+      <c r="Q27" s="10" t="inlineStr">
+        <is>
+          <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
+        </is>
+      </c>
+      <c r="R27" s="10" t="inlineStr"/>
+      <c r="S27" s="10" t="inlineStr"/>
+      <c r="T27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Disposal drill</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Approver, Status, Records disposed</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Who approved and what happened</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>No source</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>No file exists</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>No column exists in the application or the database</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>Cannot be worked out. Nothing anywhere records that a disposal was carried out</t>
+        </is>
+      </c>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t>1 Utilization Report</t>
+        </is>
+      </c>
+      <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t>DisposalStatus was removed from the design</t>
+        </is>
+      </c>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>No, deliberately</t>
+        </is>
+      </c>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O28" s="10" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="P28" s="16" t="inlineStr">
+        <is>
+          <t>Needs application change</t>
+        </is>
+      </c>
+      <c r="Q28" s="10" t="inlineStr">
+        <is>
+          <t>Raise a change request for a disposal status field: status, approver, and date disposed. Why: nothing records that a disposal happened, so every completion figure is unanswerable</t>
+        </is>
+      </c>
+      <c r="R28" s="10" t="inlineStr"/>
+      <c r="S28" s="10" t="inlineStr"/>
+      <c r="T28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Overview of sites</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Department table and treemap</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Table and chart</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>Sites, documents, records and counterparts per department</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>No single file. Computed from the tables above</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Produced by the refresh job from the sources above rather than read from one export. Verify it by checking the inputs named in the next two columns</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Combines the site usage export, the Records table and the RAC department list</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>For each department: count its sites from the usage export, sum 'File Count' for documents, count Records rows for declared, count HasPhysical for counterparts. Join everything on the site, and the department onto the site from the RAC list</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
+          <t>1 Utilization Report and 2 Site Activity</t>
+        </is>
+      </c>
+      <c r="L29" s="10" t="inlineStr">
+        <is>
+          <t>ADBDepartmentOwner and the measures above</t>
+        </is>
+      </c>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="O29" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P29" s="12" t="inlineStr">
+        <is>
+          <t>Needs department list</t>
+        </is>
+      </c>
+      <c r="Q29" s="10" t="inlineStr">
+        <is>
+          <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
+        </is>
+      </c>
+      <c r="R29" s="10" t="inlineStr"/>
+      <c r="S29" s="10" t="inlineStr"/>
+      <c r="T29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Overview of sites</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Sites created, last 90 days</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>New compliant sites</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>Microsoft Graph</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Microsoft Graph, run interactively</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>1. Go to https://aka.ms/ge, the Graph Explorer
+2. Sign in with a tenant account and consent to the scope named in the next column
+3. Paste the call from the Exact column heading cell into the address bar and click Run query
+4. Read the field named in that same cell out of the JSON response</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>GET /sites?search=*&amp;$select=id,displayName,webUrl,createdDateTime&amp;$top=999, then the createdDateTime field</t>
+        </is>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>Count the sites whose createdDateTime falls in the last 90 days. Graph returns this on every site, confirmed against the tenant</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t>2 Site Activity</t>
+        </is>
+      </c>
+      <c r="L30" s="10" t="inlineStr">
+        <is>
+          <t>SiteCreatedDate</t>
+        </is>
+      </c>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N30" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O30" s="10" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="P30" s="11" t="inlineStr">
+        <is>
+          <t>Buildable now</t>
+        </is>
+      </c>
+      <c r="Q30" s="10" t="inlineStr"/>
+      <c r="R30" s="10" t="inlineStr"/>
+      <c r="S30" s="10" t="inlineStr"/>
+      <c r="T30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Overview of sites</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Inactive over 90 days</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>Sites with no recent activity</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>M365 usage report</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>SharePoint site usage report, exported as CSV</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
 2. Sign in as a Microsoft 365 reports reader or global reader
@@ -4219,1065 +5313,90 @@
 6. WARNING: the Site URL column is EMPTY on every row. Use Site Id and match it to a site list from Graph if you need the address</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>'Storage Used (Byte)'</t>
-        </is>
-      </c>
-      <c r="J19" s="10" t="inlineStr">
-        <is>
-          <t>Sum 'Storage Used (Byte)' then divide by 1,073,741,824 to get GB. The test tenant totals 142.4 GB. NOTE this includes version history, so it reads higher than the sum of file sizes, which is expected and not an error</t>
-        </is>
-      </c>
-      <c r="K19" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>'Last Activity Date' and 'Is Deleted'</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>Filter out 'Is Deleted' True, then count rows where 'Last Activity Date' is older than 90 days before 'Report Refresh Date'. Only 381 of 1,918 live sites carry a date at all</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="inlineStr">
         <is>
           <t>2 Site Activity</t>
         </is>
       </c>
-      <c r="L19" s="10" t="inlineStr">
-        <is>
-          <t>StorageUsed</t>
-        </is>
-      </c>
-      <c r="M19" s="10" t="inlineStr">
+      <c r="L31" s="10" t="inlineStr">
+        <is>
+          <t>LastActivityDate</t>
+        </is>
+      </c>
+      <c r="M31" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N19" s="10" t="inlineStr">
+      <c r="N31" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="O19" s="10" t="inlineStr">
+      <c r="O31" s="10" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P19" s="12" t="inlineStr">
-        <is>
-          <t>Needs department list</t>
-        </is>
-      </c>
-      <c r="Q19" s="10" t="inlineStr">
-        <is>
-          <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
-        </is>
-      </c>
-      <c r="R19" s="10" t="inlineStr"/>
-      <c r="S19" s="10" t="inlineStr"/>
-      <c r="T19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Documents drill</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Users creating documents</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>Distinct authors</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>No source</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>No file exists</t>
-        </is>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>No author column exists in any export, and the scan does not capture one</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="inlineStr">
-        <is>
-          <t>Cannot be worked out for undeclared documents. For declared records only, it would be COUNT(DISTINCT "CreatedBy") on the Records table, which counts declarers not authors</t>
-        </is>
-      </c>
-      <c r="K20" s="10" t="inlineStr">
-        <is>
-          <t>1 Utilization Report</t>
-        </is>
-      </c>
-      <c r="L20" s="10" t="inlineStr">
-        <is>
-          <t>CreatedBy covers declarers only</t>
-        </is>
-      </c>
-      <c r="M20" s="10" t="inlineStr">
-        <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="N20" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O20" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="P20" s="15" t="inlineStr">
-        <is>
-          <t>Needs new column or join</t>
-        </is>
-      </c>
-      <c r="Q20" s="10" t="inlineStr">
-        <is>
-          <t>Ask the development team to capture Author on the document scan. Why: without it, creation activity can only be measured for records, not for documents</t>
-        </is>
-      </c>
-      <c r="R20" s="10" t="inlineStr"/>
-      <c r="S20" s="10" t="inlineStr"/>
-      <c r="T20" s="10" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>Records drill</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Records declared per department</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>Declaration volume</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>EDRMS database</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>The EDRMS database, drm-npr, table public."Records"</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>1. Connect to the drm-npr PostgreSQL database with any SQL client
-2. The table is public."Records", quoted because of the capital R
-3. It holds DECLARED RECORDS ONLY, about 1,990 rows in UAT. There is no row for a document that was never declared, which is why every rate needs the scan built first</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>The whole table, plus SiteUrl to attach a department</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(*) FROM public."Records" GROUP BY the department that owns "SiteUrl". The department itself comes from the RAC list, matched on site URL</t>
-        </is>
-      </c>
-      <c r="K21" s="10" t="inlineStr">
-        <is>
-          <t>1 Utilization Report</t>
-        </is>
-      </c>
-      <c r="L21" s="10" t="inlineStr">
-        <is>
-          <t>IsDeclaredRecord, ADBDepartmentOwner</t>
-        </is>
-      </c>
-      <c r="M21" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N21" s="10" t="inlineStr">
-        <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="O21" s="10" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="P21" s="12" t="inlineStr">
-        <is>
-          <t>Needs department list</t>
-        </is>
-      </c>
-      <c r="Q21" s="10" t="inlineStr">
-        <is>
-          <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
-        </is>
-      </c>
-      <c r="R21" s="10" t="inlineStr"/>
-      <c r="S21" s="10" t="inlineStr"/>
-      <c r="T21" s="10" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>Records drill</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>Users declaring records</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>How many people are declaring</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>EDRMS database</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>The EDRMS database, drm-npr, table public."Records"</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>1. Connect to the drm-npr PostgreSQL database with any SQL client
-2. The table is public."Records", quoted because of the capital R
-3. It holds DECLARED RECORDS ONLY, about 1,990 rows in UAT. There is no row for a document that was never declared, which is why every rate needs the scan built first</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>'CreatedBy'</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(DISTINCT "CreatedBy") FROM public."Records". Distinct, not a row count, or one person declaring 400 records counts 400 times</t>
-        </is>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>1 Utilization Report</t>
-        </is>
-      </c>
-      <c r="L22" s="10" t="inlineStr">
-        <is>
-          <t>CreatedBy</t>
-        </is>
-      </c>
-      <c r="M22" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N22" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O22" s="10" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="P22" s="12" t="inlineStr">
-        <is>
-          <t>Needs department list</t>
-        </is>
-      </c>
-      <c r="Q22" s="10" t="inlineStr">
-        <is>
-          <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
-        </is>
-      </c>
-      <c r="R22" s="10" t="inlineStr"/>
-      <c r="S22" s="10" t="inlineStr"/>
-      <c r="T22" s="10" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>Records drill</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Declaration rate</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>Share of content formally declared</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>EDRMS database</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>No single file. Computed from the tables above</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>Produced by the refresh job from the sources above rather than read from one export. Verify it by checking the inputs named in the next two columns</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>Two numbers: declared records, and total documents</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="inlineStr">
-        <is>
-          <t>Records Declared divided by Total Documents, times 100. The numerator comes from the Records table, the denominator from the scan. Until the scan exists this rate CANNOT be produced, because the denominator does not exist anywhere</t>
-        </is>
-      </c>
-      <c r="K23" s="10" t="inlineStr">
-        <is>
-          <t>1 Utilization Report</t>
-        </is>
-      </c>
-      <c r="L23" s="10" t="inlineStr">
-        <is>
-          <t>IsDeclaredRecord over all rows</t>
-        </is>
-      </c>
-      <c r="M23" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N23" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O23" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="P23" s="12" t="inlineStr">
-        <is>
-          <t>Needs department list</t>
-        </is>
-      </c>
-      <c r="Q23" s="10" t="inlineStr">
-        <is>
-          <t>None, but be explicit with the client that every rate waits on the scan</t>
-        </is>
-      </c>
-      <c r="R23" s="10" t="inlineStr"/>
-      <c r="S23" s="10" t="inlineStr"/>
-      <c r="T23" s="10" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>Records drill</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>By division</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>Drill tier</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>The same figures one level below department</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>No source</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>No file exists</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
-        </is>
-      </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>No division column exists anywhere</t>
-        </is>
-      </c>
-      <c r="J24" s="10" t="inlineStr">
-        <is>
-          <t>Cannot be worked out. The RAC list would have to carry a division alongside department</t>
-        </is>
-      </c>
-      <c r="K24" s="10" t="inlineStr">
-        <is>
-          <t>1 Utilization Report</t>
-        </is>
-      </c>
-      <c r="L24" s="10" t="inlineStr">
-        <is>
-          <t>No division column exists</t>
-        </is>
-      </c>
-      <c r="M24" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N24" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O24" s="10" t="inlineStr">
-        <is>
-          <t>Easy once supplied</t>
-        </is>
-      </c>
-      <c r="P24" s="13" t="inlineStr">
-        <is>
-          <t>Needs new data source</t>
-        </is>
-      </c>
-      <c r="Q24" s="10" t="inlineStr">
-        <is>
-          <t>Ask who supplies division alongside department. Why: the tier was reinstated at the client's request but nothing in the tenant populates it, so the RAC list has to carry a division column too</t>
-        </is>
-      </c>
-      <c r="R24" s="10" t="inlineStr"/>
-      <c r="S24" s="10" t="inlineStr"/>
-      <c r="T24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>Counterparts drill</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>Physical counterparts by department</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>Records with a paper copy</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>EDRMS database</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>The EDRMS database, drm-npr, table public."Records"</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>1. Connect to the drm-npr PostgreSQL database with any SQL client
-2. The table is public."Records", quoted because of the capital R
-3. It holds DECLARED RECORDS ONLY, about 1,990 rows in UAT. There is no row for a document that was never declared, which is why every rate needs the scan built first</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>EDRMSMeta key HasPhysical, plus SiteUrl</t>
-        </is>
-      </c>
-      <c r="J25" s="10" t="inlineStr">
-        <is>
-          <t>Count rows where the HasPhysical key is true, grouped by the department that owns the site</t>
-        </is>
-      </c>
-      <c r="K25" s="10" t="inlineStr">
-        <is>
-          <t>1 Utilization Report</t>
-        </is>
-      </c>
-      <c r="L25" s="10" t="inlineStr">
-        <is>
-          <t>HasPhysical, ADBDepartmentOwner</t>
-        </is>
-      </c>
-      <c r="M25" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N25" s="10" t="inlineStr">
-        <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="O25" s="10" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="P25" s="12" t="inlineStr">
-        <is>
-          <t>Needs department list</t>
-        </is>
-      </c>
-      <c r="Q25" s="10" t="inlineStr">
-        <is>
-          <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
-        </is>
-      </c>
-      <c r="R25" s="10" t="inlineStr"/>
-      <c r="S25" s="10" t="inlineStr"/>
-      <c r="T25" s="10" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>Counterparts drill</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>Turned over to RAC, Completion rate</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>Counterparts physically transferred</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>No source</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>No file exists</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
-        </is>
-      </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>No column exists in any system</t>
-        </is>
-      </c>
-      <c r="J26" s="10" t="inlineStr">
-        <is>
-          <t>Cannot be worked out. Would be transferred divided by flagged as having a counterpart</t>
-        </is>
-      </c>
-      <c r="K26" s="10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L26" s="10" t="inlineStr">
-        <is>
-          <t>No column exists</t>
-        </is>
-      </c>
-      <c r="M26" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N26" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O26" s="10" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="P26" s="13" t="inlineStr">
-        <is>
-          <t>Needs new data source</t>
-        </is>
-      </c>
-      <c r="Q26" s="10" t="inlineStr">
-        <is>
-          <t>Ask RAC for the physical holdings system: boxes, folders, locations, transfers and retrievals. Slide 67 names eServe for retrievals and shows an IR Dashboard screenshot. Why: none of it is in any system this report reads, and access to that dashboard may answer most of it</t>
-        </is>
-      </c>
-      <c r="R26" s="10" t="inlineStr"/>
-      <c r="S26" s="10" t="inlineStr"/>
-      <c r="T26" s="10" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>Disposal drill</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>Records due, Next due date</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>What falls due and when</t>
-        </is>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>EDRMS database</t>
-        </is>
-      </c>
-      <c r="G27" s="10" t="inlineStr">
-        <is>
-          <t>The EDRMS database, drm-npr, table public."Records"</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>1. Connect to the drm-npr PostgreSQL database with any SQL client
-2. The table is public."Records", quoted because of the capital R
-3. It holds DECLARED RECORDS ONLY, about 1,990 rows in UAT. There is no row for a document that was never declared, which is why every rate needs the scan built first</t>
-        </is>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>'EDRMSDueDateForDisposal'</t>
-        </is>
-      </c>
-      <c r="J27" s="10" t="inlineStr">
-        <is>
-          <t>COUNT(*) for the number due, and MIN("EDRMSDueDateForDisposal") for the next date, grouped by department. Exclude anything whose duration is Permanent, which never falls due</t>
-        </is>
-      </c>
-      <c r="K27" s="10" t="inlineStr">
-        <is>
-          <t>1 Utilization Report</t>
-        </is>
-      </c>
-      <c r="L27" s="10" t="inlineStr">
-        <is>
-          <t>EDRMSDueDateForDisposal</t>
-        </is>
-      </c>
-      <c r="M27" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N27" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O27" s="10" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="P27" s="12" t="inlineStr">
-        <is>
-          <t>Needs department list</t>
-        </is>
-      </c>
-      <c r="Q27" s="10" t="inlineStr">
-        <is>
-          <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
-        </is>
-      </c>
-      <c r="R27" s="10" t="inlineStr"/>
-      <c r="S27" s="10" t="inlineStr"/>
-      <c r="T27" s="10" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Disposal drill</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>Approver, Status, Records disposed</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>Who approved and what happened</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>No source</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>No file exists</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>No column exists in the application or the database</t>
-        </is>
-      </c>
-      <c r="J28" s="10" t="inlineStr">
-        <is>
-          <t>Cannot be worked out. Nothing anywhere records that a disposal was carried out</t>
-        </is>
-      </c>
-      <c r="K28" s="10" t="inlineStr">
-        <is>
-          <t>1 Utilization Report</t>
-        </is>
-      </c>
-      <c r="L28" s="10" t="inlineStr">
-        <is>
-          <t>DisposalStatus was removed from the design</t>
-        </is>
-      </c>
-      <c r="M28" s="10" t="inlineStr">
-        <is>
-          <t>No, deliberately</t>
-        </is>
-      </c>
-      <c r="N28" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O28" s="10" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="P28" s="16" t="inlineStr">
-        <is>
-          <t>Needs application change</t>
-        </is>
-      </c>
-      <c r="Q28" s="10" t="inlineStr">
-        <is>
-          <t>Raise a change request for a disposal status field: status, approver, and date disposed. Why: nothing records that a disposal happened, so every completion figure is unanswerable</t>
-        </is>
-      </c>
-      <c r="R28" s="10" t="inlineStr"/>
-      <c r="S28" s="10" t="inlineStr"/>
-      <c r="T28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="P31" s="11" t="inlineStr">
+        <is>
+          <t>Buildable now</t>
+        </is>
+      </c>
+      <c r="Q31" s="10" t="inlineStr">
+        <is>
+          <t>Ask whether an inactive site is 90 days or 300. The deck says 90, the metrics document says 300. Why: it changes every inactivity figure, and it is a one line change either way</t>
+        </is>
+      </c>
+      <c r="R31" s="10" t="inlineStr"/>
+      <c r="S31" s="10" t="inlineStr"/>
+      <c r="T31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>Overview of sites</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Department table and treemap</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>Table and chart</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>Sites, documents, records and counterparts per department</t>
-        </is>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>EDRMS database</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>No single file. Computed from the tables above</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>Produced by the refresh job from the sources above rather than read from one export. Verify it by checking the inputs named in the next two columns</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>Combines the site usage export, the Records table and the RAC department list</t>
-        </is>
-      </c>
-      <c r="J29" s="10" t="inlineStr">
-        <is>
-          <t>For each department: count its sites from the usage export, sum 'File Count' for documents, count Records rows for declared, count HasPhysical for counterparts. Join everything on the site, and the department onto the site from the RAC list</t>
-        </is>
-      </c>
-      <c r="K29" s="10" t="inlineStr">
-        <is>
-          <t>1 Utilization Report and 2 Site Activity</t>
-        </is>
-      </c>
-      <c r="L29" s="10" t="inlineStr">
-        <is>
-          <t>ADBDepartmentOwner and the measures above</t>
-        </is>
-      </c>
-      <c r="M29" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N29" s="10" t="inlineStr">
-        <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="O29" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="P29" s="12" t="inlineStr">
-        <is>
-          <t>Needs department list</t>
-        </is>
-      </c>
-      <c r="Q29" s="10" t="inlineStr">
-        <is>
-          <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
-        </is>
-      </c>
-      <c r="R29" s="10" t="inlineStr"/>
-      <c r="S29" s="10" t="inlineStr"/>
-      <c r="T29" s="10" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Overview of sites</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Sites created, last 90 days</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Sites deleted</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>Tile</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>New compliant sites</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>Microsoft Graph</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>Microsoft Graph, run interactively</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>1. Go to https://aka.ms/ge, the Graph Explorer
-2. Sign in with a tenant account and consent to the scope named in the next column
-3. Paste the call from the Exact column heading cell into the address bar and click Run query
-4. Read the field named in that same cell out of the JSON response</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>GET /sites?search=*&amp;$select=id,displayName,webUrl,createdDateTime&amp;$top=999, then the createdDateTime field</t>
-        </is>
-      </c>
-      <c r="J30" s="10" t="inlineStr">
-        <is>
-          <t>Count the sites whose createdDateTime falls in the last 90 days. Graph returns this on every site, confirmed against the tenant</t>
-        </is>
-      </c>
-      <c r="K30" s="10" t="inlineStr">
-        <is>
-          <t>2 Site Activity</t>
-        </is>
-      </c>
-      <c r="L30" s="10" t="inlineStr">
-        <is>
-          <t>SiteCreatedDate</t>
-        </is>
-      </c>
-      <c r="M30" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N30" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O30" s="10" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="P30" s="11" t="inlineStr">
-        <is>
-          <t>Buildable now</t>
-        </is>
-      </c>
-      <c r="Q30" s="10" t="inlineStr"/>
-      <c r="R30" s="10" t="inlineStr"/>
-      <c r="S30" s="10" t="inlineStr"/>
-      <c r="T30" s="10" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>Overview of sites</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>Inactive over 90 days</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>Sites with no recent activity</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Sites removed since the last snapshot</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>M365 usage report</t>
         </is>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>SharePoint site usage report, exported as CSV</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
 2. Sign in as a Microsoft 365 reports reader or global reader
@@ -5287,90 +5406,612 @@
 6. WARNING: the Site URL column is EMPTY on every row. Use Site Id and match it to a site list from Graph if you need the address</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
-        <is>
-          <t>'Last Activity Date' and 'Is Deleted'</t>
-        </is>
-      </c>
-      <c r="J31" s="10" t="inlineStr">
-        <is>
-          <t>Filter out 'Is Deleted' True, then count rows where 'Last Activity Date' is older than 90 days before 'Report Refresh Date'. Only 381 of 1,918 live sites carry a date at all</t>
-        </is>
-      </c>
-      <c r="K31" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>'Is Deleted'</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>Count rows where 'Is Deleted' is True. To count deletions in a period instead, compare two weekly exports and count the Site Ids present in the older one and absent from the newer</t>
+        </is>
+      </c>
+      <c r="K32" s="10" t="inlineStr">
         <is>
           <t>2 Site Activity</t>
         </is>
       </c>
-      <c r="L31" s="10" t="inlineStr">
-        <is>
-          <t>LastActivityDate</t>
-        </is>
-      </c>
-      <c r="M31" s="10" t="inlineStr">
+      <c r="L32" s="10" t="inlineStr">
+        <is>
+          <t>IsDeleted</t>
+        </is>
+      </c>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>Yes, unpopulated</t>
+        </is>
+      </c>
+      <c r="N32" s="10" t="inlineStr">
+        <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="O32" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P32" s="15" t="inlineStr">
+        <is>
+          <t>Needs new column or join</t>
+        </is>
+      </c>
+      <c r="Q32" s="10" t="inlineStr">
+        <is>
+          <t>Confirm that a deleted site should be counted from its disappearance between two exports. Why: absence cannot distinguish a deletion from a permissions change that hides the site</t>
+        </is>
+      </c>
+      <c r="R32" s="10" t="inlineStr"/>
+      <c r="S32" s="10" t="inlineStr"/>
+      <c r="T32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Overview of sites</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Sites archived</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Tile</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>Sites moved to an archived state</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>No source</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>No file exists</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>No column in any export marks a site as archived</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>Cannot be worked out. No rule exists to compute it</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>2 Site Activity</t>
+        </is>
+      </c>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
+          <t>No column exists</t>
+        </is>
+      </c>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N33" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O33" s="10" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="P33" s="17" t="inlineStr">
+        <is>
+          <t>Decision needed</t>
+        </is>
+      </c>
+      <c r="Q33" s="10" t="inlineStr">
+        <is>
+          <t>Ask what archived means for a site, and how it is marked. Why: there is no definition anywhere, so the figure cannot be counted</t>
+        </is>
+      </c>
+      <c r="R33" s="10" t="inlineStr"/>
+      <c r="S33" s="10" t="inlineStr"/>
+      <c r="T33" s="10" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Users against documents, users against records, documents against records</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Three ratios per department</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>No single file. Computed from the tables above</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Produced by the refresh job from the sources above rather than read from one export. Verify it by checking the inputs named in the next two columns</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Combines 'Viewed Or Edited File Count' from the user export, 'File Count' from the site export, and the Records row count</t>
+        </is>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>Each pair is drawn side by side per department. The third pair, documents against records, is the declaration rate expressed as two bars rather than a percentage</t>
+        </is>
+      </c>
+      <c r="K34" s="10" t="inlineStr">
+        <is>
+          <t>1 Utilization Report, 3 User Activity</t>
+        </is>
+      </c>
+      <c r="L34" s="10" t="inlineStr">
+        <is>
+          <t>UserPrincipalName, IsDeclaredRecord</t>
+        </is>
+      </c>
+      <c r="M34" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N31" s="10" t="inlineStr">
+      <c r="N34" s="10" t="inlineStr">
+        <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="O34" s="10" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="P34" s="12" t="inlineStr">
+        <is>
+          <t>Needs department list</t>
+        </is>
+      </c>
+      <c r="Q34" s="10" t="inlineStr">
+        <is>
+          <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
+        </is>
+      </c>
+      <c r="R34" s="10" t="inlineStr"/>
+      <c r="S34" s="10" t="inlineStr"/>
+      <c r="T34" s="10" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Declaration trend</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Records declared by month</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>Declarations in each of 12 months</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>The EDRMS database, drm-npr, table public."Records"</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>1. Connect to the drm-npr PostgreSQL database with any SQL client
+2. The table is public."Records", quoted because of the capital R
+3. It holds DECLARED RECORDS ONLY, about 1,990 rows in UAT. There is no row for a document that was never declared, which is why every rate needs the scan built first</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>'CreatedDate'</t>
+        </is>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>SELECT date_trunc('month', "CreatedDate"), COUNT(*) FROM public."Records" GROUP BY 1 ORDER BY 1, then take the last 12 closed months. Use CreatedDate, which is when the record was declared, NOT EDRMSRetentionLabelApplied, which can be set on an undeclared document</t>
+        </is>
+      </c>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
+          <t>1 Utilization Report</t>
+        </is>
+      </c>
+      <c r="L35" s="10" t="inlineStr">
+        <is>
+          <t>CreatedDate</t>
+        </is>
+      </c>
+      <c r="M35" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="O31" s="10" t="inlineStr">
+      <c r="N35" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O35" s="10" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P31" s="11" t="inlineStr">
+      <c r="P35" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q31" s="10" t="inlineStr">
-        <is>
-          <t>Ask whether an inactive site is 90 days or 300. The deck says 90, the metrics document says 300. Why: it changes every inactivity figure, and it is a one line change either way</t>
-        </is>
-      </c>
-      <c r="R31" s="10" t="inlineStr"/>
-      <c r="S31" s="10" t="inlineStr"/>
-      <c r="T31" s="10" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>Overview of sites</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>Sites deleted</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="Q35" s="10" t="inlineStr"/>
+      <c r="R35" s="10" t="inlineStr"/>
+      <c r="S35" s="10" t="inlineStr"/>
+      <c r="T35" s="10" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Declaration trend</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Records declared this month, Monthly average</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>Tile</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>Sites removed since the last snapshot</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Current month against its average</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>The EDRMS database, drm-npr, table public."Records"</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>1. Connect to the drm-npr PostgreSQL database with any SQL client
+2. The table is public."Records", quoted because of the capital R
+3. It holds DECLARED RECORDS ONLY, about 1,990 rows in UAT. There is no row for a document that was never declared, which is why every rate needs the scan built first</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>'CreatedDate'</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>This month is the last bar of the same query. The average is the 12 month total divided by 12</t>
+        </is>
+      </c>
+      <c r="K36" s="10" t="inlineStr">
+        <is>
+          <t>1 Utilization Report</t>
+        </is>
+      </c>
+      <c r="L36" s="10" t="inlineStr">
+        <is>
+          <t>CreatedDate</t>
+        </is>
+      </c>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N36" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O36" s="10" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="P36" s="11" t="inlineStr">
+        <is>
+          <t>Buildable now</t>
+        </is>
+      </c>
+      <c r="Q36" s="10" t="inlineStr"/>
+      <c r="R36" s="10" t="inlineStr"/>
+      <c r="S36" s="10" t="inlineStr"/>
+      <c r="T36" s="10" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Declaration trend</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Records declared by year</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>Declarations per year</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>The EDRMS database, drm-npr, table public."Records"</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>1. Connect to the drm-npr PostgreSQL database with any SQL client
+2. The table is public."Records", quoted because of the capital R
+3. It holds DECLARED RECORDS ONLY, about 1,990 rows in UAT. There is no row for a document that was never declared, which is why every rate needs the scan built first</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>'CreatedDate'</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>The same query grouped by year instead of month. The final bar is the last 12 months, so it must equal the total of the monthly chart above it</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
+        <is>
+          <t>1 Utilization Report</t>
+        </is>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>CreatedDate</t>
+        </is>
+      </c>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N37" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O37" s="10" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="P37" s="11" t="inlineStr">
+        <is>
+          <t>Buildable now</t>
+        </is>
+      </c>
+      <c r="Q37" s="10" t="inlineStr"/>
+      <c r="R37" s="10" t="inlineStr"/>
+      <c r="S37" s="10" t="inlineStr"/>
+      <c r="T37" s="10" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Declaration trend</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Department filter</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>The same trend for one department</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>No source</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>No file exists</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
+        </is>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>No department column exists in the Records table yet</t>
+        </is>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>Add a filter on the department that owns the site in "SiteUrl", once the RAC list exists</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>1 Utilization Report</t>
+        </is>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>ADBDepartmentOwner</t>
+        </is>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>Column exists, unpopulated</t>
+        </is>
+      </c>
+      <c r="N38" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O38" s="10" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="P38" s="12" t="inlineStr">
+        <is>
+          <t>Needs department list</t>
+        </is>
+      </c>
+      <c r="Q38" s="10" t="inlineStr">
+        <is>
+          <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
+        </is>
+      </c>
+      <c r="R38" s="10" t="inlineStr"/>
+      <c r="S38" s="10" t="inlineStr"/>
+      <c r="T38" s="10" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Site activity trend</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Site visits by month</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>Page views across the estate</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>M365 usage report</t>
         </is>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="G39" s="10" t="inlineStr">
         <is>
           <t>SharePoint site usage report, exported as CSV</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
 2. Sign in as a Microsoft 365 reports reader or global reader
@@ -5380,612 +6021,90 @@
 6. WARNING: the Site URL column is EMPTY on every row. Use Site Id and match it to a site list from Graph if you need the address</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>'Is Deleted'</t>
-        </is>
-      </c>
-      <c r="J32" s="10" t="inlineStr">
-        <is>
-          <t>Count rows where 'Is Deleted' is True. To count deletions in a period instead, compare two weekly exports and count the Site Ids present in the older one and absent from the newer</t>
-        </is>
-      </c>
-      <c r="K32" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>'Page View Count' and 'Report Refresh Date'</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>Export the report weekly at the 7 day period. For each month, SUM 'Page View Count' across the weekly exports whose 'Report Refresh Date' falls in that month. CRITICAL: use the 7 DAY period only. Summing the 30, 90 or 180 day exports counts most days several times over, because those windows overlap while consecutive 7 day windows tile exactly</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="inlineStr">
         <is>
           <t>2 Site Activity</t>
         </is>
       </c>
-      <c r="L32" s="10" t="inlineStr">
-        <is>
-          <t>IsDeleted</t>
-        </is>
-      </c>
-      <c r="M32" s="10" t="inlineStr">
-        <is>
-          <t>Yes, unpopulated</t>
-        </is>
-      </c>
-      <c r="N32" s="10" t="inlineStr">
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>SiteVisits7, ReportRefreshDate</t>
+        </is>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N39" s="10" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="O32" s="10" t="inlineStr">
+      <c r="O39" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="P32" s="15" t="inlineStr">
-        <is>
-          <t>Needs new column or join</t>
-        </is>
-      </c>
-      <c r="Q32" s="10" t="inlineStr">
-        <is>
-          <t>Confirm that a deleted site should be counted from its disappearance between two exports. Why: absence cannot distinguish a deletion from a permissions change that hides the site</t>
-        </is>
-      </c>
-      <c r="R32" s="10" t="inlineStr"/>
-      <c r="S32" s="10" t="inlineStr"/>
-      <c r="T32" s="10" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>Overview of sites</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>Sites archived</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>Sites moved to an archived state</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>No source</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t>No file exists</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>No column in any export marks a site as archived</t>
-        </is>
-      </c>
-      <c r="J33" s="10" t="inlineStr">
-        <is>
-          <t>Cannot be worked out. No rule exists to compute it</t>
-        </is>
-      </c>
-      <c r="K33" s="10" t="inlineStr">
-        <is>
-          <t>2 Site Activity</t>
-        </is>
-      </c>
-      <c r="L33" s="10" t="inlineStr">
-        <is>
-          <t>No column exists</t>
-        </is>
-      </c>
-      <c r="M33" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N33" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O33" s="10" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="P33" s="17" t="inlineStr">
-        <is>
-          <t>Decision needed</t>
-        </is>
-      </c>
-      <c r="Q33" s="10" t="inlineStr">
-        <is>
-          <t>Ask what archived means for a site, and how it is marked. Why: there is no definition anywhere, so the figure cannot be counted</t>
-        </is>
-      </c>
-      <c r="R33" s="10" t="inlineStr"/>
-      <c r="S33" s="10" t="inlineStr"/>
-      <c r="T33" s="10" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>Comparison</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>Users against documents, users against records, documents against records</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>Three ratios per department</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>EDRMS database</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>No single file. Computed from the tables above</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>Produced by the refresh job from the sources above rather than read from one export. Verify it by checking the inputs named in the next two columns</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>Combines 'Viewed Or Edited File Count' from the user export, 'File Count' from the site export, and the Records row count</t>
-        </is>
-      </c>
-      <c r="J34" s="10" t="inlineStr">
-        <is>
-          <t>Each pair is drawn side by side per department. The third pair, documents against records, is the declaration rate expressed as two bars rather than a percentage</t>
-        </is>
-      </c>
-      <c r="K34" s="10" t="inlineStr">
-        <is>
-          <t>1 Utilization Report, 3 User Activity</t>
-        </is>
-      </c>
-      <c r="L34" s="10" t="inlineStr">
-        <is>
-          <t>UserPrincipalName, IsDeclaredRecord</t>
-        </is>
-      </c>
-      <c r="M34" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N34" s="10" t="inlineStr">
-        <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="O34" s="10" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="P34" s="12" t="inlineStr">
-        <is>
-          <t>Needs department list</t>
-        </is>
-      </c>
-      <c r="Q34" s="10" t="inlineStr">
-        <is>
-          <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
-        </is>
-      </c>
-      <c r="R34" s="10" t="inlineStr"/>
-      <c r="S34" s="10" t="inlineStr"/>
-      <c r="T34" s="10" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>Declaration trend</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>Records declared by month</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="E35" s="10" t="inlineStr">
-        <is>
-          <t>Declarations in each of 12 months</t>
-        </is>
-      </c>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t>EDRMS database</t>
-        </is>
-      </c>
-      <c r="G35" s="10" t="inlineStr">
-        <is>
-          <t>The EDRMS database, drm-npr, table public."Records"</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>1. Connect to the drm-npr PostgreSQL database with any SQL client
-2. The table is public."Records", quoted because of the capital R
-3. It holds DECLARED RECORDS ONLY, about 1,990 rows in UAT. There is no row for a document that was never declared, which is why every rate needs the scan built first</t>
-        </is>
-      </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>'CreatedDate'</t>
-        </is>
-      </c>
-      <c r="J35" s="10" t="inlineStr">
-        <is>
-          <t>SELECT date_trunc('month', "CreatedDate"), COUNT(*) FROM public."Records" GROUP BY 1 ORDER BY 1, then take the last 12 closed months. Use CreatedDate, which is when the record was declared, NOT EDRMSRetentionLabelApplied, which can be set on an undeclared document</t>
-        </is>
-      </c>
-      <c r="K35" s="10" t="inlineStr">
-        <is>
-          <t>1 Utilization Report</t>
-        </is>
-      </c>
-      <c r="L35" s="10" t="inlineStr">
-        <is>
-          <t>CreatedDate</t>
-        </is>
-      </c>
-      <c r="M35" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N35" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O35" s="10" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="P35" s="11" t="inlineStr">
+      <c r="P39" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q35" s="10" t="inlineStr"/>
-      <c r="R35" s="10" t="inlineStr"/>
-      <c r="S35" s="10" t="inlineStr"/>
-      <c r="T35" s="10" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>Declaration trend</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>Records declared this month, Monthly average</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>Current month against its average</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>EDRMS database</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>The EDRMS database, drm-npr, table public."Records"</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>1. Connect to the drm-npr PostgreSQL database with any SQL client
-2. The table is public."Records", quoted because of the capital R
-3. It holds DECLARED RECORDS ONLY, about 1,990 rows in UAT. There is no row for a document that was never declared, which is why every rate needs the scan built first</t>
-        </is>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>'CreatedDate'</t>
-        </is>
-      </c>
-      <c r="J36" s="10" t="inlineStr">
-        <is>
-          <t>This month is the last bar of the same query. The average is the 12 month total divided by 12</t>
-        </is>
-      </c>
-      <c r="K36" s="10" t="inlineStr">
-        <is>
-          <t>1 Utilization Report</t>
-        </is>
-      </c>
-      <c r="L36" s="10" t="inlineStr">
-        <is>
-          <t>CreatedDate</t>
-        </is>
-      </c>
-      <c r="M36" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N36" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O36" s="10" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="P36" s="11" t="inlineStr">
-        <is>
-          <t>Buildable now</t>
-        </is>
-      </c>
-      <c r="Q36" s="10" t="inlineStr"/>
-      <c r="R36" s="10" t="inlineStr"/>
-      <c r="S36" s="10" t="inlineStr"/>
-      <c r="T36" s="10" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>Declaration trend</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>Records declared by year</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="inlineStr">
-        <is>
-          <t>Declarations per year</t>
-        </is>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>EDRMS database</t>
-        </is>
-      </c>
-      <c r="G37" s="10" t="inlineStr">
-        <is>
-          <t>The EDRMS database, drm-npr, table public."Records"</t>
-        </is>
-      </c>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>1. Connect to the drm-npr PostgreSQL database with any SQL client
-2. The table is public."Records", quoted because of the capital R
-3. It holds DECLARED RECORDS ONLY, about 1,990 rows in UAT. There is no row for a document that was never declared, which is why every rate needs the scan built first</t>
-        </is>
-      </c>
-      <c r="I37" s="10" t="inlineStr">
-        <is>
-          <t>'CreatedDate'</t>
-        </is>
-      </c>
-      <c r="J37" s="10" t="inlineStr">
-        <is>
-          <t>The same query grouped by year instead of month. The final bar is the last 12 months, so it must equal the total of the monthly chart above it</t>
-        </is>
-      </c>
-      <c r="K37" s="10" t="inlineStr">
-        <is>
-          <t>1 Utilization Report</t>
-        </is>
-      </c>
-      <c r="L37" s="10" t="inlineStr">
-        <is>
-          <t>CreatedDate</t>
-        </is>
-      </c>
-      <c r="M37" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N37" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O37" s="10" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="P37" s="11" t="inlineStr">
-        <is>
-          <t>Buildable now</t>
-        </is>
-      </c>
-      <c r="Q37" s="10" t="inlineStr"/>
-      <c r="R37" s="10" t="inlineStr"/>
-      <c r="S37" s="10" t="inlineStr"/>
-      <c r="T37" s="10" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>Declaration trend</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>Department filter</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
+      <c r="Q39" s="10" t="inlineStr">
+        <is>
+          <t>Confirm the job start date with the client. Why: the trend can only begin when weekly capture begins, and history never captured cannot be recovered</t>
+        </is>
+      </c>
+      <c r="R39" s="10" t="inlineStr"/>
+      <c r="S39" s="10" t="inlineStr"/>
+      <c r="T39" s="10" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Site activity trend</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Department and period filters</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>Filter</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>The same trend for one department</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>No source</t>
-        </is>
-      </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>No file exists</t>
-        </is>
-      </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
-        </is>
-      </c>
-      <c r="I38" s="10" t="inlineStr">
-        <is>
-          <t>No department column exists in the Records table yet</t>
-        </is>
-      </c>
-      <c r="J38" s="10" t="inlineStr">
-        <is>
-          <t>Add a filter on the department that owns the site in "SiteUrl", once the RAC list exists</t>
-        </is>
-      </c>
-      <c r="K38" s="10" t="inlineStr">
-        <is>
-          <t>1 Utilization Report</t>
-        </is>
-      </c>
-      <c r="L38" s="10" t="inlineStr">
-        <is>
-          <t>ADBDepartmentOwner</t>
-        </is>
-      </c>
-      <c r="M38" s="10" t="inlineStr">
-        <is>
-          <t>Column exists, unpopulated</t>
-        </is>
-      </c>
-      <c r="N38" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O38" s="10" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="P38" s="12" t="inlineStr">
-        <is>
-          <t>Needs department list</t>
-        </is>
-      </c>
-      <c r="Q38" s="10" t="inlineStr">
-        <is>
-          <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
-        </is>
-      </c>
-      <c r="R38" s="10" t="inlineStr"/>
-      <c r="S38" s="10" t="inlineStr"/>
-      <c r="T38" s="10" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>Site activity trend</t>
-        </is>
-      </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>Site visits by month</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>Page views across the estate</t>
-        </is>
-      </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>The series cut two ways</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>M365 usage report</t>
         </is>
       </c>
-      <c r="G39" s="10" t="inlineStr">
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>SharePoint site usage report, exported as CSV</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
 2. Sign in as a Microsoft 365 reports reader or global reader
@@ -5995,90 +6114,529 @@
 6. WARNING: the Site URL column is EMPTY on every row. Use Site Id and match it to a site list from Graph if you need the address</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
-        <is>
-          <t>'Page View Count' and 'Report Refresh Date'</t>
-        </is>
-      </c>
-      <c r="J39" s="10" t="inlineStr">
-        <is>
-          <t>Export the report weekly at the 7 day period. For each month, SUM 'Page View Count' across the weekly exports whose 'Report Refresh Date' falls in that month. CRITICAL: use the 7 DAY period only. Summing the 30, 90 or 180 day exports counts most days several times over, because those windows overlap while consecutive 7 day windows tile exactly</t>
-        </is>
-      </c>
-      <c r="K39" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>'Report Refresh Date', plus the RAC department list</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>Period: keep only the exports whose 'Report Refresh Date' falls in the last N months. Department: keep only the sites the RAC list assigns to that department</t>
+        </is>
+      </c>
+      <c r="K40" s="10" t="inlineStr">
         <is>
           <t>2 Site Activity</t>
         </is>
       </c>
-      <c r="L39" s="10" t="inlineStr">
-        <is>
-          <t>SiteVisits7, ReportRefreshDate</t>
-        </is>
-      </c>
-      <c r="M39" s="10" t="inlineStr">
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>ADBDepartmentOwner, ReportRefreshDate</t>
+        </is>
+      </c>
+      <c r="M40" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N39" s="10" t="inlineStr">
+      <c r="N40" s="10" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="O39" s="10" t="inlineStr">
+      <c r="O40" s="10" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="P40" s="12" t="inlineStr">
+        <is>
+          <t>Needs department list</t>
+        </is>
+      </c>
+      <c r="Q40" s="10" t="inlineStr">
+        <is>
+          <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
+        </is>
+      </c>
+      <c r="R40" s="10" t="inlineStr"/>
+      <c r="S40" s="10" t="inlineStr"/>
+      <c r="T40" s="10" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Retention rollup</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Permanent and temporary split</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Chart and table</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>How the holding divides by retention type</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>The EDRMS database, drm-npr, table public."Records"</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>1. Connect to the drm-npr PostgreSQL database with any SQL client
+2. The table is public."Records", quoted because of the capital R
+3. It holds DECLARED RECORDS ONLY, about 1,990 rows in UAT. There is no row for a document that was never declared, which is why every rate needs the scan built first</t>
+        </is>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>'EDRMSDuration' and 'EDRMSRetentionLabel'</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>Permanent is WHERE "EDRMSDuration" = 'Permanent'. Temporary is everything else that has a label. The two must add up to the labelled record count. The column is TEXT, so it can hold Permanent alongside 10, and must be cast before any arithmetic</t>
+        </is>
+      </c>
+      <c r="K41" s="10" t="inlineStr">
+        <is>
+          <t>1 Utilization Report</t>
+        </is>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>EDRMSDuration, EDRMSRetentionLabel</t>
+        </is>
+      </c>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N41" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O41" s="10" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="P41" s="11" t="inlineStr">
+        <is>
+          <t>Buildable now</t>
+        </is>
+      </c>
+      <c r="Q41" s="10" t="inlineStr"/>
+      <c r="R41" s="10" t="inlineStr"/>
+      <c r="S41" s="10" t="inlineStr"/>
+      <c r="T41" s="10" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Retention rollup</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Departments and libraries provisioned per term</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>Reach of each retention term</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>No source</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>No file exists</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>No column links a term to a library or a document</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>Cannot be worked out. The file plan table has no join key and the document row carries no term</t>
+        </is>
+      </c>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>4 File Plan</t>
+        </is>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>No join exists</t>
+        </is>
+      </c>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N42" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O42" s="10" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="P42" s="15" t="inlineStr">
+        <is>
+          <t>Needs new column or join</t>
+        </is>
+      </c>
+      <c r="Q42" s="10" t="inlineStr">
+        <is>
+          <t>Ask the development team to add a term reference to the document row, or supply a term to library mapping list. Why: nothing links a term to a document, so no per term figure can be produced even once the file plan is located</t>
+        </is>
+      </c>
+      <c r="R42" s="10" t="inlineStr"/>
+      <c r="S42" s="10" t="inlineStr"/>
+      <c r="T42" s="10" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>Retention rollup</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Disposed</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>Records actually disposed of</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>No source</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>No file exists</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>No column exists</t>
+        </is>
+      </c>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>Cannot be worked out. Nothing records that a disposal happened</t>
+        </is>
+      </c>
+      <c r="K43" s="10" t="inlineStr">
+        <is>
+          <t>1 Utilization Report</t>
+        </is>
+      </c>
+      <c r="L43" s="10" t="inlineStr">
+        <is>
+          <t>No column exists</t>
+        </is>
+      </c>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N43" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O43" s="10" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="P43" s="16" t="inlineStr">
+        <is>
+          <t>Needs application change</t>
+        </is>
+      </c>
+      <c r="Q43" s="10" t="inlineStr">
+        <is>
+          <t>Raise a change request for a disposal status field: status, approver, and date disposed. Why: nothing records that a disposal happened, so every completion figure is unanswerable</t>
+        </is>
+      </c>
+      <c r="R43" s="10" t="inlineStr"/>
+      <c r="S43" s="10" t="inlineStr"/>
+      <c r="T43" s="10" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>Format and storage</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>Files by format group</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Chart and table</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>The eight format families</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>EDRMS database</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>The EDRMS database, drm-npr, table public."Records"</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>1. Connect to the drm-npr PostgreSQL database with any SQL client
+2. The table is public."Records", quoted because of the capital R
+3. It holds DECLARED RECORDS ONLY, about 1,990 rows in UAT. There is no row for a document that was never declared, which is why every rate needs the scan built first</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>The FileMeta JSON column, key FileType</t>
+        </is>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>Take the extension from the FileType key, map it to one of the eight groups using the RAC mapping list (doc and docx both become Word), then COUNT(*) per group. The eight groups must add up to Total Records Declared exactly, which is the check that the mapping missed nothing</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
+          <t>1 Utilization Report</t>
+        </is>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>FormatGroup, FileType</t>
+        </is>
+      </c>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>Yes, mapping outstanding</t>
+        </is>
+      </c>
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="O44" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="P39" s="11" t="inlineStr">
+      <c r="P44" s="17" t="inlineStr">
+        <is>
+          <t>Decision needed</t>
+        </is>
+      </c>
+      <c r="Q44" s="10" t="inlineStr">
+        <is>
+          <t>Ask RAC for the file extension to format group mapping, a short list. Why: without it every extension falls into All other formats</t>
+        </is>
+      </c>
+      <c r="R44" s="10" t="inlineStr"/>
+      <c r="S44" s="10" t="inlineStr"/>
+      <c r="T44" s="10" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Format and storage</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>Storage by format group, Average file size</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Chart and table</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>Space each format consumes</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>Microsoft Graph</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>Microsoft Graph, run interactively</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>1. Go to https://aka.ms/ge, the Graph Explorer
+2. Sign in with a tenant account and consent to the scope named in the next column
+3. Paste the call from the Exact column heading cell into the address bar and click Run query
+4. Read the field named in that same cell out of the JSON response</t>
+        </is>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>GET /sites/{siteId}/drive/items, then the size field on each item</t>
+        </is>
+      </c>
+      <c r="J45" s="10" t="inlineStr">
+        <is>
+          <t>SUM the size field per format group for storage, and SUM(size)/COUNT(*) for the average. WARNING: a folder returns a CUMULATIVE size in Graph, so filter to files only or storage double counts</t>
+        </is>
+      </c>
+      <c r="K45" s="10" t="inlineStr">
+        <is>
+          <t>1 Utilization Report</t>
+        </is>
+      </c>
+      <c r="L45" s="10" t="inlineStr">
+        <is>
+          <t>FileSize</t>
+        </is>
+      </c>
+      <c r="M45" s="10" t="inlineStr">
+        <is>
+          <t>Yes, new key</t>
+        </is>
+      </c>
+      <c r="N45" s="10" t="inlineStr">
+        <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="O45" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P45" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q39" s="10" t="inlineStr">
-        <is>
-          <t>Confirm the job start date with the client. Why: the trend can only begin when weekly capture begins, and history never captured cannot be recovered</t>
-        </is>
-      </c>
-      <c r="R39" s="10" t="inlineStr"/>
-      <c r="S39" s="10" t="inlineStr"/>
-      <c r="T39" s="10" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>Site activity trend</t>
-        </is>
-      </c>
-      <c r="C40" s="10" t="inlineStr">
-        <is>
-          <t>Department and period filters</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>Filter</t>
-        </is>
-      </c>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>The series cut two ways</t>
-        </is>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="Q45" s="10" t="inlineStr"/>
+      <c r="R45" s="10" t="inlineStr"/>
+      <c r="S45" s="10" t="inlineStr"/>
+      <c r="T45" s="10" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Risk and compliance</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Compliant, active and inactive sites</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Tile and chart</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>Site health across the estate</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t>M365 usage report</t>
         </is>
       </c>
-      <c r="G40" s="10" t="inlineStr">
+      <c r="G46" s="10" t="inlineStr">
         <is>
           <t>SharePoint site usage report, exported as CSV</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
 2. Sign in as a Microsoft 365 reports reader or global reader
@@ -6088,581 +6646,49 @@
 6. WARNING: the Site URL column is EMPTY on every row. Use Site Id and match it to a site list from Graph if you need the address</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
-        <is>
-          <t>'Report Refresh Date', plus the RAC department list</t>
-        </is>
-      </c>
-      <c r="J40" s="10" t="inlineStr">
-        <is>
-          <t>Period: keep only the exports whose 'Report Refresh Date' falls in the last N months. Department: keep only the sites the RAC list assigns to that department</t>
-        </is>
-      </c>
-      <c r="K40" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>'Last Activity Date', 'Is Deleted'</t>
+        </is>
+      </c>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>Live sites are rows where 'Is Deleted' is False, 1,918 in the test tenant. Active is those with 'Last Activity Date' inside 90 days, inactive is the rest. The compliant subset cannot be filtered yet</t>
+        </is>
+      </c>
+      <c r="K46" s="10" t="inlineStr">
         <is>
           <t>2 Site Activity</t>
         </is>
       </c>
-      <c r="L40" s="10" t="inlineStr">
-        <is>
-          <t>ADBDepartmentOwner, ReportRefreshDate</t>
-        </is>
-      </c>
-      <c r="M40" s="10" t="inlineStr">
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>IsEdrmsCompliant, LastActivityDate</t>
+        </is>
+      </c>
+      <c r="M46" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N40" s="10" t="inlineStr">
+      <c r="N46" s="10" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="O40" s="10" t="inlineStr">
+      <c r="O46" s="10" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P40" s="12" t="inlineStr">
-        <is>
-          <t>Needs department list</t>
-        </is>
-      </c>
-      <c r="Q40" s="10" t="inlineStr">
-        <is>
-          <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
-        </is>
-      </c>
-      <c r="R40" s="10" t="inlineStr"/>
-      <c r="S40" s="10" t="inlineStr"/>
-      <c r="T40" s="10" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>Retention rollup</t>
-        </is>
-      </c>
-      <c r="C41" s="10" t="inlineStr">
-        <is>
-          <t>Permanent and temporary split</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
-        <is>
-          <t>Chart and table</t>
-        </is>
-      </c>
-      <c r="E41" s="10" t="inlineStr">
-        <is>
-          <t>How the holding divides by retention type</t>
-        </is>
-      </c>
-      <c r="F41" s="10" t="inlineStr">
-        <is>
-          <t>EDRMS database</t>
-        </is>
-      </c>
-      <c r="G41" s="10" t="inlineStr">
-        <is>
-          <t>The EDRMS database, drm-npr, table public."Records"</t>
-        </is>
-      </c>
-      <c r="H41" s="10" t="inlineStr">
-        <is>
-          <t>1. Connect to the drm-npr PostgreSQL database with any SQL client
-2. The table is public."Records", quoted because of the capital R
-3. It holds DECLARED RECORDS ONLY, about 1,990 rows in UAT. There is no row for a document that was never declared, which is why every rate needs the scan built first</t>
-        </is>
-      </c>
-      <c r="I41" s="10" t="inlineStr">
-        <is>
-          <t>'EDRMSDuration' and 'EDRMSRetentionLabel'</t>
-        </is>
-      </c>
-      <c r="J41" s="10" t="inlineStr">
-        <is>
-          <t>Permanent is WHERE "EDRMSDuration" = 'Permanent'. Temporary is everything else that has a label. The two must add up to the labelled record count. The column is TEXT, so it can hold Permanent alongside 10, and must be cast before any arithmetic</t>
-        </is>
-      </c>
-      <c r="K41" s="10" t="inlineStr">
-        <is>
-          <t>1 Utilization Report</t>
-        </is>
-      </c>
-      <c r="L41" s="10" t="inlineStr">
-        <is>
-          <t>EDRMSDuration, EDRMSRetentionLabel</t>
-        </is>
-      </c>
-      <c r="M41" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N41" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O41" s="10" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="P41" s="11" t="inlineStr">
-        <is>
-          <t>Buildable now</t>
-        </is>
-      </c>
-      <c r="Q41" s="10" t="inlineStr"/>
-      <c r="R41" s="10" t="inlineStr"/>
-      <c r="S41" s="10" t="inlineStr"/>
-      <c r="T41" s="10" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>Retention rollup</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
-        <is>
-          <t>Departments and libraries provisioned per term</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="E42" s="10" t="inlineStr">
-        <is>
-          <t>Reach of each retention term</t>
-        </is>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>No source</t>
-        </is>
-      </c>
-      <c r="G42" s="10" t="inlineStr">
-        <is>
-          <t>No file exists</t>
-        </is>
-      </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
-        </is>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
-        <is>
-          <t>No column links a term to a library or a document</t>
-        </is>
-      </c>
-      <c r="J42" s="10" t="inlineStr">
-        <is>
-          <t>Cannot be worked out. The file plan table has no join key and the document row carries no term</t>
-        </is>
-      </c>
-      <c r="K42" s="10" t="inlineStr">
-        <is>
-          <t>4 File Plan</t>
-        </is>
-      </c>
-      <c r="L42" s="10" t="inlineStr">
-        <is>
-          <t>No join exists</t>
-        </is>
-      </c>
-      <c r="M42" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N42" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O42" s="10" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="P42" s="15" t="inlineStr">
-        <is>
-          <t>Needs new column or join</t>
-        </is>
-      </c>
-      <c r="Q42" s="10" t="inlineStr">
-        <is>
-          <t>Ask the development team to add a term reference to the document row, or supply a term to library mapping list. Why: nothing links a term to a document, so no per term figure can be produced even once the file plan is located</t>
-        </is>
-      </c>
-      <c r="R42" s="10" t="inlineStr"/>
-      <c r="S42" s="10" t="inlineStr"/>
-      <c r="T42" s="10" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>Retention rollup</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>Disposed</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="E43" s="10" t="inlineStr">
-        <is>
-          <t>Records actually disposed of</t>
-        </is>
-      </c>
-      <c r="F43" s="10" t="inlineStr">
-        <is>
-          <t>No source</t>
-        </is>
-      </c>
-      <c r="G43" s="10" t="inlineStr">
-        <is>
-          <t>No file exists</t>
-        </is>
-      </c>
-      <c r="H43" s="10" t="inlineStr">
-        <is>
-          <t>There is nothing to open. No system this report can reach holds this figure. See the question column for who to ask</t>
-        </is>
-      </c>
-      <c r="I43" s="10" t="inlineStr">
-        <is>
-          <t>No column exists</t>
-        </is>
-      </c>
-      <c r="J43" s="10" t="inlineStr">
-        <is>
-          <t>Cannot be worked out. Nothing records that a disposal happened</t>
-        </is>
-      </c>
-      <c r="K43" s="10" t="inlineStr">
-        <is>
-          <t>1 Utilization Report</t>
-        </is>
-      </c>
-      <c r="L43" s="10" t="inlineStr">
-        <is>
-          <t>No column exists</t>
-        </is>
-      </c>
-      <c r="M43" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N43" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O43" s="10" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="P43" s="16" t="inlineStr">
-        <is>
-          <t>Needs application change</t>
-        </is>
-      </c>
-      <c r="Q43" s="10" t="inlineStr">
-        <is>
-          <t>Raise a change request for a disposal status field: status, approver, and date disposed. Why: nothing records that a disposal happened, so every completion figure is unanswerable</t>
-        </is>
-      </c>
-      <c r="R43" s="10" t="inlineStr"/>
-      <c r="S43" s="10" t="inlineStr"/>
-      <c r="T43" s="10" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>Format and storage</t>
-        </is>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t>Files by format group</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>Chart and table</t>
-        </is>
-      </c>
-      <c r="E44" s="10" t="inlineStr">
-        <is>
-          <t>The eight format families</t>
-        </is>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>EDRMS database</t>
-        </is>
-      </c>
-      <c r="G44" s="10" t="inlineStr">
-        <is>
-          <t>The EDRMS database, drm-npr, table public."Records"</t>
-        </is>
-      </c>
-      <c r="H44" s="10" t="inlineStr">
-        <is>
-          <t>1. Connect to the drm-npr PostgreSQL database with any SQL client
-2. The table is public."Records", quoted because of the capital R
-3. It holds DECLARED RECORDS ONLY, about 1,990 rows in UAT. There is no row for a document that was never declared, which is why every rate needs the scan built first</t>
-        </is>
-      </c>
-      <c r="I44" s="10" t="inlineStr">
-        <is>
-          <t>The FileMeta JSON column, key FileType</t>
-        </is>
-      </c>
-      <c r="J44" s="10" t="inlineStr">
-        <is>
-          <t>Take the extension from the FileType key, map it to one of the eight groups using the RAC mapping list (doc and docx both become Word), then COUNT(*) per group. The eight groups must add up to Total Records Declared exactly, which is the check that the mapping missed nothing</t>
-        </is>
-      </c>
-      <c r="K44" s="10" t="inlineStr">
-        <is>
-          <t>1 Utilization Report</t>
-        </is>
-      </c>
-      <c r="L44" s="10" t="inlineStr">
-        <is>
-          <t>FormatGroup, FileType</t>
-        </is>
-      </c>
-      <c r="M44" s="10" t="inlineStr">
-        <is>
-          <t>Yes, mapping outstanding</t>
-        </is>
-      </c>
-      <c r="N44" s="10" t="inlineStr">
-        <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="O44" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="P44" s="17" t="inlineStr">
+      <c r="P46" s="17" t="inlineStr">
         <is>
           <t>Decision needed</t>
         </is>
       </c>
-      <c r="Q44" s="10" t="inlineStr">
-        <is>
-          <t>Ask RAC for the file extension to format group mapping, a short list. Why: without it every extension falls into All other formats</t>
-        </is>
-      </c>
-      <c r="R44" s="10" t="inlineStr"/>
-      <c r="S44" s="10" t="inlineStr"/>
-      <c r="T44" s="10" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="9" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>Format and storage</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="inlineStr">
-        <is>
-          <t>Storage by format group, Average file size</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>Chart and table</t>
-        </is>
-      </c>
-      <c r="E45" s="10" t="inlineStr">
-        <is>
-          <t>Space each format consumes</t>
-        </is>
-      </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>Microsoft Graph</t>
-        </is>
-      </c>
-      <c r="G45" s="10" t="inlineStr">
-        <is>
-          <t>Microsoft Graph, run interactively</t>
-        </is>
-      </c>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t>1. Go to https://aka.ms/ge, the Graph Explorer
-2. Sign in with a tenant account and consent to the scope named in the next column
-3. Paste the call from the Exact column heading cell into the address bar and click Run query
-4. Read the field named in that same cell out of the JSON response</t>
-        </is>
-      </c>
-      <c r="I45" s="10" t="inlineStr">
-        <is>
-          <t>GET /sites/{siteId}/drive/items, then the size field on each item</t>
-        </is>
-      </c>
-      <c r="J45" s="10" t="inlineStr">
-        <is>
-          <t>SUM the size field per format group for storage, and SUM(size)/COUNT(*) for the average. WARNING: a folder returns a CUMULATIVE size in Graph, so filter to files only or storage double counts</t>
-        </is>
-      </c>
-      <c r="K45" s="10" t="inlineStr">
-        <is>
-          <t>1 Utilization Report</t>
-        </is>
-      </c>
-      <c r="L45" s="10" t="inlineStr">
-        <is>
-          <t>FileSize</t>
-        </is>
-      </c>
-      <c r="M45" s="10" t="inlineStr">
-        <is>
-          <t>Yes, new key</t>
-        </is>
-      </c>
-      <c r="N45" s="10" t="inlineStr">
-        <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="O45" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="P45" s="11" t="inlineStr">
-        <is>
-          <t>Buildable now</t>
-        </is>
-      </c>
-      <c r="Q45" s="10" t="inlineStr"/>
-      <c r="R45" s="10" t="inlineStr"/>
-      <c r="S45" s="10" t="inlineStr"/>
-      <c r="T45" s="10" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="9" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>Risk and compliance</t>
-        </is>
-      </c>
-      <c r="C46" s="10" t="inlineStr">
-        <is>
-          <t>Compliant, active and inactive sites</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>Tile and chart</t>
-        </is>
-      </c>
-      <c r="E46" s="10" t="inlineStr">
-        <is>
-          <t>Site health across the estate</t>
-        </is>
-      </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>M365 usage report</t>
-        </is>
-      </c>
-      <c r="G46" s="10" t="inlineStr">
-        <is>
-          <t>SharePoint site usage report, exported as CSV</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
-2. Sign in as a Microsoft 365 reports reader or global reader
-3. Set the period selector to 30 days
-4. Click Export, top right. A CSV downloads, named like SharePointSiteUsageDetail_2026-08-12.csv
-5. Open it in Excel. It has 23 columns and one row per site, 2,575 rows in the test tenant
-6. WARNING: the Site URL column is EMPTY on every row. Use Site Id and match it to a site list from Graph if you need the address</t>
-        </is>
-      </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>'Last Activity Date', 'Is Deleted'</t>
-        </is>
-      </c>
-      <c r="J46" s="10" t="inlineStr">
-        <is>
-          <t>Live sites are rows where 'Is Deleted' is False, 1,918 in the test tenant. Active is those with 'Last Activity Date' inside 90 days, inactive is the rest. The compliant subset cannot be filtered yet</t>
-        </is>
-      </c>
-      <c r="K46" s="10" t="inlineStr">
-        <is>
-          <t>2 Site Activity</t>
-        </is>
-      </c>
-      <c r="L46" s="10" t="inlineStr">
-        <is>
-          <t>IsEdrmsCompliant, LastActivityDate</t>
-        </is>
-      </c>
-      <c r="M46" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N46" s="10" t="inlineStr">
-        <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="O46" s="10" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="P46" s="17" t="inlineStr">
-        <is>
-          <t>Decision needed</t>
-        </is>
-      </c>
       <c r="Q46" s="10" t="inlineStr">
         <is>
-          <t>Ask Mihal Le which API returns the installed app list per site, for app {B255A2AF-7F63-4A30-966A-5D5FD99F97D7}. Why: it defines which sites are in the report at all. Also Ask whether an inactive site is 90 days or 300. The deck says 90, the metrics document says 300. Why: it changes every inactivity figure, and it is a one line change either way</t>
+          <t>Ask Leah Bancale for the PRODUCTION Cloud Governance Workspace report export, and whether a converted site is recorded in Cloud Governance the same way a created one is. Why: 'EDRMS Site Type' in that export is the compliant site list, so this single file defines which sites are in the report at all. Also Ask whether an inactive site is 90 days or 300. The deck says 90, the metrics document says 300. Why: it changes every inactivity figure, and it is a one line change either way</t>
         </is>
       </c>
       <c r="R46" s="10" t="inlineStr"/>
@@ -11176,7 +11202,8 @@
         <is>
           <t>1. Go to https://7rkd12-admin.sharepoint.com
 2. Open Content services, then Term store
-3. Expand the groups. The tenant holds 6 value sets and 16 terms, one level deep, which is NOT an institutional file plan</t>
+3. Expand the groups. 19 term groups were visible on 14 Aug 2026: ADB, ADB Exchange, ADB Test, ADB-Test, CPM Terms, Deleted Required, Emails, File Type, Finance, Group01, Group02, HR Tracking, LeilaTest, OneDrive, People, Search Dictionaries, SharePoint, Short Term Storage, System. NONE is named File Plan, Classification or Records.
+4. NOT RE-VERIFIED: the earlier note of 6 value sets and 16 terms one level deep was taken before those 19 groups were seen, and the groups were not expanded. Expand ADB and File Type and count depth before quoting either figure</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -11266,7 +11293,8 @@
         <is>
           <t>1. Go to https://7rkd12-admin.sharepoint.com
 2. Open Content services, then Term store
-3. Expand the groups. The tenant holds 6 value sets and 16 terms, one level deep, which is NOT an institutional file plan</t>
+3. Expand the groups. 19 term groups were visible on 14 Aug 2026: ADB, ADB Exchange, ADB Test, ADB-Test, CPM Terms, Deleted Required, Emails, File Type, Finance, Group01, Group02, HR Tracking, LeilaTest, OneDrive, People, Search Dictionaries, SharePoint, Short Term Storage, System. NONE is named File Plan, Classification or Records.
+4. NOT RE-VERIFIED: the earlier note of 6 value sets and 16 terms one level deep was taken before those 19 groups were seen, and the groups were not expanded. Expand ADB and File Type and count depth before quoting either figure</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">

--- a/EDRMS_Utilization_Report_Checker_2026-08-14.xlsx
+++ b/EDRMS_Utilization_Report_Checker_2026-08-14.xlsx
@@ -641,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C33"/>
+  <dimension ref="B1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -836,26 +836,38 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="3" t="inlineStr"/>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Questions</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>His own question against that row, in his words</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>The single most important fact</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr"/>
+          <t>What we found</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>What checking actually returned. Kept separate from his question so it stays visible which half is the ask and which half is the result</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Records holds declared records only</t>
+          <t>FINAL REMARKS</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>public."Records" in drm-npr contains declared records only, about 1,990 in UAT, and no row at all for an undeclared document. So every figure about declared records can be produced today, and every figure needing a denominator waits on the weekly SharePoint scan being built.</t>
+          <t>The conclusion, once it is settled</t>
         </is>
       </c>
     </row>
@@ -866,106 +878,222 @@
     <row r="24">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>The three query rules</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Getting any of these wrong produces a plausible wrong number, not an error</t>
-        </is>
-      </c>
+          <t>THE TEST TENANT AND THE ADB TENANT</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>1. Read the latest snapshot</t>
+          <t>The method transfers. The numbers do not.</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Or 1,057 compliant sites silently becomes 55,000 after a year of retained history</t>
+          <t>Everything in this workbook was proved against the 7rkd12 TEST tenant. Treat the METHOD as valid for ADB production: the same reports exist, under the same names, with the same column headings, and the same rules govern them. Microsoft and AvePoint do not ship different products to different tenants. What does NOT transfer is any figure. 1,032 compliant sites, 1,676 sites, 32,833 files, 1,990 declared records: all test tenant. Re-run each export against production and read the real number off it.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>2. A range sums SiteVisits7</t>
+          <t>What to change for ADB</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Never the 30, 90 or 180 day figures. Consecutive 7 day windows tile exactly, longer ones overlap and would count most days several times over</t>
+          <t>Two things only. Swap the tenant name in every admin URL, so 7rkd12-admin.sharepoint.com becomes ADB's equivalent. And point Cloud Governance at ADB's own AvePoint Online Services instance. Every click path, column name, Graph call and SQL statement is unchanged.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>3. Match on ReportRefreshDate, not SnapshotDate</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>The first is what Microsoft measured, the second is when the job ran, and they differ. An export taken on 12 Aug carried figures as at 10 Aug</t>
-        </is>
-      </c>
+          <t>The four exports that reproduce this workbook in production</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="B28" s="3" t="inlineStr"/>
-      <c r="C28" s="3" t="inlineStr"/>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>1. Cloud Governance Workspace report</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>AvePoint Online Services, Cloud Governance, Directory, Workspace report, Export report. Collect from Job monitor. Gives the EDRMS compliant site list via 'EDRMS Site Type', the site to department mapping via 'Department', plus owner, storage, activity and status. The single highest value file in the project. Ask Leah Bancale.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Sheets</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr"/>
+          <t>2. SharePoint site usage report</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>admin.microsoft.com, Reports, Usage, SharePoint site usage, Export. Gives File Count per site. Join to export 1 on Site Id to get the interim document total.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>01 to 06</t>
+          <t>3. SharePoint activity user detail report</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>One per dashboard, in the client's own order from PPT s13</t>
+          <t>admin.microsoft.com, Reports, Usage, SharePoint activity, Export. One row per LICENSED user, not per active user. Filter on Viewed Or Edited File Count above zero.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>DB 1 to DB 4</t>
+          <t>4. The drm-npr database</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>The four tables, every column, its type, source and remarks</t>
+          <t>Any SQL client against public."Records". Declared records only. Everything else in the report needs the weekly scan, which needs export 1 to know which sites to scan.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Questions to client</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Every question from the dashboard sheets, deduplicated and prioritised</t>
-        </is>
-      </c>
+      <c r="B32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="B33" s="4" t="inlineStr">
         <is>
+          <t>The single most important fact</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Records holds declared records only</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>public."Records" in drm-npr contains declared records only, about 1,990 in UAT, and no row at all for an undeclared document. So every figure about declared records can be produced today, and every figure needing a denominator waits on the weekly SharePoint scan being built.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>The three query rules</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Getting any of these wrong produces a plausible wrong number, not an error</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>1. Read the latest snapshot</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Or 1,057 compliant sites silently becomes 55,000 after a year of retained history</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>2. A range sums SiteVisits7</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Never the 30, 90 or 180 day figures. Consecutive 7 day windows tile exactly, longer ones overlap and would count most days several times over</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>3. Match on ReportRefreshDate, not SnapshotDate</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>The first is what Microsoft measured, the second is when the job ran, and they differ. An export taken on 12 Aug carried figures as at 10 Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="3" t="inlineStr"/>
+      <c r="C40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Sheets</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>01 to 06</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>One per dashboard, in the client's own order from PPT s13</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>DB 1 to DB 4</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>The four tables, every column, its type, source and remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Questions to client</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Every question from the dashboard sheets, deduplicated and prioritised</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="4" t="inlineStr">
+        <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Counts by status and by dashboard, computed from the sheets</t>
         </is>
@@ -2896,6 +3024,7 @@
       <c r="H5" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointActivity
+   (tenant independent URL: signing in as an ADB reports reader gives ADB figures)
 2. Sign in as a Microsoft 365 reports reader or global reader
 3. Set the period selector to 30 days
 4. Click Export. A CSV downloads, named like SharePointActivityUserDetail_2026-08-12.csv
@@ -3012,6 +3141,7 @@
       <c r="H6" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
+   (tenant independent URL: signing in as an ADB reports reader gives ADB figures)
 2. Sign in as a Microsoft 365 reports reader or global reader
 3. Set the period selector to 30 days
 4. Click Export, top right. A CSV downloads, named like SharePointSiteUsageDetail_2026-08-12.csv
@@ -3409,7 +3539,8 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>1. Open AvePoint Online Services, then Cloud Governance
+          <t>0. FOR ADB PRODUCTION: same product, same screen, same columns. Only the AvePoint Online Services instance differs. Ask Leah Bancale for access or for the export itself
+1. Open AvePoint Online Services, then Cloud Governance
 2. Left nav: Directory, then Workspace report
 3. Click Export report, top left. The file is queued, not downloaded immediately
 4. Collect it from Job monitor in the left nav when the job shows green
@@ -3705,6 +3836,7 @@
       <c r="H13" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointActivity
+   (tenant independent URL: signing in as an ADB reports reader gives ADB figures)
 2. Sign in as a Microsoft 365 reports reader or global reader
 3. Set the period selector to 30 days
 4. Click Export. A CSV downloads, named like SharePointActivityUserDetail_2026-08-12.csv
@@ -3793,6 +3925,7 @@
       <c r="H14" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointActivity
+   (tenant independent URL: signing in as an ADB reports reader gives ADB figures)
 2. Sign in as a Microsoft 365 reports reader or global reader
 3. Set the period selector to 30 days
 4. Click Export. A CSV downloads, named like SharePointActivityUserDetail_2026-08-12.csv
@@ -4145,6 +4278,7 @@
       <c r="H18" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
+   (tenant independent URL: signing in as an ADB reports reader gives ADB figures)
 2. Sign in as a Microsoft 365 reports reader or global reader
 3. Set the period selector to 30 days
 4. Click Export, top right. A CSV downloads, named like SharePointSiteUsageDetail_2026-08-12.csv
@@ -4238,6 +4372,7 @@
       <c r="H19" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
+   (tenant independent URL: signing in as an ADB reports reader gives ADB figures)
 2. Sign in as a Microsoft 365 reports reader or global reader
 3. Set the period selector to 30 days
 4. Click Export, top right. A CSV downloads, named like SharePointSiteUsageDetail_2026-08-12.csv
@@ -5306,6 +5441,7 @@
       <c r="H31" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
+   (tenant independent URL: signing in as an ADB reports reader gives ADB figures)
 2. Sign in as a Microsoft 365 reports reader or global reader
 3. Set the period selector to 30 days
 4. Click Export, top right. A CSV downloads, named like SharePointSiteUsageDetail_2026-08-12.csv
@@ -5399,6 +5535,7 @@
       <c r="H32" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
+   (tenant independent URL: signing in as an ADB reports reader gives ADB figures)
 2. Sign in as a Microsoft 365 reports reader or global reader
 3. Set the period selector to 30 days
 4. Click Export, top right. A CSV downloads, named like SharePointSiteUsageDetail_2026-08-12.csv
@@ -6014,6 +6151,7 @@
       <c r="H39" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
+   (tenant independent URL: signing in as an ADB reports reader gives ADB figures)
 2. Sign in as a Microsoft 365 reports reader or global reader
 3. Set the period selector to 30 days
 4. Click Export, top right. A CSV downloads, named like SharePointSiteUsageDetail_2026-08-12.csv
@@ -6107,6 +6245,7 @@
       <c r="H40" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
+   (tenant independent URL: signing in as an ADB reports reader gives ADB figures)
 2. Sign in as a Microsoft 365 reports reader or global reader
 3. Set the period selector to 30 days
 4. Click Export, top right. A CSV downloads, named like SharePointSiteUsageDetail_2026-08-12.csv
@@ -6639,6 +6778,7 @@
       <c r="H46" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
+   (tenant independent URL: signing in as an ADB reports reader gives ADB figures)
 2. Sign in as a Microsoft 365 reports reader or global reader
 3. Set the period selector to 30 days
 4. Click Export, top right. A CSV downloads, named like SharePointSiteUsageDetail_2026-08-12.csv
@@ -6732,6 +6872,7 @@
       <c r="H47" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
+   (tenant independent URL: signing in as an ADB reports reader gives ADB figures)
 2. Sign in as a Microsoft 365 reports reader or global reader
 3. Set the period selector to 30 days
 4. Click Export, top right. A CSV downloads, named like SharePointSiteUsageDetail_2026-08-12.csv
@@ -7692,6 +7833,7 @@
       <c r="H58" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
+   (tenant independent URL: signing in as an ADB reports reader gives ADB figures)
 2. Sign in as a Microsoft 365 reports reader or global reader
 3. Set the period selector to 30 days
 4. Click Export, top right. A CSV downloads, named like SharePointSiteUsageDetail_2026-08-12.csv
@@ -8592,6 +8734,7 @@
       <c r="H8" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
+   (tenant independent URL: signing in as an ADB reports reader gives ADB figures)
 2. Sign in as a Microsoft 365 reports reader or global reader
 3. Set the period selector to 30 days
 4. Click Export, top right. A CSV downloads, named like SharePointSiteUsageDetail_2026-08-12.csv
@@ -9128,6 +9271,7 @@
       <c r="H14" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
+   (tenant independent URL: signing in as an ADB reports reader gives ADB figures)
 2. Sign in as a Microsoft 365 reports reader or global reader
 3. Set the period selector to 30 days
 4. Click Export, top right. A CSV downloads, named like SharePointSiteUsageDetail_2026-08-12.csv
@@ -9309,6 +9453,7 @@
       <c r="H16" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
+   (tenant independent URL: signing in as an ADB reports reader gives ADB figures)
 2. Sign in as a Microsoft 365 reports reader or global reader
 3. Set the period selector to 30 days
 4. Click Export, top right. A CSV downloads, named like SharePointSiteUsageDetail_2026-08-12.csv
@@ -9402,6 +9547,7 @@
       <c r="H17" s="10" t="inlineStr">
         <is>
           <t>1. Go to https://admin.microsoft.com/#/reportsUsage/SharePointSiteUsage
+   (tenant independent URL: signing in as an ADB reports reader gives ADB figures)
 2. Sign in as a Microsoft 365 reports reader or global reader
 3. Set the period selector to 30 days
 4. Click Export, top right. A CSV downloads, named like SharePointSiteUsageDetail_2026-08-12.csv

--- a/EDRMS_Utilization_Report_Checker_2026-08-14.xlsx
+++ b/EDRMS_Utilization_Report_Checker_2026-08-14.xlsx
@@ -22,12 +22,12 @@
     <sheet name="Summary" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01 Bank-wide Oversight'!$A$4:$T$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02 Department Insights'!$A$4:$T$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03 Project Insights'!$A$4:$T$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04 Institutional File Plan'!$A$4:$T$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05 Retention and Disposal'!$A$4:$T$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06 Records and Archive Holdings'!$A$4:$T$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01 Bank-wide Oversight'!$A$4:$V$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02 Department Insights'!$A$4:$V$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03 Project Insights'!$A$4:$V$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04 Institutional File Plan'!$A$4:$V$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05 Retention and Disposal'!$A$4:$V$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06 Records and Archive Holdings'!$A$4:$V$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'DB 1 UtilizationReport'!$A$4:$I$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'DB 2 SiteActivity'!$A$4:$I$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'DB 3 UserActivity'!$A$4:$I$12</definedName>
@@ -641,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C45"/>
+  <dimension ref="B1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -778,322 +778,346 @@
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>In the tenant today?</t>
+          <t>Proved in test tenant (7rkd12)?</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Whether the data exists in the test tenant now</t>
+          <t>Whether the data was actually seen in the test tenant</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Testable in the tenant, and how</t>
+          <t>Proved in ADB production?</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>The actual check to run, with the export or the API call</t>
+          <t>Whether this has been run against ADB. TODAY EVERY ROW READS 'Not yet', because no export has been taken from production. The column exists so that gap is visible rather than assumed away. It is the checklist to work through once Leah Bancale supplies the production exports</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Effort</t>
+          <t>Exactly how it was proved</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Easy, Medium or Blocked</t>
+          <t>The evidence: which file, which columns, what came back, and on what date. Where a row was NOT proved it says so and says why. Where something was proved only partly, the sentence starting WHAT IS NOT PROVED names the half that is still assumption</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Testable in the tenant, and how</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>The verdict. Colour coded, see the Summary sheet</t>
+          <t>The actual check to run, with the export or the API call</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Question to ask the client</t>
+          <t>Effort</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>What to ask, and why it matters. Blank means nothing to ask</t>
+          <t>Easy, Medium or Blocked</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>His own question against that row, in his words</t>
+          <t>The verdict. Colour coded, see the Summary sheet</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>What we found</t>
+          <t>Question to ask the client</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>What checking actually returned. Kept separate from his question so it stays visible which half is the ask and which half is the result</t>
+          <t>What to ask, and why it matters. Blank means nothing to ask</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>FINAL REMARKS</t>
+          <t>Questions</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>The conclusion, once it is settled</t>
+          <t>His own question against that row, in his words</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="3" t="inlineStr"/>
-      <c r="C23" s="3" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>What we found</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>What checking actually returned. Kept separate from his question so it stays visible which half is the ask and which half is the result</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>THE TEST TENANT AND THE ADB TENANT</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr"/>
+          <t>FINAL REMARKS</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>The conclusion, once it is settled</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>The method transfers. The numbers do not.</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Everything in this workbook was proved against the 7rkd12 TEST tenant. Treat the METHOD as valid for ADB production: the same reports exist, under the same names, with the same column headings, and the same rules govern them. Microsoft and AvePoint do not ship different products to different tenants. What does NOT transfer is any figure. 1,032 compliant sites, 1,676 sites, 32,833 files, 1,990 declared records: all test tenant. Re-run each export against production and read the real number off it.</t>
-        </is>
-      </c>
+      <c r="B25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>What to change for ADB</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Two things only. Swap the tenant name in every admin URL, so 7rkd12-admin.sharepoint.com becomes ADB's equivalent. And point Cloud Governance at ADB's own AvePoint Online Services instance. Every click path, column name, Graph call and SQL statement is unchanged.</t>
-        </is>
-      </c>
+          <t>THE TEST TENANT AND THE ADB TENANT</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>The four exports that reproduce this workbook in production</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr"/>
+          <t>The method transfers. The numbers do not.</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Everything in this workbook was proved against the 7rkd12 TEST tenant. Treat the METHOD as valid for ADB production: the same reports exist, under the same names, with the same column headings, and the same rules govern them. Microsoft and AvePoint do not ship different products to different tenants. What does NOT transfer is any figure. 1,032 compliant sites, 1,676 sites, 32,833 files, 1,990 declared records: all test tenant. Re-run each export against production and read the real number off it.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>1. Cloud Governance Workspace report</t>
+          <t>What to change for ADB</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>AvePoint Online Services, Cloud Governance, Directory, Workspace report, Export report. Collect from Job monitor. Gives the EDRMS compliant site list via 'EDRMS Site Type', the site to department mapping via 'Department', plus owner, storage, activity and status. The single highest value file in the project. Ask Leah Bancale.</t>
+          <t>Two things only. Swap the tenant name in every admin URL, so 7rkd12-admin.sharepoint.com becomes ADB's equivalent. And point Cloud Governance at ADB's own AvePoint Online Services instance. Every click path, column name, Graph call and SQL statement is unchanged.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2. SharePoint site usage report</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>admin.microsoft.com, Reports, Usage, SharePoint site usage, Export. Gives File Count per site. Join to export 1 on Site Id to get the interim document total.</t>
-        </is>
-      </c>
+          <t>The four exports that reproduce this workbook in production</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>3. SharePoint activity user detail report</t>
+          <t>1. Cloud Governance Workspace report</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>admin.microsoft.com, Reports, Usage, SharePoint activity, Export. One row per LICENSED user, not per active user. Filter on Viewed Or Edited File Count above zero.</t>
+          <t>AvePoint Online Services, Cloud Governance, Directory, Workspace report, Export report. Collect from Job monitor. Gives the EDRMS compliant site list via 'EDRMS Site Type', the site to department mapping via 'Department', plus owner, storage, activity and status. The single highest value file in the project. Ask Leah Bancale.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>4. The drm-npr database</t>
+          <t>2. SharePoint site usage report</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Any SQL client against public."Records". Declared records only. Everything else in the report needs the weekly scan, which needs export 1 to know which sites to scan.</t>
+          <t>admin.microsoft.com, Reports, Usage, SharePoint site usage, Export. Gives File Count per site. Join to export 1 on Site Id to get the interim document total.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="3" t="inlineStr"/>
-      <c r="C32" s="3" t="inlineStr"/>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>3. SharePoint activity user detail report</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>admin.microsoft.com, Reports, Usage, SharePoint activity, Export. One row per LICENSED user, not per active user. Filter on Viewed Or Edited File Count above zero.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="B33" s="4" t="inlineStr">
         <is>
+          <t>4. The drm-npr database</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Any SQL client against public."Records". Declared records only. Everything else in the report needs the weekly scan, which needs export 1 to know which sites to scan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="3" t="inlineStr"/>
+      <c r="C34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
           <t>The single most important fact</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Records holds declared records only</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>public."Records" in drm-npr contains declared records only, about 1,990 in UAT, and no row at all for an undeclared document. So every figure about declared records can be produced today, and every figure needing a denominator waits on the weekly SharePoint scan being built.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="3" t="inlineStr"/>
       <c r="C35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>The three query rules</t>
+          <t>Records holds declared records only</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Getting any of these wrong produces a plausible wrong number, not an error</t>
+          <t>public."Records" in drm-npr contains declared records only, about 1,990 in UAT, and no row at all for an undeclared document. So every figure about declared records can be produced today, and every figure needing a denominator waits on the weekly SharePoint scan being built.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>1. Read the latest snapshot</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Or 1,057 compliant sites silently becomes 55,000 after a year of retained history</t>
-        </is>
-      </c>
+      <c r="B37" s="3" t="inlineStr"/>
+      <c r="C37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>2. A range sums SiteVisits7</t>
+          <t>The three query rules</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Never the 30, 90 or 180 day figures. Consecutive 7 day windows tile exactly, longer ones overlap and would count most days several times over</t>
+          <t>Getting any of these wrong produces a plausible wrong number, not an error</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>3. Match on ReportRefreshDate, not SnapshotDate</t>
+          <t>1. Read the latest snapshot</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>The first is what Microsoft measured, the second is when the job ran, and they differ. An export taken on 12 Aug carried figures as at 10 Aug</t>
+          <t>Or 1,057 compliant sites silently becomes 55,000 after a year of retained history</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="3" t="inlineStr"/>
-      <c r="C40" s="3" t="inlineStr"/>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2. A range sums SiteVisits7</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Never the 30, 90 or 180 day figures. Consecutive 7 day windows tile exactly, longer ones overlap and would count most days several times over</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Sheets</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr"/>
+          <t>3. Match on ReportRefreshDate, not SnapshotDate</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>The first is what Microsoft measured, the second is when the job ran, and they differ. An export taken on 12 Aug carried figures as at 10 Aug</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>01 to 06</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>One per dashboard, in the client's own order from PPT s13</t>
-        </is>
-      </c>
+      <c r="B42" s="3" t="inlineStr"/>
+      <c r="C42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>DB 1 to DB 4</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>The four tables, every column, its type, source and remarks</t>
-        </is>
-      </c>
+          <t>Sheets</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Questions to client</t>
+          <t>01 to 06</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Every question from the dashboard sheets, deduplicated and prioritised</t>
+          <t>One per dashboard, in the client's own order from PPT s13</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="4" t="inlineStr">
         <is>
+          <t>DB 1 to DB 4</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>The four tables, every column, its type, source and remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Questions to client</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Every question from the dashboard sheets, deduplicated and prioritised</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Counts by status and by dashboard, computed from the sheets</t>
         </is>
@@ -2454,7 +2478,7 @@
         </is>
       </c>
       <c r="C6" s="21">
-        <f>COUNTIF('01 Bank-wide Oversight'!$P:$P,$B6)+COUNTIF('02 Department Insights'!$P:$P,$B6)+COUNTIF('03 Project Insights'!$P:$P,$B6)+COUNTIF('04 Institutional File Plan'!$P:$P,$B6)+COUNTIF('05 Retention and Disposal'!$P:$P,$B6)+COUNTIF('06 Records and Archive Holdings'!$P:$P,$B6)</f>
+        <f>COUNTIF('01 Bank-wide Oversight'!$R:$R,$B6)+COUNTIF('02 Department Insights'!$R:$R,$B6)+COUNTIF('03 Project Insights'!$R:$R,$B6)+COUNTIF('04 Institutional File Plan'!$R:$R,$B6)+COUNTIF('05 Retention and Disposal'!$R:$R,$B6)+COUNTIF('06 Records and Archive Holdings'!$R:$R,$B6)</f>
         <v/>
       </c>
       <c r="D6" s="22">
@@ -2475,7 +2499,7 @@
         </is>
       </c>
       <c r="C7" s="21">
-        <f>COUNTIF('01 Bank-wide Oversight'!$P:$P,$B7)+COUNTIF('02 Department Insights'!$P:$P,$B7)+COUNTIF('03 Project Insights'!$P:$P,$B7)+COUNTIF('04 Institutional File Plan'!$P:$P,$B7)+COUNTIF('05 Retention and Disposal'!$P:$P,$B7)+COUNTIF('06 Records and Archive Holdings'!$P:$P,$B7)</f>
+        <f>COUNTIF('01 Bank-wide Oversight'!$R:$R,$B7)+COUNTIF('02 Department Insights'!$R:$R,$B7)+COUNTIF('03 Project Insights'!$R:$R,$B7)+COUNTIF('04 Institutional File Plan'!$R:$R,$B7)+COUNTIF('05 Retention and Disposal'!$R:$R,$B7)+COUNTIF('06 Records and Archive Holdings'!$R:$R,$B7)</f>
         <v/>
       </c>
       <c r="D7" s="22">
@@ -2496,7 +2520,7 @@
         </is>
       </c>
       <c r="C8" s="21">
-        <f>COUNTIF('01 Bank-wide Oversight'!$P:$P,$B8)+COUNTIF('02 Department Insights'!$P:$P,$B8)+COUNTIF('03 Project Insights'!$P:$P,$B8)+COUNTIF('04 Institutional File Plan'!$P:$P,$B8)+COUNTIF('05 Retention and Disposal'!$P:$P,$B8)+COUNTIF('06 Records and Archive Holdings'!$P:$P,$B8)</f>
+        <f>COUNTIF('01 Bank-wide Oversight'!$R:$R,$B8)+COUNTIF('02 Department Insights'!$R:$R,$B8)+COUNTIF('03 Project Insights'!$R:$R,$B8)+COUNTIF('04 Institutional File Plan'!$R:$R,$B8)+COUNTIF('05 Retention and Disposal'!$R:$R,$B8)+COUNTIF('06 Records and Archive Holdings'!$R:$R,$B8)</f>
         <v/>
       </c>
       <c r="D8" s="22">
@@ -2517,7 +2541,7 @@
         </is>
       </c>
       <c r="C9" s="21">
-        <f>COUNTIF('01 Bank-wide Oversight'!$P:$P,$B9)+COUNTIF('02 Department Insights'!$P:$P,$B9)+COUNTIF('03 Project Insights'!$P:$P,$B9)+COUNTIF('04 Institutional File Plan'!$P:$P,$B9)+COUNTIF('05 Retention and Disposal'!$P:$P,$B9)+COUNTIF('06 Records and Archive Holdings'!$P:$P,$B9)</f>
+        <f>COUNTIF('01 Bank-wide Oversight'!$R:$R,$B9)+COUNTIF('02 Department Insights'!$R:$R,$B9)+COUNTIF('03 Project Insights'!$R:$R,$B9)+COUNTIF('04 Institutional File Plan'!$R:$R,$B9)+COUNTIF('05 Retention and Disposal'!$R:$R,$B9)+COUNTIF('06 Records and Archive Holdings'!$R:$R,$B9)</f>
         <v/>
       </c>
       <c r="D9" s="22">
@@ -2538,7 +2562,7 @@
         </is>
       </c>
       <c r="C10" s="21">
-        <f>COUNTIF('01 Bank-wide Oversight'!$P:$P,$B10)+COUNTIF('02 Department Insights'!$P:$P,$B10)+COUNTIF('03 Project Insights'!$P:$P,$B10)+COUNTIF('04 Institutional File Plan'!$P:$P,$B10)+COUNTIF('05 Retention and Disposal'!$P:$P,$B10)+COUNTIF('06 Records and Archive Holdings'!$P:$P,$B10)</f>
+        <f>COUNTIF('01 Bank-wide Oversight'!$R:$R,$B10)+COUNTIF('02 Department Insights'!$R:$R,$B10)+COUNTIF('03 Project Insights'!$R:$R,$B10)+COUNTIF('04 Institutional File Plan'!$R:$R,$B10)+COUNTIF('05 Retention and Disposal'!$R:$R,$B10)+COUNTIF('06 Records and Archive Holdings'!$R:$R,$B10)</f>
         <v/>
       </c>
       <c r="D10" s="22">
@@ -2559,7 +2583,7 @@
         </is>
       </c>
       <c r="C11" s="21">
-        <f>COUNTIF('01 Bank-wide Oversight'!$P:$P,$B11)+COUNTIF('02 Department Insights'!$P:$P,$B11)+COUNTIF('03 Project Insights'!$P:$P,$B11)+COUNTIF('04 Institutional File Plan'!$P:$P,$B11)+COUNTIF('05 Retention and Disposal'!$P:$P,$B11)+COUNTIF('06 Records and Archive Holdings'!$P:$P,$B11)</f>
+        <f>COUNTIF('01 Bank-wide Oversight'!$R:$R,$B11)+COUNTIF('02 Department Insights'!$R:$R,$B11)+COUNTIF('03 Project Insights'!$R:$R,$B11)+COUNTIF('04 Institutional File Plan'!$R:$R,$B11)+COUNTIF('05 Retention and Disposal'!$R:$R,$B11)+COUNTIF('06 Records and Archive Holdings'!$R:$R,$B11)</f>
         <v/>
       </c>
       <c r="D11" s="22">
@@ -2580,7 +2604,7 @@
         </is>
       </c>
       <c r="C12" s="21">
-        <f>COUNTIF('01 Bank-wide Oversight'!$P:$P,$B12)+COUNTIF('02 Department Insights'!$P:$P,$B12)+COUNTIF('03 Project Insights'!$P:$P,$B12)+COUNTIF('04 Institutional File Plan'!$P:$P,$B12)+COUNTIF('05 Retention and Disposal'!$P:$P,$B12)+COUNTIF('06 Records and Archive Holdings'!$P:$P,$B12)</f>
+        <f>COUNTIF('01 Bank-wide Oversight'!$R:$R,$B12)+COUNTIF('02 Department Insights'!$R:$R,$B12)+COUNTIF('03 Project Insights'!$R:$R,$B12)+COUNTIF('04 Institutional File Plan'!$R:$R,$B12)+COUNTIF('05 Retention and Disposal'!$R:$R,$B12)+COUNTIF('06 Records and Archive Holdings'!$R:$R,$B12)</f>
         <v/>
       </c>
       <c r="D12" s="22">
@@ -2645,11 +2669,11 @@
         </is>
       </c>
       <c r="C17" s="21">
-        <f>COUNTA('01 Bank-wide Oversight'!$P$5:$P$200)</f>
+        <f>COUNTA('01 Bank-wide Oversight'!$R$5:$R$200)</f>
         <v/>
       </c>
       <c r="D17" s="21">
-        <f>COUNTIF('01 Bank-wide Oversight'!$P$5:$P$200,"Buildable now")</f>
+        <f>COUNTIF('01 Bank-wide Oversight'!$R$5:$R$200,"Buildable now")</f>
         <v/>
       </c>
       <c r="E17" s="21">
@@ -2665,11 +2689,11 @@
         </is>
       </c>
       <c r="C18" s="21">
-        <f>COUNTA('02 Department Insights'!$P$5:$P$200)</f>
+        <f>COUNTA('02 Department Insights'!$R$5:$R$200)</f>
         <v/>
       </c>
       <c r="D18" s="21">
-        <f>COUNTIF('02 Department Insights'!$P$5:$P$200,"Buildable now")</f>
+        <f>COUNTIF('02 Department Insights'!$R$5:$R$200,"Buildable now")</f>
         <v/>
       </c>
       <c r="E18" s="21">
@@ -2685,11 +2709,11 @@
         </is>
       </c>
       <c r="C19" s="21">
-        <f>COUNTA('03 Project Insights'!$P$5:$P$200)</f>
+        <f>COUNTA('03 Project Insights'!$R$5:$R$200)</f>
         <v/>
       </c>
       <c r="D19" s="21">
-        <f>COUNTIF('03 Project Insights'!$P$5:$P$200,"Buildable now")</f>
+        <f>COUNTIF('03 Project Insights'!$R$5:$R$200,"Buildable now")</f>
         <v/>
       </c>
       <c r="E19" s="21">
@@ -2705,11 +2729,11 @@
         </is>
       </c>
       <c r="C20" s="21">
-        <f>COUNTA('04 Institutional File Plan'!$P$5:$P$200)</f>
+        <f>COUNTA('04 Institutional File Plan'!$R$5:$R$200)</f>
         <v/>
       </c>
       <c r="D20" s="21">
-        <f>COUNTIF('04 Institutional File Plan'!$P$5:$P$200,"Buildable now")</f>
+        <f>COUNTIF('04 Institutional File Plan'!$R$5:$R$200,"Buildable now")</f>
         <v/>
       </c>
       <c r="E20" s="21">
@@ -2725,11 +2749,11 @@
         </is>
       </c>
       <c r="C21" s="21">
-        <f>COUNTA('05 Retention and Disposal'!$P$5:$P$200)</f>
+        <f>COUNTA('05 Retention and Disposal'!$R$5:$R$200)</f>
         <v/>
       </c>
       <c r="D21" s="21">
-        <f>COUNTIF('05 Retention and Disposal'!$P$5:$P$200,"Buildable now")</f>
+        <f>COUNTIF('05 Retention and Disposal'!$R$5:$R$200,"Buildable now")</f>
         <v/>
       </c>
       <c r="E21" s="21">
@@ -2745,11 +2769,11 @@
         </is>
       </c>
       <c r="C22" s="21">
-        <f>COUNTA('06 Records and Archive Holdings'!$P$5:$P$200)</f>
+        <f>COUNTA('06 Records and Archive Holdings'!$R$5:$R$200)</f>
         <v/>
       </c>
       <c r="D22" s="21">
-        <f>COUNTIF('06 Records and Archive Holdings'!$P$5:$P$200,"Buildable now")</f>
+        <f>COUNTIF('06 Records and Archive Holdings'!$R$5:$R$200,"Buildable now")</f>
         <v/>
       </c>
       <c r="E22" s="21">
@@ -2808,7 +2832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T62"/>
+  <dimension ref="A1:V62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2824,13 +2848,15 @@
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="58" customWidth="1" min="17" max="17"/>
-    <col width="46" customWidth="1" min="18" max="18"/>
-    <col width="40" customWidth="1" min="19" max="19"/>
-    <col width="69" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="66" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="58" customWidth="1" min="19" max="19"/>
+    <col width="46" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="69" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -2858,6 +2884,8 @@
       <c r="R1" s="6" t="n"/>
       <c r="S1" s="6" t="n"/>
       <c r="T1" s="6" t="n"/>
+      <c r="U1" s="6" t="n"/>
+      <c r="V1" s="6" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
@@ -2884,6 +2912,8 @@
       <c r="R2" s="6" t="n"/>
       <c r="S2" s="6" t="n"/>
       <c r="T2" s="6" t="n"/>
+      <c r="U2" s="6" t="n"/>
+      <c r="V2" s="6" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
@@ -2953,35 +2983,45 @@
       </c>
       <c r="N4" s="8" t="inlineStr">
         <is>
-          <t>In the tenant today?</t>
+          <t>Proved in test tenant (7rkd12)?</t>
         </is>
       </c>
       <c r="O4" s="8" t="inlineStr">
         <is>
+          <t>Proved in ADB production?</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>Exactly how it was proved: file, columns, result</t>
+        </is>
+      </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
           <t>Effort</t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t>Question to ask the client, and why</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>Questions</t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>What we found</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>FINAL REMARKS</t>
         </is>
@@ -3063,25 +3103,35 @@
       </c>
       <c r="O5" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 12 Aug 2026. Opened evidence_SharePointActivityUserDetail_2026-08-12.csv in Excel, filtered 'Viewed Or Edited File Count' to greater than 0. 30 rows in, 8 rows out. The answer is 8, not 30. WHAT IS NOT PROVED: the figure covers ALL SharePoint activity, not EDRMS sites, because the export has no per site breakdown, so it overstates adoption by an unknown amount</t>
+        </is>
+      </c>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr">
+      <c r="R5" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>How should EDRMS User be defined? Aldo Enriquez raised this on 10 Aug and Kylee Williamson replied that it will need defining. Neither settled it, and every option is buildable today, so this is a definition to agree rather than work to do</t>
         </is>
       </c>
-      <c r="R5" s="10" t="inlineStr">
+      <c r="T5" s="10" t="inlineStr">
         <is>
           <t>Is it accurate to determine the total edrms users in the sharepoint export? Do we have any other report as basis to get this number? Why sharepoint specifically? It is kpi and when clicked, opens the list of departments and each department determines the active users? How to map this?</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="U5" s="10" t="inlineStr">
         <is>
           <t>M365 Activity Report: it does not contain any activity that guarantees a person used an EDRMS compliant site.
 This report only includes activities made to any SharePoint file anywhere, including a team site that has nothing to do with EDRMS. The figure overstates EDRMS adoption, because it counts non EDRMS SharePoint use.
@@ -3090,7 +3140,7 @@
 Mapping users to departments: not from the RAC site list. That maps SITE to department. USER to department comes from the Entra ID 'department' attribute, joined on User Principal Name. Whether ADB populates it is NOT yet confirmed: four Graph Explorer attempts all returned the default property set, so the check has not actually run.</t>
         </is>
       </c>
-      <c r="T5" s="10" t="inlineStr">
+      <c r="V5" s="10" t="inlineStr">
         <is>
           <t>Kylee and Aldo have a conversation regarding how EDRMS user should be defined.
 CAVEATS:
@@ -3181,26 +3231,36 @@
       </c>
       <c r="O6" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 12 and 14 Aug 2026. Summed 'File Count' over evidence_SharePointSiteUsageDetail_2026-08-12.csv after excluding rows where 'Is Deleted' is True: 32,833 across 1,071 sites. Separately, on 14 Aug, ran /drives/{id}/root/delta by hand on one library: 73 items returned, 19 folders, 54 documents, and summing size over all 73 gave 684.3 MB against a true 172.2 MB. WHAT IS NOT PROVED: the scan has never been run at scale. 32,833 is an upper bound because File Count includes system libraries and non EDRMS sites</t>
+        </is>
+      </c>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr">
+      <c r="R6" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q6" s="10" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>Four questions, in the FINAL REMARKS column, ready to send to development</t>
         </is>
       </c>
-      <c r="R6" s="10" t="inlineStr">
+      <c r="T6" s="10" t="inlineStr">
         <is>
           <t>Where would I be getting this: site list from Graph.
 In the export, does this File Count count what specific documents it includes? Does a folder get classified as a file?</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="U6" s="10" t="inlineStr">
         <is>
           <t>FOLDERS: answered by measurement, not by reading documentation. Graph returns a facet on every item: an item carrying a 'folder' facet is a folder, one carrying a 'file' facet is a document.
 Measured on org_csd_1.4testsite, Documents library, 14 Aug 2026: 73 items returned, 19 of them folders, 54 documents. Counting rows instead of checking facets overstates by 35 percent.
@@ -3210,7 +3270,7 @@
 NOT VERIFIED: whether the plain GUID in the usage export's 'Site Id' is the same GUID that sits inside the Graph composite site id. If it is not, the usage report route needs a different join key.</t>
         </is>
       </c>
-      <c r="T6" s="10" t="inlineStr">
+      <c r="V6" s="10" t="inlineStr">
         <is>
           <t>The exact number does not exist in any system today. Not in the database, not in any report. public."Records" holds declared records only and has no concept of an undeclared document.
 TWO ROUTES, and the answer is to do both.
@@ -3297,18 +3357,28 @@
       </c>
       <c r="O7" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P7" s="11" t="inlineStr">
+      <c r="R7" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q7" s="10" t="inlineStr"/>
-      <c r="R7" s="10" t="inlineStr"/>
       <c r="S7" s="10" t="inlineStr"/>
       <c r="T7" s="10" t="inlineStr"/>
+      <c r="U7" s="10" t="inlineStr"/>
+      <c r="V7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -3383,18 +3453,28 @@
       </c>
       <c r="O8" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P8" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q8" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P8" s="11" t="inlineStr">
+      <c r="R8" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q8" s="10" t="inlineStr"/>
-      <c r="R8" s="10" t="inlineStr"/>
       <c r="S8" s="10" t="inlineStr"/>
       <c r="T8" s="10" t="inlineStr"/>
+      <c r="U8" s="10" t="inlineStr"/>
+      <c r="V8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -3469,32 +3549,42 @@
       </c>
       <c r="O9" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P9" s="10" t="inlineStr">
+        <is>
+          <t>NOT PROVED. The column EDRMSDueDateForDisposal is in the design and the query is written, but nobody has run SELECT COUNT(*), COUNT("EDRMSDueDateForDisposal") FROM public."Records" to see whether it is populated. If coverage is low this KPI measures retention label coverage, not disposal workload</t>
+        </is>
+      </c>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P9" s="11" t="inlineStr">
+      <c r="R9" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q9" s="10" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>Confirm the 12 month window is the one they want on the tile, and that the 30 day, 90 day and 12 month figures should nest inside one another</t>
         </is>
       </c>
-      <c r="R9" s="10" t="inlineStr">
+      <c r="T9" s="10" t="inlineStr">
         <is>
           <t>How do we determine the numbers here? Should the KPI change to a more specific title like Total Records Due for Disposal within 12 months or something similar?</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="U9" s="10" t="inlineStr">
         <is>
           <t>NOT VERIFIED: whether EDRMSDueDateForDisposal is actually populated. Run SELECT COUNT(*), COUNT("EDRMSDueDateForDisposal") FROM public."Records". If coverage is low, this KPI measures retention label coverage rather than disposal workload, which is a different thing wearing the same name.
 Records carrying no retention label have no due date and drop out of this figure SILENTLY. Nothing on screen says so. 'Records without a retention schedule' has to stay visible beside this KPI or the number flatters.
 Due for disposal does not mean awaiting action. Nothing records whether a disposal actually happened, because there is no DisposalStatus field. That is an application change for development, not a report change, and it is why S/N 36 to 38 on this sheet cannot be built.</t>
         </is>
       </c>
-      <c r="T9" s="10" t="inlineStr">
+      <c r="V9" s="10" t="inlineStr">
         <is>
           <t>DECIDED: change the KPI title to include the window. It now reads 'Total Records Due for Disposal, Next 12 Months'.
 This is consistent with the caption rule, which bans computed numbers in a label, not definitions. A window in the title is part of what the figure IS.
@@ -3575,30 +3665,40 @@
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
-          <t>Yes, in test</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O10" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P10" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 14 Aug 2026. Exported Cloud Governance Workspace report to evidence_CloudGovernance_WorkspaceReport_2026-08-14.csv, 1,209 rows, 93 columns. Filtered to rows where 'EDRMS Site Type' is not blank: 1,032 sites, all Status Active. The 177 excluded are template and admin sites. 'Department' is filled on 1,030 of the 1,032, of which 240 carry several departments separated by semicolons. Result saved as compliant_sites.csv and it feeds -CompliantSiteList directly. WHAT IS NOT PROVED: that a workspace carrying 'EDRMS Site Type' actually has the app installed. The register records intent, the app records reality</t>
+        </is>
+      </c>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P10" s="12" t="inlineStr">
+      <c r="R10" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q10" s="10" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>Ask Leah Bancale for the PRODUCTION Cloud Governance Workspace report export, and whether a converted site is recorded in Cloud Governance the same way a created one is. Why: 'EDRMS Site Type' in that export is the compliant site list, so this single file defines which sites are in the report at all. Also Ask whether an inactive site is 90 days or 300. The deck says 90, the metrics document says 300. Why: it changes every inactivity figure, and it is a one line change either way</t>
         </is>
       </c>
-      <c r="R10" s="10" t="inlineStr">
+      <c r="T10" s="10" t="inlineStr">
         <is>
           <t>How do we determine the list of all edrms compliant sites? Currently we know a site is an edrms compliant if it gets cg adopted. How are we going to know these list? Is it possible that all sites in the cloud governance be the count for this? Essentially when a site is cg created it is found in cloud governance and is it possible that all cg adopted sites are going to be move to the cloud governance then from there we can get the list?</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="U10" s="10" t="inlineStr">
         <is>
           <t>ANSWERED 14 Aug 2026 by exporting the Cloud Governance Workspace report.
 The export carries 93 columns over 1,209 workspaces. The column 'EDRMS Site Type' is populated on 1,032 rows with a single value, 'EDRMS Project Site'. It is a yes/no flag and it is the compliant site list. The 177 blanks are template and admin sites: edrmstemplate, template_drmdefault, app_edrms_data.
@@ -3610,7 +3710,7 @@
 TEST TENANT. Every URL is 7rkd12 and the site names are generated, such as dane-Site-Title-ddos-125. No count here transfers to production.</t>
         </is>
       </c>
-      <c r="T10" s="10" t="inlineStr">
+      <c r="V10" s="10" t="inlineStr">
         <is>
           <t>Get the list from the cloud governance. In cloud gov, sites listed are both cg adopted and cg created which are the basis of the edrms compliant site number.
 Leah Bancale confirmed on 14 Aug that EDRMS sites exist which did not come through Cloud Governance originally, and that those get converted to become compliant. So the CG CREATED list alone would be incomplete: it would miss every converted site, and those are the older, established departmental sites most likely to hold the largest volume of declared records.
@@ -3694,22 +3794,32 @@
       </c>
       <c r="O11" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P11" s="13" t="inlineStr">
+      <c r="R11" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q11" s="10" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>Ask whether a project site register exists: site URL to project number, and sovereign or nonsovereign. Check Cloud Governance first. Why: it is the only thing missing for the whole Project Insights dashboard, every measure on it is already producible</t>
         </is>
       </c>
-      <c r="R11" s="10" t="inlineStr"/>
-      <c r="S11" s="10" t="inlineStr"/>
       <c r="T11" s="10" t="inlineStr"/>
+      <c r="U11" s="10" t="inlineStr"/>
+      <c r="V11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
@@ -3782,22 +3892,32 @@
       </c>
       <c r="O12" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P12" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q12" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P12" s="13" t="inlineStr">
+      <c r="R12" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q12" s="10" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>Ask whether a project site register exists: site URL to project number, and sovereign or nonsovereign. Check Cloud Governance first. Why: it is the only thing missing for the whole Project Insights dashboard, every measure on it is already producible</t>
         </is>
       </c>
-      <c r="R12" s="10" t="inlineStr"/>
-      <c r="S12" s="10" t="inlineStr"/>
       <c r="T12" s="10" t="inlineStr"/>
+      <c r="U12" s="10" t="inlineStr"/>
+      <c r="V12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
@@ -3875,18 +3995,28 @@
       </c>
       <c r="O13" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P13" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 12 Aug 2026. evidence_SharePointActivityUserDetail_2026-08-12.csv, 30 rows, 12 columns, one row per LICENSED user. Only 8 rows have 'Viewed Or Edited File Count' above zero, so a row count overstates adoption by nearly four times</t>
+        </is>
+      </c>
+      <c r="Q13" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P13" s="11" t="inlineStr">
+      <c r="R13" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q13" s="10" t="inlineStr"/>
-      <c r="R13" s="10" t="inlineStr"/>
       <c r="S13" s="10" t="inlineStr"/>
       <c r="T13" s="10" t="inlineStr"/>
+      <c r="U13" s="10" t="inlineStr"/>
+      <c r="V13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
@@ -3964,18 +4094,28 @@
       </c>
       <c r="O14" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P14" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 12 Aug 2026. evidence_SharePointActivityUserDetail_2026-08-12.csv, 30 rows, 12 columns, one row per LICENSED user. Only 8 rows have 'Viewed Or Edited File Count' above zero, so a row count overstates adoption by nearly four times</t>
+        </is>
+      </c>
+      <c r="Q14" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P14" s="11" t="inlineStr">
+      <c r="R14" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr"/>
-      <c r="R14" s="10" t="inlineStr"/>
       <c r="S14" s="10" t="inlineStr"/>
       <c r="T14" s="10" t="inlineStr"/>
+      <c r="U14" s="10" t="inlineStr"/>
+      <c r="V14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
@@ -4048,22 +4188,32 @@
       </c>
       <c r="O15" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P15" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P15" s="13" t="inlineStr">
+      <c r="R15" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q15" s="10" t="inlineStr">
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>Ask which system owns staff, contractor and consultant classification and training completion. The client asks the same question on their own slide 54. Why: nothing in SharePoint holds it</t>
         </is>
       </c>
-      <c r="R15" s="10" t="inlineStr"/>
-      <c r="S15" s="10" t="inlineStr"/>
       <c r="T15" s="10" t="inlineStr"/>
+      <c r="U15" s="10" t="inlineStr"/>
+      <c r="V15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
@@ -4136,22 +4286,32 @@
       </c>
       <c r="O16" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P16" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q16" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P16" s="14" t="inlineStr">
+      <c r="R16" s="14" t="inlineStr">
         <is>
           <t>Needs reference list</t>
         </is>
       </c>
-      <c r="Q16" s="10" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>Ask which system owns staff, contractor and consultant classification and training completion. The client asks the same question on their own slide 54. Why: nothing in SharePoint holds it</t>
         </is>
       </c>
-      <c r="R16" s="10" t="inlineStr"/>
-      <c r="S16" s="10" t="inlineStr"/>
       <c r="T16" s="10" t="inlineStr"/>
+      <c r="U16" s="10" t="inlineStr"/>
+      <c r="V16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
@@ -4224,22 +4384,32 @@
       </c>
       <c r="O17" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P17" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P17" s="12" t="inlineStr">
+      <c r="R17" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q17" s="10" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R17" s="10" t="inlineStr"/>
-      <c r="S17" s="10" t="inlineStr"/>
       <c r="T17" s="10" t="inlineStr"/>
+      <c r="U17" s="10" t="inlineStr"/>
+      <c r="V17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
@@ -4318,22 +4488,32 @@
       </c>
       <c r="O18" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P18" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 12 Aug 2026. evidence_SharePointSiteUsageDetail_2026-08-12.csv, 2,575 rows, 23 columns, one row per site. Every column heading quoted in this workbook is checked against that file when it is rebuilt. Site URL is EMPTY on all 2,575 rows, so Site Id is the only usable site key</t>
+        </is>
+      </c>
+      <c r="Q18" s="10" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="P18" s="12" t="inlineStr">
+      <c r="R18" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q18" s="10" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R18" s="10" t="inlineStr"/>
-      <c r="S18" s="10" t="inlineStr"/>
       <c r="T18" s="10" t="inlineStr"/>
+      <c r="U18" s="10" t="inlineStr"/>
+      <c r="V18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
@@ -4412,22 +4592,32 @@
       </c>
       <c r="O19" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P19" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 12 Aug 2026. evidence_SharePointSiteUsageDetail_2026-08-12.csv, 2,575 rows, 23 columns, one row per site. Every column heading quoted in this workbook is checked against that file when it is rebuilt. Site URL is EMPTY on all 2,575 rows, so Site Id is the only usable site key</t>
+        </is>
+      </c>
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P19" s="12" t="inlineStr">
+      <c r="R19" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q19" s="10" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R19" s="10" t="inlineStr"/>
-      <c r="S19" s="10" t="inlineStr"/>
       <c r="T19" s="10" t="inlineStr"/>
+      <c r="U19" s="10" t="inlineStr"/>
+      <c r="V19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
@@ -4500,22 +4690,32 @@
       </c>
       <c r="O20" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P20" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q20" s="10" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="P20" s="15" t="inlineStr">
+      <c r="R20" s="15" t="inlineStr">
         <is>
           <t>Needs new column or join</t>
         </is>
       </c>
-      <c r="Q20" s="10" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>Ask the development team to capture Author on the document scan. Why: without it, creation activity can only be measured for records, not for documents</t>
         </is>
       </c>
-      <c r="R20" s="10" t="inlineStr"/>
-      <c r="S20" s="10" t="inlineStr"/>
       <c r="T20" s="10" t="inlineStr"/>
+      <c r="U20" s="10" t="inlineStr"/>
+      <c r="V20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
@@ -4590,22 +4790,32 @@
       </c>
       <c r="O21" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P21" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q21" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P21" s="12" t="inlineStr">
+      <c r="R21" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q21" s="10" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R21" s="10" t="inlineStr"/>
-      <c r="S21" s="10" t="inlineStr"/>
       <c r="T21" s="10" t="inlineStr"/>
+      <c r="U21" s="10" t="inlineStr"/>
+      <c r="V21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
@@ -4680,22 +4890,32 @@
       </c>
       <c r="O22" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P22" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q22" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P22" s="12" t="inlineStr">
+      <c r="R22" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q22" s="10" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R22" s="10" t="inlineStr"/>
-      <c r="S22" s="10" t="inlineStr"/>
       <c r="T22" s="10" t="inlineStr"/>
+      <c r="U22" s="10" t="inlineStr"/>
+      <c r="V22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
@@ -4768,22 +4988,32 @@
       </c>
       <c r="O23" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P23" s="10" t="inlineStr">
+        <is>
+          <t>Not exported. Nothing has been run to prove this one either way</t>
+        </is>
+      </c>
+      <c r="Q23" s="10" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="P23" s="12" t="inlineStr">
+      <c r="R23" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q23" s="10" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>None, but be explicit with the client that every rate waits on the scan</t>
         </is>
       </c>
-      <c r="R23" s="10" t="inlineStr"/>
-      <c r="S23" s="10" t="inlineStr"/>
       <c r="T23" s="10" t="inlineStr"/>
+      <c r="U23" s="10" t="inlineStr"/>
+      <c r="V23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
@@ -4856,22 +5086,32 @@
       </c>
       <c r="O24" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P24" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q24" s="10" t="inlineStr">
+        <is>
           <t>Easy once supplied</t>
         </is>
       </c>
-      <c r="P24" s="13" t="inlineStr">
+      <c r="R24" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q24" s="10" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>Ask who supplies division alongside department. Why: the tier was reinstated at the client's request but nothing in the tenant populates it, so the RAC list has to carry a division column too</t>
         </is>
       </c>
-      <c r="R24" s="10" t="inlineStr"/>
-      <c r="S24" s="10" t="inlineStr"/>
       <c r="T24" s="10" t="inlineStr"/>
+      <c r="U24" s="10" t="inlineStr"/>
+      <c r="V24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
@@ -4946,22 +5186,32 @@
       </c>
       <c r="O25" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P25" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q25" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P25" s="12" t="inlineStr">
+      <c r="R25" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q25" s="10" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R25" s="10" t="inlineStr"/>
-      <c r="S25" s="10" t="inlineStr"/>
       <c r="T25" s="10" t="inlineStr"/>
+      <c r="U25" s="10" t="inlineStr"/>
+      <c r="V25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
@@ -5034,22 +5284,32 @@
       </c>
       <c r="O26" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P26" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q26" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P26" s="13" t="inlineStr">
+      <c r="R26" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q26" s="10" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the physical holdings system: boxes, folders, locations, transfers and retrievals. Slide 67 names eServe for retrievals and shows an IR Dashboard screenshot. Why: none of it is in any system this report reads, and access to that dashboard may answer most of it</t>
         </is>
       </c>
-      <c r="R26" s="10" t="inlineStr"/>
-      <c r="S26" s="10" t="inlineStr"/>
       <c r="T26" s="10" t="inlineStr"/>
+      <c r="U26" s="10" t="inlineStr"/>
+      <c r="V26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="9" t="n">
@@ -5124,22 +5384,32 @@
       </c>
       <c r="O27" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P27" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q27" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P27" s="12" t="inlineStr">
+      <c r="R27" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q27" s="10" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R27" s="10" t="inlineStr"/>
-      <c r="S27" s="10" t="inlineStr"/>
       <c r="T27" s="10" t="inlineStr"/>
+      <c r="U27" s="10" t="inlineStr"/>
+      <c r="V27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="n">
@@ -5212,22 +5482,32 @@
       </c>
       <c r="O28" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P28" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q28" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P28" s="16" t="inlineStr">
+      <c r="R28" s="16" t="inlineStr">
         <is>
           <t>Needs application change</t>
         </is>
       </c>
-      <c r="Q28" s="10" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>Raise a change request for a disposal status field: status, approver, and date disposed. Why: nothing records that a disposal happened, so every completion figure is unanswerable</t>
         </is>
       </c>
-      <c r="R28" s="10" t="inlineStr"/>
-      <c r="S28" s="10" t="inlineStr"/>
       <c r="T28" s="10" t="inlineStr"/>
+      <c r="U28" s="10" t="inlineStr"/>
+      <c r="V28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
@@ -5300,22 +5580,32 @@
       </c>
       <c r="O29" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P29" s="10" t="inlineStr">
+        <is>
+          <t>Not exported. Nothing has been run to prove this one either way</t>
+        </is>
+      </c>
+      <c r="Q29" s="10" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="P29" s="12" t="inlineStr">
+      <c r="R29" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q29" s="10" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R29" s="10" t="inlineStr"/>
-      <c r="S29" s="10" t="inlineStr"/>
       <c r="T29" s="10" t="inlineStr"/>
+      <c r="U29" s="10" t="inlineStr"/>
+      <c r="V29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="n">
@@ -5391,18 +5681,28 @@
       </c>
       <c r="O30" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P30" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 14 Aug 2026. Run by hand in Graph Explorer against org_csd_1.4testsite. /sites, /sites/{id}/drives, /drives/{id}/list and /drives/{id}/root/delta all returned as documented. WARNING: /sites?search=* is a SEARCH over the crawled index, not an enumeration. It returned 451 sites against 1,676 from Get-PnPTenantSite</t>
+        </is>
+      </c>
+      <c r="Q30" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P30" s="11" t="inlineStr">
+      <c r="R30" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q30" s="10" t="inlineStr"/>
-      <c r="R30" s="10" t="inlineStr"/>
       <c r="S30" s="10" t="inlineStr"/>
       <c r="T30" s="10" t="inlineStr"/>
+      <c r="U30" s="10" t="inlineStr"/>
+      <c r="V30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="9" t="n">
@@ -5481,22 +5781,32 @@
       </c>
       <c r="O31" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P31" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 12 Aug 2026. evidence_SharePointSiteUsageDetail_2026-08-12.csv, 2,575 rows, 23 columns, one row per site. Every column heading quoted in this workbook is checked against that file when it is rebuilt. Site URL is EMPTY on all 2,575 rows, so Site Id is the only usable site key</t>
+        </is>
+      </c>
+      <c r="Q31" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P31" s="11" t="inlineStr">
+      <c r="R31" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q31" s="10" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>Ask whether an inactive site is 90 days or 300. The deck says 90, the metrics document says 300. Why: it changes every inactivity figure, and it is a one line change either way</t>
         </is>
       </c>
-      <c r="R31" s="10" t="inlineStr"/>
-      <c r="S31" s="10" t="inlineStr"/>
       <c r="T31" s="10" t="inlineStr"/>
+      <c r="U31" s="10" t="inlineStr"/>
+      <c r="V31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="9" t="n">
@@ -5575,22 +5885,32 @@
       </c>
       <c r="O32" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P32" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 12 Aug 2026. evidence_SharePointSiteUsageDetail_2026-08-12.csv, 2,575 rows, 23 columns, one row per site. Every column heading quoted in this workbook is checked against that file when it is rebuilt. Site URL is EMPTY on all 2,575 rows, so Site Id is the only usable site key</t>
+        </is>
+      </c>
+      <c r="Q32" s="10" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="P32" s="15" t="inlineStr">
+      <c r="R32" s="15" t="inlineStr">
         <is>
           <t>Needs new column or join</t>
         </is>
       </c>
-      <c r="Q32" s="10" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>Confirm that a deleted site should be counted from its disappearance between two exports. Why: absence cannot distinguish a deletion from a permissions change that hides the site</t>
         </is>
       </c>
-      <c r="R32" s="10" t="inlineStr"/>
-      <c r="S32" s="10" t="inlineStr"/>
       <c r="T32" s="10" t="inlineStr"/>
+      <c r="U32" s="10" t="inlineStr"/>
+      <c r="V32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="9" t="n">
@@ -5663,22 +5983,32 @@
       </c>
       <c r="O33" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P33" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q33" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P33" s="17" t="inlineStr">
+      <c r="R33" s="17" t="inlineStr">
         <is>
           <t>Decision needed</t>
         </is>
       </c>
-      <c r="Q33" s="10" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>Ask what archived means for a site, and how it is marked. Why: there is no definition anywhere, so the figure cannot be counted</t>
         </is>
       </c>
-      <c r="R33" s="10" t="inlineStr"/>
-      <c r="S33" s="10" t="inlineStr"/>
       <c r="T33" s="10" t="inlineStr"/>
+      <c r="U33" s="10" t="inlineStr"/>
+      <c r="V33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="9" t="n">
@@ -5751,22 +6081,32 @@
       </c>
       <c r="O34" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P34" s="10" t="inlineStr">
+        <is>
+          <t>Not exported. Nothing has been run to prove this one either way</t>
+        </is>
+      </c>
+      <c r="Q34" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P34" s="12" t="inlineStr">
+      <c r="R34" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q34" s="10" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R34" s="10" t="inlineStr"/>
-      <c r="S34" s="10" t="inlineStr"/>
       <c r="T34" s="10" t="inlineStr"/>
+      <c r="U34" s="10" t="inlineStr"/>
+      <c r="V34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="9" t="n">
@@ -5841,18 +6181,28 @@
       </c>
       <c r="O35" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P35" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q35" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P35" s="11" t="inlineStr">
+      <c r="R35" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q35" s="10" t="inlineStr"/>
-      <c r="R35" s="10" t="inlineStr"/>
       <c r="S35" s="10" t="inlineStr"/>
       <c r="T35" s="10" t="inlineStr"/>
+      <c r="U35" s="10" t="inlineStr"/>
+      <c r="V35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="9" t="n">
@@ -5927,18 +6277,28 @@
       </c>
       <c r="O36" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P36" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q36" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P36" s="11" t="inlineStr">
+      <c r="R36" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q36" s="10" t="inlineStr"/>
-      <c r="R36" s="10" t="inlineStr"/>
       <c r="S36" s="10" t="inlineStr"/>
       <c r="T36" s="10" t="inlineStr"/>
+      <c r="U36" s="10" t="inlineStr"/>
+      <c r="V36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="9" t="n">
@@ -6013,18 +6373,28 @@
       </c>
       <c r="O37" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P37" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q37" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P37" s="11" t="inlineStr">
+      <c r="R37" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q37" s="10" t="inlineStr"/>
-      <c r="R37" s="10" t="inlineStr"/>
       <c r="S37" s="10" t="inlineStr"/>
       <c r="T37" s="10" t="inlineStr"/>
+      <c r="U37" s="10" t="inlineStr"/>
+      <c r="V37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="9" t="n">
@@ -6097,22 +6467,32 @@
       </c>
       <c r="O38" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P38" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q38" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P38" s="12" t="inlineStr">
+      <c r="R38" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q38" s="10" t="inlineStr">
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R38" s="10" t="inlineStr"/>
-      <c r="S38" s="10" t="inlineStr"/>
       <c r="T38" s="10" t="inlineStr"/>
+      <c r="U38" s="10" t="inlineStr"/>
+      <c r="V38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="9" t="n">
@@ -6191,22 +6571,32 @@
       </c>
       <c r="O39" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P39" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 12 Aug 2026. evidence_SharePointSiteUsageDetail_2026-08-12.csv, 2,575 rows, 23 columns, one row per site. Every column heading quoted in this workbook is checked against that file when it is rebuilt. Site URL is EMPTY on all 2,575 rows, so Site Id is the only usable site key</t>
+        </is>
+      </c>
+      <c r="Q39" s="10" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="P39" s="11" t="inlineStr">
+      <c r="R39" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q39" s="10" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>Confirm the job start date with the client. Why: the trend can only begin when weekly capture begins, and history never captured cannot be recovered</t>
         </is>
       </c>
-      <c r="R39" s="10" t="inlineStr"/>
-      <c r="S39" s="10" t="inlineStr"/>
       <c r="T39" s="10" t="inlineStr"/>
+      <c r="U39" s="10" t="inlineStr"/>
+      <c r="V39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="9" t="n">
@@ -6285,22 +6675,32 @@
       </c>
       <c r="O40" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P40" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 12 Aug 2026. evidence_SharePointSiteUsageDetail_2026-08-12.csv, 2,575 rows, 23 columns, one row per site. Every column heading quoted in this workbook is checked against that file when it is rebuilt. Site URL is EMPTY on all 2,575 rows, so Site Id is the only usable site key</t>
+        </is>
+      </c>
+      <c r="Q40" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P40" s="12" t="inlineStr">
+      <c r="R40" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q40" s="10" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R40" s="10" t="inlineStr"/>
-      <c r="S40" s="10" t="inlineStr"/>
       <c r="T40" s="10" t="inlineStr"/>
+      <c r="U40" s="10" t="inlineStr"/>
+      <c r="V40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="9" t="n">
@@ -6375,18 +6775,28 @@
       </c>
       <c r="O41" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P41" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q41" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P41" s="11" t="inlineStr">
+      <c r="R41" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q41" s="10" t="inlineStr"/>
-      <c r="R41" s="10" t="inlineStr"/>
       <c r="S41" s="10" t="inlineStr"/>
       <c r="T41" s="10" t="inlineStr"/>
+      <c r="U41" s="10" t="inlineStr"/>
+      <c r="V41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="9" t="n">
@@ -6459,22 +6869,32 @@
       </c>
       <c r="O42" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P42" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q42" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P42" s="15" t="inlineStr">
+      <c r="R42" s="15" t="inlineStr">
         <is>
           <t>Needs new column or join</t>
         </is>
       </c>
-      <c r="Q42" s="10" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>Ask the development team to add a term reference to the document row, or supply a term to library mapping list. Why: nothing links a term to a document, so no per term figure can be produced even once the file plan is located</t>
         </is>
       </c>
-      <c r="R42" s="10" t="inlineStr"/>
-      <c r="S42" s="10" t="inlineStr"/>
       <c r="T42" s="10" t="inlineStr"/>
+      <c r="U42" s="10" t="inlineStr"/>
+      <c r="V42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="9" t="n">
@@ -6547,22 +6967,32 @@
       </c>
       <c r="O43" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P43" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q43" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P43" s="16" t="inlineStr">
+      <c r="R43" s="16" t="inlineStr">
         <is>
           <t>Needs application change</t>
         </is>
       </c>
-      <c r="Q43" s="10" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>Raise a change request for a disposal status field: status, approver, and date disposed. Why: nothing records that a disposal happened, so every completion figure is unanswerable</t>
         </is>
       </c>
-      <c r="R43" s="10" t="inlineStr"/>
-      <c r="S43" s="10" t="inlineStr"/>
       <c r="T43" s="10" t="inlineStr"/>
+      <c r="U43" s="10" t="inlineStr"/>
+      <c r="V43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="9" t="n">
@@ -6637,22 +7067,32 @@
       </c>
       <c r="O44" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P44" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q44" s="10" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="P44" s="17" t="inlineStr">
+      <c r="R44" s="17" t="inlineStr">
         <is>
           <t>Decision needed</t>
         </is>
       </c>
-      <c r="Q44" s="10" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the file extension to format group mapping, a short list. Why: without it every extension falls into All other formats</t>
         </is>
       </c>
-      <c r="R44" s="10" t="inlineStr"/>
-      <c r="S44" s="10" t="inlineStr"/>
       <c r="T44" s="10" t="inlineStr"/>
+      <c r="U44" s="10" t="inlineStr"/>
+      <c r="V44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="9" t="n">
@@ -6728,18 +7168,28 @@
       </c>
       <c r="O45" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P45" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 14 Aug 2026. Run by hand in Graph Explorer against org_csd_1.4testsite. /sites, /sites/{id}/drives, /drives/{id}/list and /drives/{id}/root/delta all returned as documented. WARNING: /sites?search=* is a SEARCH over the crawled index, not an enumeration. It returned 451 sites against 1,676 from Get-PnPTenantSite</t>
+        </is>
+      </c>
+      <c r="Q45" s="10" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="P45" s="11" t="inlineStr">
+      <c r="R45" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q45" s="10" t="inlineStr"/>
-      <c r="R45" s="10" t="inlineStr"/>
       <c r="S45" s="10" t="inlineStr"/>
       <c r="T45" s="10" t="inlineStr"/>
+      <c r="U45" s="10" t="inlineStr"/>
+      <c r="V45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="9" t="n">
@@ -6818,22 +7268,32 @@
       </c>
       <c r="O46" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P46" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 12 Aug 2026. evidence_SharePointSiteUsageDetail_2026-08-12.csv, 2,575 rows, 23 columns, one row per site. Every column heading quoted in this workbook is checked against that file when it is rebuilt. Site URL is EMPTY on all 2,575 rows, so Site Id is the only usable site key</t>
+        </is>
+      </c>
+      <c r="Q46" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P46" s="17" t="inlineStr">
+      <c r="R46" s="17" t="inlineStr">
         <is>
           <t>Decision needed</t>
         </is>
       </c>
-      <c r="Q46" s="10" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>Ask Leah Bancale for the PRODUCTION Cloud Governance Workspace report export, and whether a converted site is recorded in Cloud Governance the same way a created one is. Why: 'EDRMS Site Type' in that export is the compliant site list, so this single file defines which sites are in the report at all. Also Ask whether an inactive site is 90 days or 300. The deck says 90, the metrics document says 300. Why: it changes every inactivity figure, and it is a one line change either way</t>
         </is>
       </c>
-      <c r="R46" s="10" t="inlineStr"/>
-      <c r="S46" s="10" t="inlineStr"/>
       <c r="T46" s="10" t="inlineStr"/>
+      <c r="U46" s="10" t="inlineStr"/>
+      <c r="V46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="9" t="n">
@@ -6912,18 +7372,28 @@
       </c>
       <c r="O47" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P47" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 12 Aug 2026. evidence_SharePointSiteUsageDetail_2026-08-12.csv, 2,575 rows, 23 columns, one row per site. Every column heading quoted in this workbook is checked against that file when it is rebuilt. Site URL is EMPTY on all 2,575 rows, so Site Id is the only usable site key</t>
+        </is>
+      </c>
+      <c r="Q47" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P47" s="11" t="inlineStr">
+      <c r="R47" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q47" s="10" t="inlineStr"/>
-      <c r="R47" s="10" t="inlineStr"/>
       <c r="S47" s="10" t="inlineStr"/>
       <c r="T47" s="10" t="inlineStr"/>
+      <c r="U47" s="10" t="inlineStr"/>
+      <c r="V47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="9" t="n">
@@ -6999,18 +7469,28 @@
       </c>
       <c r="O48" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P48" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 14 Aug 2026. Run by hand in Graph Explorer against org_csd_1.4testsite. /sites, /sites/{id}/drives, /drives/{id}/list and /drives/{id}/root/delta all returned as documented. WARNING: /sites?search=* is a SEARCH over the crawled index, not an enumeration. It returned 451 sites against 1,676 from Get-PnPTenantSite</t>
+        </is>
+      </c>
+      <c r="Q48" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P48" s="11" t="inlineStr">
+      <c r="R48" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q48" s="10" t="inlineStr"/>
-      <c r="R48" s="10" t="inlineStr"/>
       <c r="S48" s="10" t="inlineStr"/>
       <c r="T48" s="10" t="inlineStr"/>
+      <c r="U48" s="10" t="inlineStr"/>
+      <c r="V48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="9" t="n">
@@ -7083,18 +7563,28 @@
       </c>
       <c r="O49" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P49" s="10" t="inlineStr">
+        <is>
+          <t>Not exported. Nothing has been run to prove this one either way</t>
+        </is>
+      </c>
+      <c r="Q49" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P49" s="11" t="inlineStr">
+      <c r="R49" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q49" s="10" t="inlineStr"/>
-      <c r="R49" s="10" t="inlineStr"/>
       <c r="S49" s="10" t="inlineStr"/>
       <c r="T49" s="10" t="inlineStr"/>
+      <c r="U49" s="10" t="inlineStr"/>
+      <c r="V49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="9" t="n">
@@ -7169,18 +7659,28 @@
       </c>
       <c r="O50" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P50" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q50" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P50" s="11" t="inlineStr">
+      <c r="R50" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q50" s="10" t="inlineStr"/>
-      <c r="R50" s="10" t="inlineStr"/>
       <c r="S50" s="10" t="inlineStr"/>
       <c r="T50" s="10" t="inlineStr"/>
+      <c r="U50" s="10" t="inlineStr"/>
+      <c r="V50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="9" t="n">
@@ -7253,18 +7753,28 @@
       </c>
       <c r="O51" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P51" s="10" t="inlineStr">
+        <is>
+          <t>Not exported. Nothing has been run to prove this one either way</t>
+        </is>
+      </c>
+      <c r="Q51" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P51" s="11" t="inlineStr">
+      <c r="R51" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q51" s="10" t="inlineStr"/>
-      <c r="R51" s="10" t="inlineStr"/>
       <c r="S51" s="10" t="inlineStr"/>
       <c r="T51" s="10" t="inlineStr"/>
+      <c r="U51" s="10" t="inlineStr"/>
+      <c r="V51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="9" t="n">
@@ -7337,22 +7847,32 @@
       </c>
       <c r="O52" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P52" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q52" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P52" s="13" t="inlineStr">
+      <c r="R52" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q52" s="10" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>Tell the client this cannot be produced and offer records created per library instead. Why: Microsoft exposes no per library activity anywhere</t>
         </is>
       </c>
-      <c r="R52" s="10" t="inlineStr"/>
-      <c r="S52" s="10" t="inlineStr"/>
       <c r="T52" s="10" t="inlineStr"/>
+      <c r="U52" s="10" t="inlineStr"/>
+      <c r="V52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="9" t="n">
@@ -7425,22 +7945,32 @@
       </c>
       <c r="O53" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P53" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q53" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P53" s="15" t="inlineStr">
+      <c r="R53" s="15" t="inlineStr">
         <is>
           <t>Needs new column or join</t>
         </is>
       </c>
-      <c r="Q53" s="10" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>Ask whether a library owner is maintained anywhere. Why: the site owner is the only one the tenant returns</t>
         </is>
       </c>
-      <c r="R53" s="10" t="inlineStr"/>
-      <c r="S53" s="10" t="inlineStr"/>
       <c r="T53" s="10" t="inlineStr"/>
+      <c r="U53" s="10" t="inlineStr"/>
+      <c r="V53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="9" t="n">
@@ -7515,22 +8045,32 @@
       </c>
       <c r="O54" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P54" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q54" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P54" s="11" t="inlineStr">
+      <c r="R54" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q54" s="10" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>Confirm the definition. Why: the client wrote 'with same filenames?' themselves, so they already suspect it is imprecise</t>
         </is>
       </c>
-      <c r="R54" s="10" t="inlineStr"/>
-      <c r="S54" s="10" t="inlineStr"/>
       <c r="T54" s="10" t="inlineStr"/>
+      <c r="U54" s="10" t="inlineStr"/>
+      <c r="V54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="9" t="n">
@@ -7603,22 +8143,32 @@
       </c>
       <c r="O55" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P55" s="10" t="inlineStr">
+        <is>
+          <t>Not exported. Nothing has been run to prove this one either way</t>
+        </is>
+      </c>
+      <c r="Q55" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P55" s="11" t="inlineStr">
+      <c r="R55" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q55" s="10" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>Confirm what counts as orphaned. Why: a missing site, a missing library and a missing owner give three different numbers</t>
         </is>
       </c>
-      <c r="R55" s="10" t="inlineStr"/>
-      <c r="S55" s="10" t="inlineStr"/>
       <c r="T55" s="10" t="inlineStr"/>
+      <c r="U55" s="10" t="inlineStr"/>
+      <c r="V55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="9" t="n">
@@ -7693,18 +8243,28 @@
       </c>
       <c r="O56" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P56" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q56" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P56" s="11" t="inlineStr">
+      <c r="R56" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q56" s="10" t="inlineStr"/>
-      <c r="R56" s="10" t="inlineStr"/>
       <c r="S56" s="10" t="inlineStr"/>
       <c r="T56" s="10" t="inlineStr"/>
+      <c r="U56" s="10" t="inlineStr"/>
+      <c r="V56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="9" t="n">
@@ -7779,22 +8339,32 @@
       </c>
       <c r="O57" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P57" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q57" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P57" s="11" t="inlineStr">
+      <c r="R57" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q57" s="10" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>Confirm the label names in use. Why: the tiles must carry the tenant's own wording</t>
         </is>
       </c>
-      <c r="R57" s="10" t="inlineStr"/>
-      <c r="S57" s="10" t="inlineStr"/>
       <c r="T57" s="10" t="inlineStr"/>
+      <c r="U57" s="10" t="inlineStr"/>
+      <c r="V57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="9" t="n">
@@ -7873,22 +8443,32 @@
       </c>
       <c r="O58" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P58" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 12 Aug 2026. evidence_SharePointSiteUsageDetail_2026-08-12.csv, 2,575 rows, 23 columns, one row per site. Every column heading quoted in this workbook is checked against that file when it is rebuilt. Site URL is EMPTY on all 2,575 rows, so Site Id is the only usable site key</t>
+        </is>
+      </c>
+      <c r="Q58" s="10" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="P58" s="15" t="inlineStr">
+      <c r="R58" s="15" t="inlineStr">
         <is>
           <t>Needs new column or join</t>
         </is>
       </c>
-      <c r="Q58" s="10" t="inlineStr">
+      <c r="S58" s="10" t="inlineStr">
         <is>
           <t>Add External Sharing to the site table, and check the four link count columns on production. Why: they are all zero in the test tenant, which may mean no sharing or may mean not populated, and those are very different answers</t>
         </is>
       </c>
-      <c r="R58" s="10" t="inlineStr"/>
-      <c r="S58" s="10" t="inlineStr"/>
       <c r="T58" s="10" t="inlineStr"/>
+      <c r="U58" s="10" t="inlineStr"/>
+      <c r="V58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="9" t="n">
@@ -7961,22 +8541,32 @@
       </c>
       <c r="O59" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P59" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q59" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P59" s="13" t="inlineStr">
+      <c r="R59" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q59" s="10" t="inlineStr">
+      <c r="S59" s="10" t="inlineStr">
         <is>
           <t>Ask whether audit log access can be granted, and confirm the purpose. Why: access requests, external sharing and permission exceptions live in the audit log, a different Graph surface with a different permission set</t>
         </is>
       </c>
-      <c r="R59" s="10" t="inlineStr"/>
-      <c r="S59" s="10" t="inlineStr"/>
       <c r="T59" s="10" t="inlineStr"/>
+      <c r="U59" s="10" t="inlineStr"/>
+      <c r="V59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="9" t="n">
@@ -8049,22 +8639,32 @@
       </c>
       <c r="O60" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P60" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q60" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P60" s="13" t="inlineStr">
+      <c r="R60" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q60" s="10" t="inlineStr">
+      <c r="S60" s="10" t="inlineStr">
         <is>
           <t>Ask whether audit log access can be granted, and confirm the purpose. Why: access requests, external sharing and permission exceptions live in the audit log, a different Graph surface with a different permission set</t>
         </is>
       </c>
-      <c r="R60" s="10" t="inlineStr"/>
-      <c r="S60" s="10" t="inlineStr"/>
       <c r="T60" s="10" t="inlineStr"/>
+      <c r="U60" s="10" t="inlineStr"/>
+      <c r="V60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="9" t="n">
@@ -8137,22 +8737,32 @@
       </c>
       <c r="O61" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P61" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q61" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P61" s="13" t="inlineStr">
+      <c r="R61" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q61" s="10" t="inlineStr">
+      <c r="S61" s="10" t="inlineStr">
         <is>
           <t>Tell the client search analytics cannot be attributed to a record. Why: Microsoft reports them at tenant level only</t>
         </is>
       </c>
-      <c r="R61" s="10" t="inlineStr"/>
-      <c r="S61" s="10" t="inlineStr"/>
       <c r="T61" s="10" t="inlineStr"/>
+      <c r="U61" s="10" t="inlineStr"/>
+      <c r="V61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="9" t="n">
@@ -8225,25 +8835,35 @@
       </c>
       <c r="O62" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P62" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q62" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P62" s="13" t="inlineStr">
+      <c r="R62" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q62" s="10" t="inlineStr">
+      <c r="S62" s="10" t="inlineStr">
         <is>
           <t>Offer most active sites instead. Why: document grain analytics do not exist</t>
         </is>
       </c>
-      <c r="R62" s="10" t="inlineStr"/>
-      <c r="S62" s="10" t="inlineStr"/>
       <c r="T62" s="10" t="inlineStr"/>
+      <c r="U62" s="10" t="inlineStr"/>
+      <c r="V62" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T62"/>
+  <autoFilter ref="A4:V62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8254,7 +8874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T26"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8270,13 +8890,15 @@
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="58" customWidth="1" min="17" max="17"/>
-    <col width="46" customWidth="1" min="18" max="18"/>
-    <col width="40" customWidth="1" min="19" max="19"/>
-    <col width="69" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="66" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="58" customWidth="1" min="19" max="19"/>
+    <col width="46" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="69" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -8304,6 +8926,8 @@
       <c r="R1" s="6" t="n"/>
       <c r="S1" s="6" t="n"/>
       <c r="T1" s="6" t="n"/>
+      <c r="U1" s="6" t="n"/>
+      <c r="V1" s="6" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
@@ -8330,6 +8954,8 @@
       <c r="R2" s="6" t="n"/>
       <c r="S2" s="6" t="n"/>
       <c r="T2" s="6" t="n"/>
+      <c r="U2" s="6" t="n"/>
+      <c r="V2" s="6" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
@@ -8399,35 +9025,45 @@
       </c>
       <c r="N4" s="8" t="inlineStr">
         <is>
-          <t>In the tenant today?</t>
+          <t>Proved in test tenant (7rkd12)?</t>
         </is>
       </c>
       <c r="O4" s="8" t="inlineStr">
         <is>
+          <t>Proved in ADB production?</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>Exactly how it was proved: file, columns, result</t>
+        </is>
+      </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
           <t>Effort</t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t>Question to ask the client, and why</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>Questions</t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>What we found</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>FINAL REMARKS</t>
         </is>
@@ -8504,22 +9140,32 @@
       </c>
       <c r="O5" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P5" s="12" t="inlineStr">
+      <c r="R5" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R5" s="10" t="inlineStr"/>
-      <c r="S5" s="10" t="inlineStr"/>
       <c r="T5" s="10" t="inlineStr"/>
+      <c r="U5" s="10" t="inlineStr"/>
+      <c r="V5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -8592,22 +9238,32 @@
       </c>
       <c r="O6" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P6" s="14" t="inlineStr">
+      <c r="R6" s="14" t="inlineStr">
         <is>
           <t>Needs reference list</t>
         </is>
       </c>
-      <c r="Q6" s="10" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>Ask who maintains this list and where it will live. Why: it is not a measurement, nothing can generate it, and without an owner the panel stays empty</t>
         </is>
       </c>
-      <c r="R6" s="10" t="inlineStr"/>
-      <c r="S6" s="10" t="inlineStr"/>
       <c r="T6" s="10" t="inlineStr"/>
+      <c r="U6" s="10" t="inlineStr"/>
+      <c r="V6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -8680,22 +9336,32 @@
       </c>
       <c r="O7" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>Not exported. Nothing has been run to prove this one either way</t>
+        </is>
+      </c>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P7" s="12" t="inlineStr">
+      <c r="R7" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q7" s="10" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R7" s="10" t="inlineStr"/>
-      <c r="S7" s="10" t="inlineStr"/>
       <c r="T7" s="10" t="inlineStr"/>
+      <c r="U7" s="10" t="inlineStr"/>
+      <c r="V7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -8774,22 +9440,32 @@
       </c>
       <c r="O8" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P8" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 12 Aug 2026. evidence_SharePointSiteUsageDetail_2026-08-12.csv, 2,575 rows, 23 columns, one row per site. Every column heading quoted in this workbook is checked against that file when it is rebuilt. Site URL is EMPTY on all 2,575 rows, so Site Id is the only usable site key</t>
+        </is>
+      </c>
+      <c r="Q8" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P8" s="12" t="inlineStr">
+      <c r="R8" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q8" s="10" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>Ask whether an inactive site is 90 days or 300. The deck says 90, the metrics document says 300. Why: it changes every inactivity figure, and it is a one line change either way</t>
         </is>
       </c>
-      <c r="R8" s="10" t="inlineStr"/>
-      <c r="S8" s="10" t="inlineStr"/>
       <c r="T8" s="10" t="inlineStr"/>
+      <c r="U8" s="10" t="inlineStr"/>
+      <c r="V8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -8862,22 +9538,32 @@
       </c>
       <c r="O9" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P9" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
           <t>Easy once supplied</t>
         </is>
       </c>
-      <c r="P9" s="13" t="inlineStr">
+      <c r="R9" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q9" s="10" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>Ask who supplies division alongside department. Why: the tier was reinstated at the client's request but nothing in the tenant populates it, so the RAC list has to carry a division column too</t>
         </is>
       </c>
-      <c r="R9" s="10" t="inlineStr"/>
-      <c r="S9" s="10" t="inlineStr"/>
       <c r="T9" s="10" t="inlineStr"/>
+      <c r="U9" s="10" t="inlineStr"/>
+      <c r="V9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
@@ -8950,22 +9636,32 @@
       </c>
       <c r="O10" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P10" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P10" s="13" t="inlineStr">
+      <c r="R10" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q10" s="10" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>Ask which system owns staff, contractor and consultant classification and training completion. The client asks the same question on their own slide 54. Why: nothing in SharePoint holds it</t>
         </is>
       </c>
-      <c r="R10" s="10" t="inlineStr"/>
-      <c r="S10" s="10" t="inlineStr"/>
       <c r="T10" s="10" t="inlineStr"/>
+      <c r="U10" s="10" t="inlineStr"/>
+      <c r="V10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -9041,22 +9737,32 @@
       </c>
       <c r="O11" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 14 Aug 2026. Run by hand in Graph Explorer against org_csd_1.4testsite. /sites, /sites/{id}/drives, /drives/{id}/list and /drives/{id}/root/delta all returned as documented. WARNING: /sites?search=* is a SEARCH over the crawled index, not an enumeration. It returned 451 sites against 1,676 from Get-PnPTenantSite</t>
+        </is>
+      </c>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P11" s="11" t="inlineStr">
+      <c r="R11" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q11" s="10" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>Warn the client only 7 day and all time windows exist. Why: their slide implies a monthly figure</t>
         </is>
       </c>
-      <c r="R11" s="10" t="inlineStr"/>
-      <c r="S11" s="10" t="inlineStr"/>
       <c r="T11" s="10" t="inlineStr"/>
+      <c r="U11" s="10" t="inlineStr"/>
+      <c r="V11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
@@ -9129,22 +9835,32 @@
       </c>
       <c r="O12" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P12" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q12" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P12" s="13" t="inlineStr">
+      <c r="R12" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q12" s="10" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>Ask whether audit log access can be granted, and confirm the purpose. Why: access requests, external sharing and permission exceptions live in the audit log, a different Graph surface with a different permission set</t>
         </is>
       </c>
-      <c r="R12" s="10" t="inlineStr"/>
-      <c r="S12" s="10" t="inlineStr"/>
       <c r="T12" s="10" t="inlineStr"/>
+      <c r="U12" s="10" t="inlineStr"/>
+      <c r="V12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
@@ -9217,22 +9933,32 @@
       </c>
       <c r="O13" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P13" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q13" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P13" s="13" t="inlineStr">
+      <c r="R13" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q13" s="10" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>Ask whether audit log access can be granted, and confirm the purpose. Why: access requests, external sharing and permission exceptions live in the audit log, a different Graph surface with a different permission set</t>
         </is>
       </c>
-      <c r="R13" s="10" t="inlineStr"/>
-      <c r="S13" s="10" t="inlineStr"/>
       <c r="T13" s="10" t="inlineStr"/>
+      <c r="U13" s="10" t="inlineStr"/>
+      <c r="V13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
@@ -9311,22 +10037,32 @@
       </c>
       <c r="O14" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P14" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 12 Aug 2026. evidence_SharePointSiteUsageDetail_2026-08-12.csv, 2,575 rows, 23 columns, one row per site. Every column heading quoted in this workbook is checked against that file when it is rebuilt. Site URL is EMPTY on all 2,575 rows, so Site Id is the only usable site key</t>
+        </is>
+      </c>
+      <c r="Q14" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P14" s="12" t="inlineStr">
+      <c r="R14" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R14" s="10" t="inlineStr"/>
-      <c r="S14" s="10" t="inlineStr"/>
       <c r="T14" s="10" t="inlineStr"/>
+      <c r="U14" s="10" t="inlineStr"/>
+      <c r="V14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
@@ -9399,22 +10135,32 @@
       </c>
       <c r="O15" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P15" s="10" t="inlineStr">
+        <is>
+          <t>Not exported. Nothing has been run to prove this one either way</t>
+        </is>
+      </c>
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P15" s="12" t="inlineStr">
+      <c r="R15" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q15" s="10" t="inlineStr">
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R15" s="10" t="inlineStr"/>
-      <c r="S15" s="10" t="inlineStr"/>
       <c r="T15" s="10" t="inlineStr"/>
+      <c r="U15" s="10" t="inlineStr"/>
+      <c r="V15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
@@ -9493,22 +10239,32 @@
       </c>
       <c r="O16" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P16" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 12 Aug 2026. evidence_SharePointSiteUsageDetail_2026-08-12.csv, 2,575 rows, 23 columns, one row per site. Every column heading quoted in this workbook is checked against that file when it is rebuilt. Site URL is EMPTY on all 2,575 rows, so Site Id is the only usable site key</t>
+        </is>
+      </c>
+      <c r="Q16" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P16" s="11" t="inlineStr">
+      <c r="R16" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q16" s="10" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>Ask whether an inactive site is 90 days or 300. The deck says 90, the metrics document says 300. Why: it changes every inactivity figure, and it is a one line change either way</t>
         </is>
       </c>
-      <c r="R16" s="10" t="inlineStr"/>
-      <c r="S16" s="10" t="inlineStr"/>
       <c r="T16" s="10" t="inlineStr"/>
+      <c r="U16" s="10" t="inlineStr"/>
+      <c r="V16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
@@ -9587,22 +10343,32 @@
       </c>
       <c r="O17" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P17" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 12 Aug 2026. evidence_SharePointSiteUsageDetail_2026-08-12.csv, 2,575 rows, 23 columns, one row per site. Every column heading quoted in this workbook is checked against that file when it is rebuilt. Site URL is EMPTY on all 2,575 rows, so Site Id is the only usable site key</t>
+        </is>
+      </c>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="P17" s="12" t="inlineStr">
+      <c r="R17" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q17" s="10" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R17" s="10" t="inlineStr"/>
-      <c r="S17" s="10" t="inlineStr"/>
       <c r="T17" s="10" t="inlineStr"/>
+      <c r="U17" s="10" t="inlineStr"/>
+      <c r="V17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
@@ -9675,22 +10441,32 @@
       </c>
       <c r="O18" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P18" s="10" t="inlineStr">
+        <is>
+          <t>Not exported. Nothing has been run to prove this one either way</t>
+        </is>
+      </c>
+      <c r="Q18" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P18" s="12" t="inlineStr">
+      <c r="R18" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q18" s="10" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R18" s="10" t="inlineStr"/>
-      <c r="S18" s="10" t="inlineStr"/>
       <c r="T18" s="10" t="inlineStr"/>
+      <c r="U18" s="10" t="inlineStr"/>
+      <c r="V18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
@@ -9763,22 +10539,32 @@
       </c>
       <c r="O19" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P19" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
           <t>Easy once supplied</t>
         </is>
       </c>
-      <c r="P19" s="13" t="inlineStr">
+      <c r="R19" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q19" s="10" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>Ask who supplies division alongside department. Why: the tier was reinstated at the client's request but nothing in the tenant populates it, so the RAC list has to carry a division column too</t>
         </is>
       </c>
-      <c r="R19" s="10" t="inlineStr"/>
-      <c r="S19" s="10" t="inlineStr"/>
       <c r="T19" s="10" t="inlineStr"/>
+      <c r="U19" s="10" t="inlineStr"/>
+      <c r="V19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
@@ -9851,22 +10637,32 @@
       </c>
       <c r="O20" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P20" s="10" t="inlineStr">
+        <is>
+          <t>Not exported. Nothing has been run to prove this one either way</t>
+        </is>
+      </c>
+      <c r="Q20" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P20" s="12" t="inlineStr">
+      <c r="R20" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q20" s="10" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R20" s="10" t="inlineStr"/>
-      <c r="S20" s="10" t="inlineStr"/>
       <c r="T20" s="10" t="inlineStr"/>
+      <c r="U20" s="10" t="inlineStr"/>
+      <c r="V20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
@@ -9939,22 +10735,32 @@
       </c>
       <c r="O21" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P21" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q21" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P21" s="15" t="inlineStr">
+      <c r="R21" s="15" t="inlineStr">
         <is>
           <t>Needs new column or join</t>
         </is>
       </c>
-      <c r="Q21" s="10" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>Ask where the institutional file plan actually lives. It is in neither the term store, which holds 6 dropdown value sets and 16 terms one level deep, nor Purview, which holds 53 flat retention labels. Why: a whole dashboard waits on the answer. Also Ask the development team to add a term reference to the document row, or supply a term to library mapping list. Why: nothing links a term to a document, so no per term figure can be produced even once the file plan is located</t>
         </is>
       </c>
-      <c r="R21" s="10" t="inlineStr"/>
-      <c r="S21" s="10" t="inlineStr"/>
       <c r="T21" s="10" t="inlineStr"/>
+      <c r="U21" s="10" t="inlineStr"/>
+      <c r="V21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
@@ -10027,22 +10833,32 @@
       </c>
       <c r="O22" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P22" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q22" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P22" s="13" t="inlineStr">
+      <c r="R22" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q22" s="10" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>Tell the client this is not available at library grain. Why: Microsoft exposes no per library viewer feed</t>
         </is>
       </c>
-      <c r="R22" s="10" t="inlineStr"/>
-      <c r="S22" s="10" t="inlineStr"/>
       <c r="T22" s="10" t="inlineStr"/>
+      <c r="U22" s="10" t="inlineStr"/>
+      <c r="V22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
@@ -10117,22 +10933,32 @@
       </c>
       <c r="O23" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P23" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q23" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P23" s="12" t="inlineStr">
+      <c r="R23" s="12" t="inlineStr">
         <is>
           <t>Needs department list</t>
         </is>
       </c>
-      <c r="Q23" s="10" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R23" s="10" t="inlineStr"/>
-      <c r="S23" s="10" t="inlineStr"/>
       <c r="T23" s="10" t="inlineStr"/>
+      <c r="U23" s="10" t="inlineStr"/>
+      <c r="V23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
@@ -10207,22 +11033,32 @@
       </c>
       <c r="O24" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P24" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q24" s="10" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="P24" s="16" t="inlineStr">
+      <c r="R24" s="16" t="inlineStr">
         <is>
           <t>Needs application change</t>
         </is>
       </c>
-      <c r="Q24" s="10" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>Raise a change request for a disposal status field: status, approver, and date disposed. Why: nothing records that a disposal happened, so every completion figure is unanswerable</t>
         </is>
       </c>
-      <c r="R24" s="10" t="inlineStr"/>
-      <c r="S24" s="10" t="inlineStr"/>
       <c r="T24" s="10" t="inlineStr"/>
+      <c r="U24" s="10" t="inlineStr"/>
+      <c r="V24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
@@ -10295,22 +11131,32 @@
       </c>
       <c r="O25" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P25" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q25" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P25" s="14" t="inlineStr">
+      <c r="R25" s="14" t="inlineStr">
         <is>
           <t>Needs reference list</t>
         </is>
       </c>
-      <c r="Q25" s="10" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>Ask who maintains this list and where it will live. Why: it is not a measurement, nothing can generate it, and without an owner the panel stays empty</t>
         </is>
       </c>
-      <c r="R25" s="10" t="inlineStr"/>
-      <c r="S25" s="10" t="inlineStr"/>
       <c r="T25" s="10" t="inlineStr"/>
+      <c r="U25" s="10" t="inlineStr"/>
+      <c r="V25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
@@ -10383,25 +11229,35 @@
       </c>
       <c r="O26" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P26" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q26" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P26" s="14" t="inlineStr">
+      <c r="R26" s="14" t="inlineStr">
         <is>
           <t>Needs reference list</t>
         </is>
       </c>
-      <c r="Q26" s="10" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>Ask who maintains this list and where it will live. Why: it is not a measurement, nothing can generate it, and without an owner the panel stays empty</t>
         </is>
       </c>
-      <c r="R26" s="10" t="inlineStr"/>
-      <c r="S26" s="10" t="inlineStr"/>
       <c r="T26" s="10" t="inlineStr"/>
+      <c r="U26" s="10" t="inlineStr"/>
+      <c r="V26" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T26"/>
+  <autoFilter ref="A4:V26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10412,7 +11268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10428,13 +11284,15 @@
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="58" customWidth="1" min="17" max="17"/>
-    <col width="46" customWidth="1" min="18" max="18"/>
-    <col width="40" customWidth="1" min="19" max="19"/>
-    <col width="69" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="66" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="58" customWidth="1" min="19" max="19"/>
+    <col width="46" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="69" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -10462,6 +11320,8 @@
       <c r="R1" s="6" t="n"/>
       <c r="S1" s="6" t="n"/>
       <c r="T1" s="6" t="n"/>
+      <c r="U1" s="6" t="n"/>
+      <c r="V1" s="6" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
@@ -10488,6 +11348,8 @@
       <c r="R2" s="6" t="n"/>
       <c r="S2" s="6" t="n"/>
       <c r="T2" s="6" t="n"/>
+      <c r="U2" s="6" t="n"/>
+      <c r="V2" s="6" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
@@ -10557,35 +11419,45 @@
       </c>
       <c r="N4" s="8" t="inlineStr">
         <is>
-          <t>In the tenant today?</t>
+          <t>Proved in test tenant (7rkd12)?</t>
         </is>
       </c>
       <c r="O4" s="8" t="inlineStr">
         <is>
+          <t>Proved in ADB production?</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>Exactly how it was proved: file, columns, result</t>
+        </is>
+      </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
           <t>Effort</t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t>Question to ask the client, and why</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>Questions</t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>What we found</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>FINAL REMARKS</t>
         </is>
@@ -10662,22 +11534,32 @@
       </c>
       <c r="O5" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P5" s="13" t="inlineStr">
+      <c r="R5" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>Ask whether a project site register exists: site URL to project number, and sovereign or nonsovereign. Check Cloud Governance first. Why: it is the only thing missing for the whole Project Insights dashboard, every measure on it is already producible</t>
         </is>
       </c>
-      <c r="R5" s="10" t="inlineStr"/>
-      <c r="S5" s="10" t="inlineStr"/>
       <c r="T5" s="10" t="inlineStr"/>
+      <c r="U5" s="10" t="inlineStr"/>
+      <c r="V5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -10750,22 +11632,32 @@
       </c>
       <c r="O6" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P6" s="13" t="inlineStr">
+      <c r="R6" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q6" s="10" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>Ask whether a project site register exists: site URL to project number, and sovereign or nonsovereign. Check Cloud Governance first. Why: it is the only thing missing for the whole Project Insights dashboard, every measure on it is already producible</t>
         </is>
       </c>
-      <c r="R6" s="10" t="inlineStr"/>
-      <c r="S6" s="10" t="inlineStr"/>
       <c r="T6" s="10" t="inlineStr"/>
+      <c r="U6" s="10" t="inlineStr"/>
+      <c r="V6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -10838,22 +11730,32 @@
       </c>
       <c r="O7" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P7" s="13" t="inlineStr">
+      <c r="R7" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q7" s="10" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>Ask whether a project site register exists: site URL to project number, and sovereign or nonsovereign. Check Cloud Governance first. Why: it is the only thing missing for the whole Project Insights dashboard, every measure on it is already producible</t>
         </is>
       </c>
-      <c r="R7" s="10" t="inlineStr"/>
-      <c r="S7" s="10" t="inlineStr"/>
       <c r="T7" s="10" t="inlineStr"/>
+      <c r="U7" s="10" t="inlineStr"/>
+      <c r="V7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -10926,22 +11828,32 @@
       </c>
       <c r="O8" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P8" s="10" t="inlineStr">
+        <is>
+          <t>Not exported. Nothing has been run to prove this one either way</t>
+        </is>
+      </c>
+      <c r="Q8" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P8" s="13" t="inlineStr">
+      <c r="R8" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q8" s="10" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>Ask whether a project site register exists: site URL to project number, and sovereign or nonsovereign. Check Cloud Governance first. Why: it is the only thing missing for the whole Project Insights dashboard, every measure on it is already producible</t>
         </is>
       </c>
-      <c r="R8" s="10" t="inlineStr"/>
-      <c r="S8" s="10" t="inlineStr"/>
       <c r="T8" s="10" t="inlineStr"/>
+      <c r="U8" s="10" t="inlineStr"/>
+      <c r="V8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -11014,22 +11926,32 @@
       </c>
       <c r="O9" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P9" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P9" s="13" t="inlineStr">
+      <c r="R9" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q9" s="10" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>Ask whether a project site register exists: site URL to project number, and sovereign or nonsovereign. Check Cloud Governance first. Why: it is the only thing missing for the whole Project Insights dashboard, every measure on it is already producible</t>
         </is>
       </c>
-      <c r="R9" s="10" t="inlineStr"/>
-      <c r="S9" s="10" t="inlineStr"/>
       <c r="T9" s="10" t="inlineStr"/>
+      <c r="U9" s="10" t="inlineStr"/>
+      <c r="V9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
@@ -11102,25 +12024,35 @@
       </c>
       <c r="O10" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P10" s="10" t="inlineStr">
+        <is>
+          <t>Not exported. Nothing has been run to prove this one either way</t>
+        </is>
+      </c>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P10" s="13" t="inlineStr">
+      <c r="R10" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q10" s="10" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>Ask whether a project site register exists: site URL to project number, and sovereign or nonsovereign. Check Cloud Governance first. Why: it is the only thing missing for the whole Project Insights dashboard, every measure on it is already producible</t>
         </is>
       </c>
-      <c r="R10" s="10" t="inlineStr"/>
-      <c r="S10" s="10" t="inlineStr"/>
       <c r="T10" s="10" t="inlineStr"/>
+      <c r="U10" s="10" t="inlineStr"/>
+      <c r="V10" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T10"/>
+  <autoFilter ref="A4:V10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11131,7 +12063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11147,13 +12079,15 @@
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="58" customWidth="1" min="17" max="17"/>
-    <col width="46" customWidth="1" min="18" max="18"/>
-    <col width="40" customWidth="1" min="19" max="19"/>
-    <col width="69" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="66" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="58" customWidth="1" min="19" max="19"/>
+    <col width="46" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="69" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -11181,6 +12115,8 @@
       <c r="R1" s="6" t="n"/>
       <c r="S1" s="6" t="n"/>
       <c r="T1" s="6" t="n"/>
+      <c r="U1" s="6" t="n"/>
+      <c r="V1" s="6" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
@@ -11207,6 +12143,8 @@
       <c r="R2" s="6" t="n"/>
       <c r="S2" s="6" t="n"/>
       <c r="T2" s="6" t="n"/>
+      <c r="U2" s="6" t="n"/>
+      <c r="V2" s="6" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
@@ -11276,35 +12214,45 @@
       </c>
       <c r="N4" s="8" t="inlineStr">
         <is>
-          <t>In the tenant today?</t>
+          <t>Proved in test tenant (7rkd12)?</t>
         </is>
       </c>
       <c r="O4" s="8" t="inlineStr">
         <is>
+          <t>Proved in ADB production?</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>Exactly how it was proved: file, columns, result</t>
+        </is>
+      </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
           <t>Effort</t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t>Question to ask the client, and why</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>Questions</t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>What we found</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>FINAL REMARKS</t>
         </is>
@@ -11384,22 +12332,32 @@
       </c>
       <c r="O5" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 14 Aug 2026, LOOKED AT ONLY. 19 term groups visible in the Term Store Management Tool. None is named File Plan, Classification, Records or Retention. The groups were NOT expanded, so no statement about depth is proved either way</t>
+        </is>
+      </c>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="R5" s="17" t="inlineStr">
         <is>
           <t>Decision needed</t>
         </is>
       </c>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>Ask where the institutional file plan actually lives. It is in neither the term store, which holds 6 dropdown value sets and 16 terms one level deep, nor Purview, which holds 53 flat retention labels. Why: a whole dashboard waits on the answer</t>
         </is>
       </c>
-      <c r="R5" s="10" t="inlineStr"/>
-      <c r="S5" s="10" t="inlineStr"/>
       <c r="T5" s="10" t="inlineStr"/>
+      <c r="U5" s="10" t="inlineStr"/>
+      <c r="V5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -11475,22 +12433,32 @@
       </c>
       <c r="O6" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT, 14 Aug 2026, LOOKED AT ONLY. 19 term groups visible in the Term Store Management Tool. None is named File Plan, Classification, Records or Retention. The groups were NOT expanded, so no statement about depth is proved either way</t>
+        </is>
+      </c>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="R6" s="17" t="inlineStr">
         <is>
           <t>Decision needed</t>
         </is>
       </c>
-      <c r="Q6" s="10" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>Ask where the institutional file plan actually lives. It is in neither the term store, which holds 6 dropdown value sets and 16 terms one level deep, nor Purview, which holds 53 flat retention labels. Why: a whole dashboard waits on the answer</t>
         </is>
       </c>
-      <c r="R6" s="10" t="inlineStr"/>
-      <c r="S6" s="10" t="inlineStr"/>
       <c r="T6" s="10" t="inlineStr"/>
+      <c r="U6" s="10" t="inlineStr"/>
+      <c r="V6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -11563,22 +12531,32 @@
       </c>
       <c r="O7" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P7" s="15" t="inlineStr">
+      <c r="R7" s="15" t="inlineStr">
         <is>
           <t>Needs new column or join</t>
         </is>
       </c>
-      <c r="Q7" s="10" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>Ask the development team to add a term reference to the document row, or supply a term to library mapping list. Why: nothing links a term to a document, so no per term figure can be produced even once the file plan is located</t>
         </is>
       </c>
-      <c r="R7" s="10" t="inlineStr"/>
-      <c r="S7" s="10" t="inlineStr"/>
       <c r="T7" s="10" t="inlineStr"/>
+      <c r="U7" s="10" t="inlineStr"/>
+      <c r="V7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -11651,22 +12629,32 @@
       </c>
       <c r="O8" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P8" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q8" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P8" s="15" t="inlineStr">
+      <c r="R8" s="15" t="inlineStr">
         <is>
           <t>Needs new column or join</t>
         </is>
       </c>
-      <c r="Q8" s="10" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>Ask the development team to add a term reference to the document row, or supply a term to library mapping list. Why: nothing links a term to a document, so no per term figure can be produced even once the file plan is located. Also Ask RAC for the site to department list, roughly 1,057 rows, one department per site URL. Check AvePoint Cloud Governance first, it may already hold it from the site request. Why: this single list unlocks every departmental figure in the report</t>
         </is>
       </c>
-      <c r="R8" s="10" t="inlineStr"/>
-      <c r="S8" s="10" t="inlineStr"/>
       <c r="T8" s="10" t="inlineStr"/>
+      <c r="U8" s="10" t="inlineStr"/>
+      <c r="V8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -11739,22 +12727,32 @@
       </c>
       <c r="O9" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P9" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P9" s="15" t="inlineStr">
+      <c r="R9" s="15" t="inlineStr">
         <is>
           <t>Needs new column or join</t>
         </is>
       </c>
-      <c r="Q9" s="10" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>Ask the development team to add a term reference to the document row, or supply a term to library mapping list. Why: nothing links a term to a document, so no per term figure can be produced even once the file plan is located</t>
         </is>
       </c>
-      <c r="R9" s="10" t="inlineStr"/>
-      <c r="S9" s="10" t="inlineStr"/>
       <c r="T9" s="10" t="inlineStr"/>
+      <c r="U9" s="10" t="inlineStr"/>
+      <c r="V9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
@@ -11827,22 +12825,32 @@
       </c>
       <c r="O10" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P10" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P10" s="15" t="inlineStr">
+      <c r="R10" s="15" t="inlineStr">
         <is>
           <t>Needs new column or join</t>
         </is>
       </c>
-      <c r="Q10" s="10" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>Ask the development team to add a term reference to the document row, or supply a term to library mapping list. Why: nothing links a term to a document, so no per term figure can be produced even once the file plan is located</t>
         </is>
       </c>
-      <c r="R10" s="10" t="inlineStr"/>
-      <c r="S10" s="10" t="inlineStr"/>
       <c r="T10" s="10" t="inlineStr"/>
+      <c r="U10" s="10" t="inlineStr"/>
+      <c r="V10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -11915,25 +12923,35 @@
       </c>
       <c r="O11" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="R11" s="17" t="inlineStr">
         <is>
           <t>Decision needed</t>
         </is>
       </c>
-      <c r="Q11" s="10" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>Ask what a business process is and how it relates to a file plan term. Why: the two are not the same thing, and it cannot be counted until somebody says what it counts</t>
         </is>
       </c>
-      <c r="R11" s="10" t="inlineStr"/>
-      <c r="S11" s="10" t="inlineStr"/>
       <c r="T11" s="10" t="inlineStr"/>
+      <c r="U11" s="10" t="inlineStr"/>
+      <c r="V11" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T11"/>
+  <autoFilter ref="A4:V11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11944,7 +12962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11960,13 +12978,15 @@
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="58" customWidth="1" min="17" max="17"/>
-    <col width="46" customWidth="1" min="18" max="18"/>
-    <col width="40" customWidth="1" min="19" max="19"/>
-    <col width="69" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="66" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="58" customWidth="1" min="19" max="19"/>
+    <col width="46" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="69" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -11994,6 +13014,8 @@
       <c r="R1" s="6" t="n"/>
       <c r="S1" s="6" t="n"/>
       <c r="T1" s="6" t="n"/>
+      <c r="U1" s="6" t="n"/>
+      <c r="V1" s="6" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
@@ -12020,6 +13042,8 @@
       <c r="R2" s="6" t="n"/>
       <c r="S2" s="6" t="n"/>
       <c r="T2" s="6" t="n"/>
+      <c r="U2" s="6" t="n"/>
+      <c r="V2" s="6" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
@@ -12089,35 +13113,45 @@
       </c>
       <c r="N4" s="8" t="inlineStr">
         <is>
-          <t>In the tenant today?</t>
+          <t>Proved in test tenant (7rkd12)?</t>
         </is>
       </c>
       <c r="O4" s="8" t="inlineStr">
         <is>
+          <t>Proved in ADB production?</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>Exactly how it was proved: file, columns, result</t>
+        </is>
+      </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
           <t>Effort</t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t>Question to ask the client, and why</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>Questions</t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>What we found</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>FINAL REMARKS</t>
         </is>
@@ -12196,18 +13230,28 @@
       </c>
       <c r="O5" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr">
+      <c r="R5" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q5" s="10" t="inlineStr"/>
-      <c r="R5" s="10" t="inlineStr"/>
       <c r="S5" s="10" t="inlineStr"/>
       <c r="T5" s="10" t="inlineStr"/>
+      <c r="U5" s="10" t="inlineStr"/>
+      <c r="V5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -12282,22 +13326,32 @@
       </c>
       <c r="O6" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr">
+      <c r="R6" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q6" s="10" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>Confirm the 12 month window is the one they want on the tile, and that the 30 day, 90 day and 12 month figures should nest inside one another</t>
         </is>
       </c>
-      <c r="R6" s="10" t="inlineStr"/>
-      <c r="S6" s="10" t="inlineStr"/>
       <c r="T6" s="10" t="inlineStr"/>
+      <c r="U6" s="10" t="inlineStr"/>
+      <c r="V6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -12372,18 +13426,28 @@
       </c>
       <c r="O7" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>NOT EXPORTED. The 53 label figure came from looking at the screen, not from an export. Every retention and disposal figure rests on it. Export it before quoting anything from this row</t>
+        </is>
+      </c>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P7" s="11" t="inlineStr">
+      <c r="R7" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q7" s="10" t="inlineStr"/>
-      <c r="R7" s="10" t="inlineStr"/>
       <c r="S7" s="10" t="inlineStr"/>
       <c r="T7" s="10" t="inlineStr"/>
+      <c r="U7" s="10" t="inlineStr"/>
+      <c r="V7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -12458,22 +13522,32 @@
       </c>
       <c r="O8" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P8" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q8" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P8" s="11" t="inlineStr">
+      <c r="R8" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q8" s="10" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>Warn that this counts dates passed, not action outstanding. Why: the two read alike and are not the same</t>
         </is>
       </c>
-      <c r="R8" s="10" t="inlineStr"/>
-      <c r="S8" s="10" t="inlineStr"/>
       <c r="T8" s="10" t="inlineStr"/>
+      <c r="U8" s="10" t="inlineStr"/>
+      <c r="V8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -12548,18 +13622,28 @@
       </c>
       <c r="O9" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P9" s="10" t="inlineStr">
+        <is>
+          <t>TEST TENANT / UAT. Direct query against public."Records" in drm-npr. About 1,990 rows, all declared records. NOT re-run recently: treat the row count as indicative and re-query before quoting it</t>
+        </is>
+      </c>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P9" s="11" t="inlineStr">
+      <c r="R9" s="11" t="inlineStr">
         <is>
           <t>Buildable now</t>
         </is>
       </c>
-      <c r="Q9" s="10" t="inlineStr"/>
-      <c r="R9" s="10" t="inlineStr"/>
       <c r="S9" s="10" t="inlineStr"/>
       <c r="T9" s="10" t="inlineStr"/>
+      <c r="U9" s="10" t="inlineStr"/>
+      <c r="V9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
@@ -12634,22 +13718,32 @@
       </c>
       <c r="O10" s="10" t="inlineStr">
         <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="P10" s="10" t="inlineStr">
+        <is>
+          <t>Not exported. Nothing has been run to prove this one either way</t>
+        </is>
+      </c>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="R10" s="17" t="inlineStr">
         <is>
           <t>Decision needed</t>
         </is>
       </c>
-      <c r="Q10" s="10" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>Check the mapping list's key yourself before asking anyone. Why: it decides whether this metric is safe or fragile, and it is a five minute check</t>
         </is>
       </c>
-      <c r="R10" s="10" t="inlineStr"/>
-      <c r="S10" s="10" t="inlineStr"/>
       <c r="T10" s="10" t="inlineStr"/>
+      <c r="U10" s="10" t="inlineStr"/>
+      <c r="V10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -12722,22 +13816,32 @@
       </c>
       <c r="O11" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P11" s="15" t="inlineStr">
+      <c r="R11" s="15" t="inlineStr">
         <is>
           <t>Needs new column or join</t>
         </is>
       </c>
-      <c r="Q11" s="10" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>Ask the development team to add a term reference to the document row, or supply a term to library mapping list. Why: nothing links a term to a document, so no per term figure can be produced even once the file plan is located</t>
         </is>
       </c>
-      <c r="R11" s="10" t="inlineStr"/>
-      <c r="S11" s="10" t="inlineStr"/>
       <c r="T11" s="10" t="inlineStr"/>
+      <c r="U11" s="10" t="inlineStr"/>
+      <c r="V11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
@@ -12810,22 +13914,32 @@
       </c>
       <c r="O12" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P12" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q12" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P12" s="16" t="inlineStr">
+      <c r="R12" s="16" t="inlineStr">
         <is>
           <t>Needs application change</t>
         </is>
       </c>
-      <c r="Q12" s="10" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>Raise a change request for a disposal status field: status, approver, and date disposed. Why: nothing records that a disposal happened, so every completion figure is unanswerable</t>
         </is>
       </c>
-      <c r="R12" s="10" t="inlineStr"/>
-      <c r="S12" s="10" t="inlineStr"/>
       <c r="T12" s="10" t="inlineStr"/>
+      <c r="U12" s="10" t="inlineStr"/>
+      <c r="V12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
@@ -12898,25 +14012,35 @@
       </c>
       <c r="O13" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P13" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q13" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P13" s="13" t="inlineStr">
+      <c r="R13" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q13" s="10" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the physical holdings system: boxes, folders, locations, transfers and retrievals. Slide 67 names eServe for retrievals and shows an IR Dashboard screenshot. Why: none of it is in any system this report reads, and access to that dashboard may answer most of it</t>
         </is>
       </c>
-      <c r="R13" s="10" t="inlineStr"/>
-      <c r="S13" s="10" t="inlineStr"/>
       <c r="T13" s="10" t="inlineStr"/>
+      <c r="U13" s="10" t="inlineStr"/>
+      <c r="V13" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T13"/>
+  <autoFilter ref="A4:V13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12927,7 +14051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -12943,13 +14067,15 @@
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="58" customWidth="1" min="17" max="17"/>
-    <col width="46" customWidth="1" min="18" max="18"/>
-    <col width="40" customWidth="1" min="19" max="19"/>
-    <col width="69" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="66" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="58" customWidth="1" min="19" max="19"/>
+    <col width="46" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="69" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -12977,6 +14103,8 @@
       <c r="R1" s="6" t="n"/>
       <c r="S1" s="6" t="n"/>
       <c r="T1" s="6" t="n"/>
+      <c r="U1" s="6" t="n"/>
+      <c r="V1" s="6" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
@@ -13003,6 +14131,8 @@
       <c r="R2" s="6" t="n"/>
       <c r="S2" s="6" t="n"/>
       <c r="T2" s="6" t="n"/>
+      <c r="U2" s="6" t="n"/>
+      <c r="V2" s="6" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
@@ -13072,35 +14202,45 @@
       </c>
       <c r="N4" s="8" t="inlineStr">
         <is>
-          <t>In the tenant today?</t>
+          <t>Proved in test tenant (7rkd12)?</t>
         </is>
       </c>
       <c r="O4" s="8" t="inlineStr">
         <is>
+          <t>Proved in ADB production?</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>Exactly how it was proved: file, columns, result</t>
+        </is>
+      </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
           <t>Effort</t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t>Question to ask the client, and why</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>Questions</t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>What we found</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>FINAL REMARKS</t>
         </is>
@@ -13177,22 +14317,32 @@
       </c>
       <c r="O5" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P5" s="13" t="inlineStr">
+      <c r="R5" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the physical holdings system: boxes, folders, locations, transfers and retrievals. Slide 67 names eServe for retrievals and shows an IR Dashboard screenshot. Why: none of it is in any system this report reads, and access to that dashboard may answer most of it</t>
         </is>
       </c>
-      <c r="R5" s="10" t="inlineStr"/>
-      <c r="S5" s="10" t="inlineStr"/>
       <c r="T5" s="10" t="inlineStr"/>
+      <c r="U5" s="10" t="inlineStr"/>
+      <c r="V5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -13265,22 +14415,32 @@
       </c>
       <c r="O6" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P6" s="13" t="inlineStr">
+      <c r="R6" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q6" s="10" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the physical holdings system: boxes, folders, locations, transfers and retrievals. Slide 67 names eServe for retrievals and shows an IR Dashboard screenshot. Why: none of it is in any system this report reads, and access to that dashboard may answer most of it</t>
         </is>
       </c>
-      <c r="R6" s="10" t="inlineStr"/>
-      <c r="S6" s="10" t="inlineStr"/>
       <c r="T6" s="10" t="inlineStr"/>
+      <c r="U6" s="10" t="inlineStr"/>
+      <c r="V6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -13353,22 +14513,32 @@
       </c>
       <c r="O7" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P7" s="13" t="inlineStr">
+      <c r="R7" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q7" s="10" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the physical holdings system: boxes, folders, locations, transfers and retrievals. Slide 67 names eServe for retrievals and shows an IR Dashboard screenshot. Why: none of it is in any system this report reads, and access to that dashboard may answer most of it. Answer their direct question: capacity can be displayed the moment somebody holds the figure</t>
         </is>
       </c>
-      <c r="R7" s="10" t="inlineStr"/>
-      <c r="S7" s="10" t="inlineStr"/>
       <c r="T7" s="10" t="inlineStr"/>
+      <c r="U7" s="10" t="inlineStr"/>
+      <c r="V7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -13441,22 +14611,32 @@
       </c>
       <c r="O8" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P8" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q8" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P8" s="13" t="inlineStr">
+      <c r="R8" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q8" s="10" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the physical holdings system: boxes, folders, locations, transfers and retrievals. Slide 67 names eServe for retrievals and shows an IR Dashboard screenshot. Why: none of it is in any system this report reads, and access to that dashboard may answer most of it</t>
         </is>
       </c>
-      <c r="R8" s="10" t="inlineStr"/>
-      <c r="S8" s="10" t="inlineStr"/>
       <c r="T8" s="10" t="inlineStr"/>
+      <c r="U8" s="10" t="inlineStr"/>
+      <c r="V8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -13529,22 +14709,32 @@
       </c>
       <c r="O9" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P9" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P9" s="13" t="inlineStr">
+      <c r="R9" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q9" s="10" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the physical holdings system: boxes, folders, locations, transfers and retrievals. Slide 67 names eServe for retrievals and shows an IR Dashboard screenshot. Why: none of it is in any system this report reads, and access to that dashboard may answer most of it</t>
         </is>
       </c>
-      <c r="R9" s="10" t="inlineStr"/>
-      <c r="S9" s="10" t="inlineStr"/>
       <c r="T9" s="10" t="inlineStr"/>
+      <c r="U9" s="10" t="inlineStr"/>
+      <c r="V9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
@@ -13617,22 +14807,32 @@
       </c>
       <c r="O10" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P10" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="P10" s="13" t="inlineStr">
+      <c r="R10" s="13" t="inlineStr">
         <is>
           <t>Needs new data source</t>
         </is>
       </c>
-      <c r="Q10" s="10" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>Ask RAC for the physical holdings system: boxes, folders, locations, transfers and retrievals. Slide 67 names eServe for retrievals and shows an IR Dashboard screenshot. Why: none of it is in any system this report reads, and access to that dashboard may answer most of it</t>
         </is>
       </c>
-      <c r="R10" s="10" t="inlineStr"/>
-      <c r="S10" s="10" t="inlineStr"/>
       <c r="T10" s="10" t="inlineStr"/>
+      <c r="U10" s="10" t="inlineStr"/>
+      <c r="V10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -13705,25 +14905,35 @@
       </c>
       <c r="O11" s="10" t="inlineStr">
         <is>
+          <t>n/a, no source</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>Nothing to prove. No system this report can reach holds this figure</t>
+        </is>
+      </c>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="R11" s="17" t="inlineStr">
         <is>
           <t>Decision needed</t>
         </is>
       </c>
-      <c r="Q11" s="10" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>Ask for access to the IR Dashboard shown on slide 67, and ask what is available in Opus. Why: both are their own questions to us, and the IR Dashboard may already hold most of this</t>
         </is>
       </c>
-      <c r="R11" s="10" t="inlineStr"/>
-      <c r="S11" s="10" t="inlineStr"/>
       <c r="T11" s="10" t="inlineStr"/>
+      <c r="U11" s="10" t="inlineStr"/>
+      <c r="V11" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T11"/>
+  <autoFilter ref="A4:V11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
